--- a/input_data/Per_capita_disposable_income_by_district_2020.xlsx
+++ b/input_data/Per_capita_disposable_income_by_district_2020.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17160"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41449,16 +41449,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -41498,7 +41498,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -41506,14 +41506,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -41521,7 +41521,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -41529,7 +41529,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -41537,7 +41537,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -41545,7 +41545,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -41553,14 +41553,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -41568,7 +41568,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -41576,7 +41576,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -41584,14 +41584,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -41599,64 +41599,52 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -41971,19 +41959,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -41992,7 +41980,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -42016,16 +42004,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -42034,85 +42022,85 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -42123,90 +42111,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -42684,23 +42672,24 @@
   <dimension ref="A1:F2701"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9.5" style="1"/>
-    <col min="6" max="6" width="9.5" style="2"/>
+    <col min="1" max="4" width="9" style="2"/>
+    <col min="5" max="5" width="9.5" style="2"/>
+    <col min="6" max="6" width="9.5" style="3"/>
     <col min="7" max="16310" width="9" style="1"/>
+    <col min="16311" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="62.4" customHeight="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -53705,7 +53694,8 @@
       <c r="D599" s="12" t="s">
         <v>1267</v>
       </c>
-      <c r="F599" s="2"/>
+      <c r="E599" s="2"/>
+      <c r="F599" s="3"/>
     </row>
     <row r="600" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A600" s="8" t="s">
@@ -53720,7 +53710,8 @@
       <c r="D600" s="12" t="s">
         <v>1269</v>
       </c>
-      <c r="F600" s="2"/>
+      <c r="E600" s="2"/>
+      <c r="F600" s="3"/>
     </row>
     <row r="601" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A601" s="8" t="s">
@@ -53735,7 +53726,8 @@
       <c r="D601" s="12" t="s">
         <v>1271</v>
       </c>
-      <c r="F601" s="2"/>
+      <c r="E601" s="2"/>
+      <c r="F601" s="3"/>
     </row>
     <row r="602" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A602" s="8" t="s">
@@ -53750,7 +53742,8 @@
       <c r="D602" s="12" t="s">
         <v>1273</v>
       </c>
-      <c r="F602" s="2"/>
+      <c r="E602" s="2"/>
+      <c r="F602" s="3"/>
     </row>
     <row r="603" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A603" s="8" t="s">
@@ -53765,7 +53758,8 @@
       <c r="D603" s="12" t="s">
         <v>1275</v>
       </c>
-      <c r="F603" s="2"/>
+      <c r="E603" s="2"/>
+      <c r="F603" s="3"/>
     </row>
     <row r="604" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A604" s="8" t="s">
@@ -53780,7 +53774,8 @@
       <c r="D604" s="12" t="s">
         <v>1277</v>
       </c>
-      <c r="F604" s="2"/>
+      <c r="E604" s="2"/>
+      <c r="F604" s="3"/>
     </row>
     <row r="605" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A605" s="8" t="s">
@@ -53795,7 +53790,8 @@
       <c r="D605" s="12" t="s">
         <v>1279</v>
       </c>
-      <c r="F605" s="2"/>
+      <c r="E605" s="2"/>
+      <c r="F605" s="3"/>
     </row>
     <row r="606" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A606" s="8" t="s">
@@ -53810,7 +53806,8 @@
       <c r="D606" s="12" t="s">
         <v>1282</v>
       </c>
-      <c r="F606" s="2"/>
+      <c r="E606" s="2"/>
+      <c r="F606" s="3"/>
     </row>
     <row r="607" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A607" s="8" t="s">
@@ -53825,7 +53822,8 @@
       <c r="D607" s="12" t="s">
         <v>1285</v>
       </c>
-      <c r="F607" s="2"/>
+      <c r="E607" s="2"/>
+      <c r="F607" s="3"/>
     </row>
     <row r="608" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A608" s="8" t="s">
@@ -53840,7 +53838,8 @@
       <c r="D608" s="12" t="s">
         <v>1287</v>
       </c>
-      <c r="F608" s="2"/>
+      <c r="E608" s="2"/>
+      <c r="F608" s="3"/>
     </row>
     <row r="609" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A609" s="8" t="s">
@@ -53855,7 +53854,8 @@
       <c r="D609" s="12" t="s">
         <v>1289</v>
       </c>
-      <c r="F609" s="2"/>
+      <c r="E609" s="2"/>
+      <c r="F609" s="3"/>
     </row>
     <row r="610" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A610" s="8" t="s">
@@ -53870,7 +53870,8 @@
       <c r="D610" s="12" t="s">
         <v>1291</v>
       </c>
-      <c r="F610" s="2"/>
+      <c r="E610" s="2"/>
+      <c r="F610" s="3"/>
     </row>
     <row r="611" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A611" s="8" t="s">
@@ -53885,7 +53886,8 @@
       <c r="D611" s="12" t="s">
         <v>1293</v>
       </c>
-      <c r="F611" s="2"/>
+      <c r="E611" s="2"/>
+      <c r="F611" s="3"/>
     </row>
     <row r="612" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A612" s="8" t="s">
@@ -53900,7 +53902,8 @@
       <c r="D612" s="12" t="s">
         <v>1295</v>
       </c>
-      <c r="F612" s="2"/>
+      <c r="E612" s="2"/>
+      <c r="F612" s="3"/>
     </row>
     <row r="613" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A613" s="8" t="s">
@@ -53915,7 +53918,8 @@
       <c r="D613" s="12" t="s">
         <v>1297</v>
       </c>
-      <c r="F613" s="2"/>
+      <c r="E613" s="2"/>
+      <c r="F613" s="3"/>
     </row>
     <row r="614" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A614" s="8" t="s">
@@ -53930,7 +53934,8 @@
       <c r="D614" s="12" t="s">
         <v>1300</v>
       </c>
-      <c r="F614" s="2"/>
+      <c r="E614" s="2"/>
+      <c r="F614" s="3"/>
     </row>
     <row r="615" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A615" s="8" t="s">
@@ -53945,7 +53950,8 @@
       <c r="D615" s="12" t="s">
         <v>1302</v>
       </c>
-      <c r="F615" s="2"/>
+      <c r="E615" s="2"/>
+      <c r="F615" s="3"/>
     </row>
     <row r="616" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A616" s="8" t="s">
@@ -53960,7 +53966,8 @@
       <c r="D616" s="12" t="s">
         <v>1304</v>
       </c>
-      <c r="F616" s="2"/>
+      <c r="E616" s="2"/>
+      <c r="F616" s="3"/>
     </row>
     <row r="617" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A617" s="8" t="s">
@@ -53975,7 +53982,8 @@
       <c r="D617" s="12" t="s">
         <v>1306</v>
       </c>
-      <c r="F617" s="2"/>
+      <c r="E617" s="2"/>
+      <c r="F617" s="3"/>
     </row>
     <row r="618" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A618" s="8" t="s">
@@ -53990,7 +53998,8 @@
       <c r="D618" s="12" t="s">
         <v>1308</v>
       </c>
-      <c r="F618" s="2"/>
+      <c r="E618" s="2"/>
+      <c r="F618" s="3"/>
     </row>
     <row r="619" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A619" s="8" t="s">
@@ -54005,7 +54014,8 @@
       <c r="D619" s="12" t="s">
         <v>1310</v>
       </c>
-      <c r="F619" s="2"/>
+      <c r="E619" s="2"/>
+      <c r="F619" s="3"/>
     </row>
     <row r="620" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A620" s="8" t="s">
@@ -54020,7 +54030,8 @@
       <c r="D620" s="12" t="s">
         <v>1313</v>
       </c>
-      <c r="F620" s="2"/>
+      <c r="E620" s="2"/>
+      <c r="F620" s="3"/>
     </row>
     <row r="621" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A621" s="8" t="s">
@@ -54035,7 +54046,8 @@
       <c r="D621" s="12" t="s">
         <v>1315</v>
       </c>
-      <c r="F621" s="2"/>
+      <c r="E621" s="2"/>
+      <c r="F621" s="3"/>
     </row>
     <row r="622" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A622" s="8" t="s">
@@ -54050,7 +54062,8 @@
       <c r="D622" s="12" t="s">
         <v>1317</v>
       </c>
-      <c r="F622" s="2"/>
+      <c r="E622" s="2"/>
+      <c r="F622" s="3"/>
     </row>
     <row r="623" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A623" s="8" t="s">
@@ -54065,7 +54078,8 @@
       <c r="D623" s="12" t="s">
         <v>1319</v>
       </c>
-      <c r="F623" s="2"/>
+      <c r="E623" s="2"/>
+      <c r="F623" s="3"/>
     </row>
     <row r="624" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A624" s="8" t="s">
@@ -54080,7 +54094,8 @@
       <c r="D624" s="12" t="s">
         <v>1321</v>
       </c>
-      <c r="F624" s="2"/>
+      <c r="E624" s="2"/>
+      <c r="F624" s="3"/>
     </row>
     <row r="625" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A625" s="8" t="s">
@@ -54095,7 +54110,8 @@
       <c r="D625" s="12" t="s">
         <v>1323</v>
       </c>
-      <c r="F625" s="2"/>
+      <c r="E625" s="2"/>
+      <c r="F625" s="3"/>
     </row>
     <row r="626" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A626" s="8" t="s">
@@ -54110,7 +54126,8 @@
       <c r="D626" s="12" t="s">
         <v>1325</v>
       </c>
-      <c r="F626" s="2"/>
+      <c r="E626" s="2"/>
+      <c r="F626" s="3"/>
     </row>
     <row r="627" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A627" s="8" t="s">
@@ -54125,7 +54142,8 @@
       <c r="D627" s="12" t="s">
         <v>1327</v>
       </c>
-      <c r="F627" s="2"/>
+      <c r="E627" s="2"/>
+      <c r="F627" s="3"/>
     </row>
     <row r="628" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A628" s="8" t="s">
@@ -54140,7 +54158,8 @@
       <c r="D628" s="12" t="s">
         <v>1329</v>
       </c>
-      <c r="F628" s="2"/>
+      <c r="E628" s="2"/>
+      <c r="F628" s="3"/>
     </row>
     <row r="629" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A629" s="8" t="s">
@@ -54155,7 +54174,8 @@
       <c r="D629" s="12" t="s">
         <v>1331</v>
       </c>
-      <c r="F629" s="2"/>
+      <c r="E629" s="2"/>
+      <c r="F629" s="3"/>
     </row>
     <row r="630" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A630" s="8" t="s">
@@ -54170,7 +54190,8 @@
       <c r="D630" s="12" t="s">
         <v>1334</v>
       </c>
-      <c r="F630" s="2"/>
+      <c r="E630" s="2"/>
+      <c r="F630" s="3"/>
     </row>
     <row r="631" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A631" s="8" t="s">
@@ -54185,7 +54206,8 @@
       <c r="D631" s="12" t="s">
         <v>1336</v>
       </c>
-      <c r="F631" s="2"/>
+      <c r="E631" s="2"/>
+      <c r="F631" s="3"/>
     </row>
     <row r="632" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A632" s="8" t="s">
@@ -54200,7 +54222,8 @@
       <c r="D632" s="12" t="s">
         <v>1338</v>
       </c>
-      <c r="F632" s="2"/>
+      <c r="E632" s="2"/>
+      <c r="F632" s="3"/>
     </row>
     <row r="633" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A633" s="7" t="s">
@@ -54215,7 +54238,8 @@
       <c r="D633" s="12" t="s">
         <v>1341</v>
       </c>
-      <c r="F633" s="2"/>
+      <c r="E633" s="2"/>
+      <c r="F633" s="3"/>
     </row>
     <row r="634" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A634" s="8" t="s">
@@ -54230,7 +54254,8 @@
       <c r="D634" s="12" t="s">
         <v>1343</v>
       </c>
-      <c r="F634" s="2"/>
+      <c r="E634" s="2"/>
+      <c r="F634" s="3"/>
     </row>
     <row r="635" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A635" s="8" t="s">
@@ -54245,7 +54270,8 @@
       <c r="D635" s="12" t="s">
         <v>1345</v>
       </c>
-      <c r="F635" s="2"/>
+      <c r="E635" s="2"/>
+      <c r="F635" s="3"/>
     </row>
     <row r="636" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A636" s="8" t="s">
@@ -54260,7 +54286,8 @@
       <c r="D636" s="12" t="s">
         <v>1347</v>
       </c>
-      <c r="F636" s="2"/>
+      <c r="E636" s="2"/>
+      <c r="F636" s="3"/>
     </row>
     <row r="637" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A637" s="8" t="s">
@@ -54275,7 +54302,8 @@
       <c r="D637" s="12" t="s">
         <v>1349</v>
       </c>
-      <c r="F637" s="2"/>
+      <c r="E637" s="2"/>
+      <c r="F637" s="3"/>
     </row>
     <row r="638" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A638" s="8" t="s">
@@ -54290,7 +54318,8 @@
       <c r="D638" s="12" t="s">
         <v>1351</v>
       </c>
-      <c r="F638" s="2"/>
+      <c r="E638" s="2"/>
+      <c r="F638" s="3"/>
     </row>
     <row r="639" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A639" s="8" t="s">
@@ -54305,7 +54334,8 @@
       <c r="D639" s="12" t="s">
         <v>1353</v>
       </c>
-      <c r="F639" s="2"/>
+      <c r="E639" s="2"/>
+      <c r="F639" s="3"/>
     </row>
     <row r="640" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A640" s="8" t="s">
@@ -54320,7 +54350,8 @@
       <c r="D640" s="12" t="s">
         <v>1355</v>
       </c>
-      <c r="F640" s="2"/>
+      <c r="E640" s="2"/>
+      <c r="F640" s="3"/>
     </row>
     <row r="641" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A641" s="8" t="s">
@@ -54335,7 +54366,8 @@
       <c r="D641" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="F641" s="2"/>
+      <c r="E641" s="2"/>
+      <c r="F641" s="3"/>
     </row>
     <row r="642" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A642" s="8" t="s">
@@ -54350,7 +54382,8 @@
       <c r="D642" s="12" t="s">
         <v>1359</v>
       </c>
-      <c r="F642" s="2"/>
+      <c r="E642" s="2"/>
+      <c r="F642" s="3"/>
     </row>
     <row r="643" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A643" s="8" t="s">
@@ -54365,7 +54398,8 @@
       <c r="D643" s="12" t="s">
         <v>1361</v>
       </c>
-      <c r="F643" s="2"/>
+      <c r="E643" s="2"/>
+      <c r="F643" s="3"/>
     </row>
     <row r="644" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A644" s="8" t="s">
@@ -54380,7 +54414,8 @@
       <c r="D644" s="12" t="s">
         <v>1363</v>
       </c>
-      <c r="F644" s="2"/>
+      <c r="E644" s="2"/>
+      <c r="F644" s="3"/>
     </row>
     <row r="645" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A645" s="8" t="s">
@@ -54395,7 +54430,8 @@
       <c r="D645" s="12" t="s">
         <v>1365</v>
       </c>
-      <c r="F645" s="2"/>
+      <c r="E645" s="2"/>
+      <c r="F645" s="3"/>
     </row>
     <row r="646" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A646" s="8" t="s">
@@ -54410,7 +54446,8 @@
       <c r="D646" s="12" t="s">
         <v>1367</v>
       </c>
-      <c r="F646" s="2"/>
+      <c r="E646" s="2"/>
+      <c r="F646" s="3"/>
     </row>
     <row r="647" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A647" s="8" t="s">
@@ -54425,7 +54462,8 @@
       <c r="D647" s="12" t="s">
         <v>1369</v>
       </c>
-      <c r="F647" s="2"/>
+      <c r="E647" s="2"/>
+      <c r="F647" s="3"/>
     </row>
     <row r="648" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A648" s="8" t="s">
@@ -54440,7 +54478,8 @@
       <c r="D648" s="12" t="s">
         <v>1371</v>
       </c>
-      <c r="F648" s="2"/>
+      <c r="E648" s="2"/>
+      <c r="F648" s="3"/>
     </row>
     <row r="649" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A649" s="7" t="s">
@@ -54455,7 +54494,8 @@
       <c r="D649" s="12" t="s">
         <v>1375</v>
       </c>
-      <c r="F649" s="2"/>
+      <c r="E649" s="2"/>
+      <c r="F649" s="3"/>
     </row>
     <row r="650" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A650" s="8" t="s">
@@ -54470,7 +54510,8 @@
       <c r="D650" s="12" t="s">
         <v>1377</v>
       </c>
-      <c r="F650" s="2"/>
+      <c r="E650" s="2"/>
+      <c r="F650" s="3"/>
     </row>
     <row r="651" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A651" s="8" t="s">
@@ -54485,7 +54526,8 @@
       <c r="D651" s="12" t="s">
         <v>1379</v>
       </c>
-      <c r="F651" s="2"/>
+      <c r="E651" s="2"/>
+      <c r="F651" s="3"/>
     </row>
     <row r="652" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A652" s="8" t="s">
@@ -54500,7 +54542,8 @@
       <c r="D652" s="12" t="s">
         <v>1381</v>
       </c>
-      <c r="F652" s="2"/>
+      <c r="E652" s="2"/>
+      <c r="F652" s="3"/>
     </row>
     <row r="653" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A653" s="8" t="s">
@@ -54518,7 +54561,7 @@
       <c r="E653" s="8">
         <v>62498</v>
       </c>
-      <c r="F653" s="2"/>
+      <c r="F653" s="3"/>
     </row>
     <row r="654" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A654" s="8" t="s">
@@ -54533,7 +54576,8 @@
       <c r="D654" s="12" t="s">
         <v>1385</v>
       </c>
-      <c r="F654" s="2"/>
+      <c r="E654" s="2"/>
+      <c r="F654" s="3"/>
     </row>
     <row r="655" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A655" s="8" t="s">
@@ -54548,7 +54592,8 @@
       <c r="D655" s="12" t="s">
         <v>1387</v>
       </c>
-      <c r="F655" s="2"/>
+      <c r="E655" s="2"/>
+      <c r="F655" s="3"/>
     </row>
     <row r="656" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A656" s="8" t="s">
@@ -54566,7 +54611,7 @@
       <c r="E656" s="8">
         <v>65410</v>
       </c>
-      <c r="F656" s="2"/>
+      <c r="F656" s="3"/>
     </row>
     <row r="657" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A657" s="8" t="s">
@@ -54584,7 +54629,7 @@
       <c r="E657" s="8">
         <v>60785</v>
       </c>
-      <c r="F657" s="2"/>
+      <c r="F657" s="3"/>
     </row>
     <row r="658" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A658" s="8" t="s">
@@ -54602,7 +54647,7 @@
       <c r="E658" s="8">
         <v>59740</v>
       </c>
-      <c r="F658" s="2"/>
+      <c r="F658" s="3"/>
     </row>
     <row r="659" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A659" s="8" t="s">
@@ -54620,7 +54665,7 @@
       <c r="E659" s="8">
         <v>60295</v>
       </c>
-      <c r="F659" s="2"/>
+      <c r="F659" s="3"/>
     </row>
     <row r="660" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A660" s="8" t="s">
@@ -54636,7 +54681,7 @@
         <v>1398</v>
       </c>
       <c r="E660" s="8"/>
-      <c r="F660" s="2"/>
+      <c r="F660" s="3"/>
     </row>
     <row r="661" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A661" s="8" t="s">
@@ -54651,7 +54696,8 @@
       <c r="D661" s="12" t="s">
         <v>1400</v>
       </c>
-      <c r="F661" s="2">
+      <c r="E661" s="2"/>
+      <c r="F661" s="3">
         <v>36142.59</v>
       </c>
     </row>
@@ -54668,7 +54714,8 @@
       <c r="D662" s="12" t="s">
         <v>1402</v>
       </c>
-      <c r="F662" s="2">
+      <c r="E662" s="2"/>
+      <c r="F662" s="3">
         <v>36163.6</v>
       </c>
     </row>
@@ -54685,7 +54732,8 @@
       <c r="D663" s="12" t="s">
         <v>1404</v>
       </c>
-      <c r="F663" s="2">
+      <c r="E663" s="2"/>
+      <c r="F663" s="3">
         <v>35955.89</v>
       </c>
     </row>
@@ -54702,7 +54750,8 @@
       <c r="D664" s="12" t="s">
         <v>1406</v>
       </c>
-      <c r="F664" s="2"/>
+      <c r="E664" s="2"/>
+      <c r="F664" s="3"/>
     </row>
     <row r="665" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A665" s="8" t="s">
@@ -54757,7 +54806,8 @@
       <c r="D667" s="12" t="s">
         <v>1412</v>
       </c>
-      <c r="F667" s="2"/>
+      <c r="E667" s="2"/>
+      <c r="F667" s="3"/>
     </row>
     <row r="668" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A668" s="8" t="s">
@@ -54772,7 +54822,8 @@
       <c r="D668" s="12" t="s">
         <v>1414</v>
       </c>
-      <c r="F668" s="2"/>
+      <c r="E668" s="2"/>
+      <c r="F668" s="3"/>
     </row>
     <row r="669" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A669" s="8" t="s">
@@ -54790,7 +54841,7 @@
       <c r="E669" s="8">
         <v>37023</v>
       </c>
-      <c r="F669" s="2"/>
+      <c r="F669" s="3"/>
     </row>
     <row r="670" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A670" s="8" t="s">
@@ -54805,7 +54856,8 @@
       <c r="D670" s="12" t="s">
         <v>1418</v>
       </c>
-      <c r="F670" s="2"/>
+      <c r="E670" s="2"/>
+      <c r="F670" s="3"/>
     </row>
     <row r="671" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A671" s="8" t="s">
@@ -54823,7 +54875,7 @@
       <c r="E671" s="8">
         <v>42191</v>
       </c>
-      <c r="F671" s="2"/>
+      <c r="F671" s="3"/>
     </row>
     <row r="672" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A672" s="8" t="s">
@@ -54938,7 +54990,8 @@
       <c r="D677" s="12" t="s">
         <v>1433</v>
       </c>
-      <c r="F677" s="2"/>
+      <c r="E677" s="2"/>
+      <c r="F677" s="3"/>
     </row>
     <row r="678" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A678" s="8" t="s">
@@ -54953,7 +55006,8 @@
       <c r="D678" s="12" t="s">
         <v>1435</v>
       </c>
-      <c r="F678" s="2"/>
+      <c r="E678" s="2"/>
+      <c r="F678" s="3"/>
     </row>
     <row r="679" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A679" s="8" t="s">
@@ -54968,7 +55022,8 @@
       <c r="D679" s="12" t="s">
         <v>1437</v>
       </c>
-      <c r="F679" s="2"/>
+      <c r="E679" s="2"/>
+      <c r="F679" s="3"/>
     </row>
     <row r="680" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A680" s="8" t="s">
@@ -54986,7 +55041,7 @@
       <c r="E680" s="8">
         <v>63434</v>
       </c>
-      <c r="F680" s="2"/>
+      <c r="F680" s="3"/>
     </row>
     <row r="681" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A681" s="8" t="s">
@@ -55004,7 +55059,7 @@
       <c r="E681" s="8">
         <v>57097</v>
       </c>
-      <c r="F681" s="2"/>
+      <c r="F681" s="3"/>
     </row>
     <row r="682" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A682" s="8" t="s">
@@ -55039,7 +55094,8 @@
       <c r="D683" s="12" t="s">
         <v>1446</v>
       </c>
-      <c r="F683" s="2"/>
+      <c r="E683" s="2"/>
+      <c r="F683" s="3"/>
     </row>
     <row r="684" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A684" s="8" t="s">
@@ -55054,7 +55110,8 @@
       <c r="D684" s="12" t="s">
         <v>1448</v>
       </c>
-      <c r="F684" s="2"/>
+      <c r="E684" s="2"/>
+      <c r="F684" s="3"/>
     </row>
     <row r="685" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A685" s="8" t="s">
@@ -55069,7 +55126,8 @@
       <c r="D685" s="12" t="s">
         <v>1450</v>
       </c>
-      <c r="F685" s="2"/>
+      <c r="E685" s="2"/>
+      <c r="F685" s="3"/>
     </row>
     <row r="686" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A686" s="8" t="s">
@@ -55084,7 +55142,8 @@
       <c r="D686" s="12" t="s">
         <v>1452</v>
       </c>
-      <c r="F686" s="2"/>
+      <c r="E686" s="2"/>
+      <c r="F686" s="3"/>
     </row>
     <row r="687" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A687" s="8" t="s">
@@ -55102,7 +55161,7 @@
       <c r="E687" s="8">
         <v>70910</v>
       </c>
-      <c r="F687" s="2"/>
+      <c r="F687" s="3"/>
     </row>
     <row r="688" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A688" s="8" t="s">
@@ -55197,7 +55256,8 @@
       <c r="D692" s="12" t="s">
         <v>1465</v>
       </c>
-      <c r="F692" s="2"/>
+      <c r="E692" s="2"/>
+      <c r="F692" s="3"/>
     </row>
     <row r="693" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A693" s="8" t="s">
@@ -55215,7 +55275,7 @@
       <c r="E693" s="8">
         <v>54453</v>
       </c>
-      <c r="F693" s="2"/>
+      <c r="F693" s="3"/>
     </row>
     <row r="694" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A694" s="8" t="s">
@@ -55230,7 +55290,8 @@
       <c r="D694" s="12" t="s">
         <v>1469</v>
       </c>
-      <c r="F694" s="2"/>
+      <c r="E694" s="2"/>
+      <c r="F694" s="3"/>
     </row>
     <row r="695" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A695" s="8" t="s">
@@ -55305,7 +55366,8 @@
       <c r="D698" s="12" t="s">
         <v>1477</v>
       </c>
-      <c r="F698" s="2"/>
+      <c r="E698" s="2"/>
+      <c r="F698" s="3"/>
     </row>
     <row r="699" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A699" s="8" t="s">
@@ -55340,7 +55402,8 @@
       <c r="D700" s="12" t="s">
         <v>1482</v>
       </c>
-      <c r="F700" s="2"/>
+      <c r="E700" s="2"/>
+      <c r="F700" s="3"/>
     </row>
     <row r="701" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A701" s="8" t="s">
@@ -55355,7 +55418,8 @@
       <c r="D701" s="12" t="s">
         <v>1483</v>
       </c>
-      <c r="F701" s="2"/>
+      <c r="E701" s="2"/>
+      <c r="F701" s="3"/>
     </row>
     <row r="702" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A702" s="8" t="s">
@@ -55373,7 +55437,7 @@
       <c r="E702" s="8">
         <v>35786</v>
       </c>
-      <c r="F702" s="2"/>
+      <c r="F702" s="3"/>
     </row>
     <row r="703" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A703" s="8" t="s">
@@ -55451,7 +55515,7 @@
       <c r="E706" s="8">
         <v>34889</v>
       </c>
-      <c r="F706" s="2">
+      <c r="F706" s="3">
         <v>20025</v>
       </c>
     </row>
@@ -55471,7 +55535,7 @@
       <c r="E707" s="8">
         <v>37485</v>
       </c>
-      <c r="F707" s="2">
+      <c r="F707" s="3">
         <v>18471.1</v>
       </c>
     </row>
@@ -55488,7 +55552,8 @@
       <c r="D708" s="12" t="s">
         <v>1498</v>
       </c>
-      <c r="F708" s="2">
+      <c r="E708" s="2"/>
+      <c r="F708" s="3">
         <v>24416</v>
       </c>
     </row>
@@ -55508,7 +55573,7 @@
       <c r="E709" s="8">
         <v>40371</v>
       </c>
-      <c r="F709" s="2">
+      <c r="F709" s="3">
         <v>21631.1</v>
       </c>
     </row>
@@ -55585,7 +55650,8 @@
       <c r="D713" s="12" t="s">
         <v>1509</v>
       </c>
-      <c r="F713" s="2"/>
+      <c r="E713" s="2"/>
+      <c r="F713" s="3"/>
     </row>
     <row r="714" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A714" s="8" t="s">
@@ -55603,7 +55669,7 @@
       <c r="E714" s="8">
         <v>43739</v>
       </c>
-      <c r="F714" s="2"/>
+      <c r="F714" s="3"/>
     </row>
     <row r="715" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A715" s="8" t="s">
@@ -55621,7 +55687,7 @@
       <c r="E715" s="8">
         <v>40975</v>
       </c>
-      <c r="F715" s="2"/>
+      <c r="F715" s="3"/>
     </row>
     <row r="716" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A716" s="8" t="s">
@@ -55756,7 +55822,8 @@
       <c r="D722" s="12" t="s">
         <v>1528</v>
       </c>
-      <c r="F722" s="2"/>
+      <c r="E722" s="2"/>
+      <c r="F722" s="3"/>
     </row>
     <row r="723" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A723" s="8" t="s">
@@ -55774,7 +55841,7 @@
       <c r="E723" s="8">
         <v>53008</v>
       </c>
-      <c r="F723" s="2"/>
+      <c r="F723" s="3"/>
     </row>
     <row r="724" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A724" s="8" t="s">
@@ -55792,7 +55859,7 @@
       <c r="E724" s="8">
         <v>48487</v>
       </c>
-      <c r="F724" s="2"/>
+      <c r="F724" s="3"/>
     </row>
     <row r="725" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A725" s="8" t="s">
@@ -55867,7 +55934,8 @@
       <c r="D728" s="12" t="s">
         <v>1541</v>
       </c>
-      <c r="F728" s="2"/>
+      <c r="E728" s="2"/>
+      <c r="F728" s="3"/>
     </row>
     <row r="729" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A729" s="8" t="s">
@@ -55882,7 +55950,8 @@
       <c r="D729" s="12" t="s">
         <v>1543</v>
       </c>
-      <c r="F729" s="2"/>
+      <c r="E729" s="2"/>
+      <c r="F729" s="3"/>
     </row>
     <row r="730" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A730" s="8" t="s">
@@ -55900,7 +55969,7 @@
       <c r="E730" s="8">
         <v>53568</v>
       </c>
-      <c r="F730" s="2"/>
+      <c r="F730" s="3"/>
     </row>
     <row r="731" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A731" s="8" t="s">
@@ -55975,7 +56044,8 @@
       <c r="D734" s="12" t="s">
         <v>1554</v>
       </c>
-      <c r="F734" s="2"/>
+      <c r="E734" s="2"/>
+      <c r="F734" s="3"/>
     </row>
     <row r="735" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A735" s="8" t="s">
@@ -55990,7 +56060,8 @@
       <c r="D735" s="12" t="s">
         <v>1556</v>
       </c>
-      <c r="F735" s="2"/>
+      <c r="E735" s="2"/>
+      <c r="F735" s="3"/>
     </row>
     <row r="736" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A736" s="8" t="s">
@@ -56008,7 +56079,7 @@
       <c r="E736" s="8">
         <v>49355</v>
       </c>
-      <c r="F736" s="2"/>
+      <c r="F736" s="3"/>
     </row>
     <row r="737" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A737" s="8" t="s">
@@ -56083,7 +56154,8 @@
       <c r="D740" s="12" t="s">
         <v>1567</v>
       </c>
-      <c r="F740" s="2"/>
+      <c r="E740" s="2"/>
+      <c r="F740" s="3"/>
     </row>
     <row r="741" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A741" s="8" t="s">
@@ -56101,7 +56173,7 @@
       <c r="E741" s="8">
         <v>31432</v>
       </c>
-      <c r="F741" s="2"/>
+      <c r="F741" s="3"/>
     </row>
     <row r="742" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A742" s="8" t="s">
@@ -56176,7 +56248,8 @@
       <c r="D745" s="12" t="s">
         <v>1579</v>
       </c>
-      <c r="F745" s="2"/>
+      <c r="E745" s="2"/>
+      <c r="F745" s="3"/>
     </row>
     <row r="746" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A746" s="8" t="s">
@@ -56191,7 +56264,8 @@
       <c r="D746" s="12" t="s">
         <v>1581</v>
       </c>
-      <c r="F746" s="2"/>
+      <c r="E746" s="2"/>
+      <c r="F746" s="3"/>
     </row>
     <row r="747" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A747" s="8" t="s">
@@ -56206,7 +56280,8 @@
       <c r="D747" s="12" t="s">
         <v>1583</v>
       </c>
-      <c r="F747" s="2"/>
+      <c r="E747" s="2"/>
+      <c r="F747" s="3"/>
     </row>
     <row r="748" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A748" s="8" t="s">
@@ -56221,7 +56296,8 @@
       <c r="D748" s="12" t="s">
         <v>1585</v>
       </c>
-      <c r="F748" s="2"/>
+      <c r="E748" s="2"/>
+      <c r="F748" s="3"/>
     </row>
     <row r="749" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A749" s="8" t="s">
@@ -56236,7 +56312,8 @@
       <c r="D749" s="12" t="s">
         <v>1587</v>
       </c>
-      <c r="F749" s="2"/>
+      <c r="E749" s="2"/>
+      <c r="F749" s="3"/>
     </row>
     <row r="750" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A750" s="8" t="s">
@@ -56251,7 +56328,8 @@
       <c r="D750" s="12" t="s">
         <v>1589</v>
       </c>
-      <c r="F750" s="2"/>
+      <c r="E750" s="2"/>
+      <c r="F750" s="3"/>
     </row>
     <row r="751" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A751" s="8" t="s">
@@ -57926,7 +58004,8 @@
       <c r="D834" s="12" t="s">
         <v>1768</v>
       </c>
-      <c r="F834" s="2"/>
+      <c r="E834" s="2"/>
+      <c r="F834" s="3"/>
     </row>
     <row r="835" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A835" s="8" t="s">
@@ -57941,7 +58020,8 @@
       <c r="D835" s="12" t="s">
         <v>1770</v>
       </c>
-      <c r="F835" s="2"/>
+      <c r="E835" s="2"/>
+      <c r="F835" s="3"/>
     </row>
     <row r="836" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A836" s="8" t="s">
@@ -57956,7 +58036,8 @@
       <c r="D836" s="12" t="s">
         <v>1772</v>
       </c>
-      <c r="F836" s="2"/>
+      <c r="E836" s="2"/>
+      <c r="F836" s="3"/>
     </row>
     <row r="837" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A837" s="8" t="s">
@@ -57971,7 +58052,8 @@
       <c r="D837" s="12" t="s">
         <v>1774</v>
       </c>
-      <c r="F837" s="2"/>
+      <c r="E837" s="2"/>
+      <c r="F837" s="3"/>
     </row>
     <row r="838" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A838" s="8" t="s">
@@ -57986,6 +58068,7 @@
       <c r="D838" s="12" t="s">
         <v>1776</v>
       </c>
+      <c r="E838" s="2"/>
       <c r="F838" s="8">
         <v>23261</v>
       </c>
@@ -58003,6 +58086,7 @@
       <c r="D839" s="12" t="s">
         <v>1778</v>
       </c>
+      <c r="E839" s="2"/>
       <c r="F839" s="8">
         <v>25516</v>
       </c>
@@ -58020,6 +58104,7 @@
       <c r="D840" s="12" t="s">
         <v>1780</v>
       </c>
+      <c r="E840" s="2"/>
       <c r="F840" s="8">
         <v>26062</v>
       </c>
@@ -58037,6 +58122,7 @@
       <c r="D841" s="12" t="s">
         <v>1782</v>
       </c>
+      <c r="E841" s="2"/>
       <c r="F841" s="8">
         <v>22672</v>
       </c>
@@ -58054,6 +58140,7 @@
       <c r="D842" s="12" t="s">
         <v>1784</v>
       </c>
+      <c r="E842" s="2"/>
       <c r="F842" s="8">
         <v>23896</v>
       </c>
@@ -58071,6 +58158,7 @@
       <c r="D843" s="12" t="s">
         <v>1787</v>
       </c>
+      <c r="E843" s="2"/>
       <c r="F843" s="8">
         <v>29986</v>
       </c>
@@ -58088,6 +58176,7 @@
       <c r="D844" s="12" t="s">
         <v>1789</v>
       </c>
+      <c r="E844" s="2"/>
       <c r="F844" s="8">
         <v>26228</v>
       </c>
@@ -58105,6 +58194,7 @@
       <c r="D845" s="12" t="s">
         <v>1791</v>
       </c>
+      <c r="E845" s="2"/>
       <c r="F845" s="8">
         <v>26334</v>
       </c>
@@ -58122,7 +58212,8 @@
       <c r="D846" s="12" t="s">
         <v>1793</v>
       </c>
-      <c r="F846" s="2"/>
+      <c r="E846" s="2"/>
+      <c r="F846" s="3"/>
     </row>
     <row r="847" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A847" s="8" t="s">
@@ -58137,7 +58228,8 @@
       <c r="D847" s="12" t="s">
         <v>1795</v>
       </c>
-      <c r="F847" s="2"/>
+      <c r="E847" s="2"/>
+      <c r="F847" s="3"/>
     </row>
     <row r="848" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A848" s="8" t="s">
@@ -58152,6 +58244,7 @@
       <c r="D848" s="12" t="s">
         <v>1797</v>
       </c>
+      <c r="E848" s="2"/>
       <c r="F848" s="8">
         <v>26356</v>
       </c>
@@ -58169,6 +58262,7 @@
       <c r="D849" s="12" t="s">
         <v>1799</v>
       </c>
+      <c r="E849" s="2"/>
       <c r="F849" s="8">
         <v>26586</v>
       </c>
@@ -58186,6 +58280,7 @@
       <c r="D850" s="12" t="s">
         <v>1801</v>
       </c>
+      <c r="E850" s="2"/>
       <c r="F850" s="8">
         <v>21752</v>
       </c>
@@ -58203,6 +58298,7 @@
       <c r="D851" s="12" t="s">
         <v>1804</v>
       </c>
+      <c r="E851" s="2"/>
       <c r="F851" s="8">
         <v>17126</v>
       </c>
@@ -58220,6 +58316,7 @@
       <c r="D852" s="12" t="s">
         <v>1806</v>
       </c>
+      <c r="E852" s="2"/>
       <c r="F852" s="8">
         <v>17795</v>
       </c>
@@ -58237,6 +58334,7 @@
       <c r="D853" s="12" t="s">
         <v>1808</v>
       </c>
+      <c r="E853" s="2"/>
       <c r="F853" s="8">
         <v>16666</v>
       </c>
@@ -58254,6 +58352,7 @@
       <c r="D854" s="12" t="s">
         <v>1810</v>
       </c>
+      <c r="E854" s="2"/>
       <c r="F854" s="8">
         <v>16901</v>
       </c>
@@ -58271,6 +58370,7 @@
       <c r="D855" s="12" t="s">
         <v>1812</v>
       </c>
+      <c r="E855" s="2"/>
       <c r="F855" s="8">
         <v>18265</v>
       </c>
@@ -58288,6 +58388,7 @@
       <c r="D856" s="12" t="s">
         <v>1814</v>
       </c>
+      <c r="E856" s="2"/>
       <c r="F856" s="8">
         <v>18127</v>
       </c>
@@ -58305,6 +58406,7 @@
       <c r="D857" s="12" t="s">
         <v>1816</v>
       </c>
+      <c r="E857" s="2"/>
       <c r="F857" s="8">
         <v>18211</v>
       </c>
@@ -58322,6 +58424,7 @@
       <c r="D858" s="12" t="s">
         <v>1819</v>
       </c>
+      <c r="E858" s="2"/>
       <c r="F858" s="8">
         <v>17672</v>
       </c>
@@ -58339,6 +58442,7 @@
       <c r="D859" s="12" t="s">
         <v>1821</v>
       </c>
+      <c r="E859" s="2"/>
       <c r="F859" s="8">
         <v>18727</v>
       </c>
@@ -58356,6 +58460,7 @@
       <c r="D860" s="12" t="s">
         <v>1823</v>
       </c>
+      <c r="E860" s="2"/>
       <c r="F860" s="8">
         <v>17879</v>
       </c>
@@ -58373,6 +58478,7 @@
       <c r="D861" s="12" t="s">
         <v>1825</v>
       </c>
+      <c r="E861" s="2"/>
       <c r="F861" s="8">
         <v>18044</v>
       </c>
@@ -58390,6 +58496,7 @@
       <c r="D862" s="12" t="s">
         <v>1827</v>
       </c>
+      <c r="E862" s="2"/>
       <c r="F862" s="8">
         <v>17054</v>
       </c>
@@ -58407,6 +58514,7 @@
       <c r="D863" s="12" t="s">
         <v>1829</v>
       </c>
+      <c r="E863" s="2"/>
       <c r="F863" s="8">
         <v>17336</v>
       </c>
@@ -58424,6 +58532,7 @@
       <c r="D864" s="12" t="s">
         <v>1831</v>
       </c>
+      <c r="E864" s="2"/>
       <c r="F864" s="8">
         <v>13177</v>
       </c>
@@ -58441,6 +58550,7 @@
       <c r="D865" s="12" t="s">
         <v>1834</v>
       </c>
+      <c r="E865" s="2"/>
       <c r="F865" s="8">
         <v>34319</v>
       </c>
@@ -58458,6 +58568,7 @@
       <c r="D866" s="12" t="s">
         <v>1836</v>
       </c>
+      <c r="E866" s="2"/>
       <c r="F866" s="8">
         <v>33659</v>
       </c>
@@ -58475,6 +58586,7 @@
       <c r="D867" s="12" t="s">
         <v>1838</v>
       </c>
+      <c r="E867" s="2"/>
       <c r="F867" s="8">
         <v>27946</v>
       </c>
@@ -58492,6 +58604,7 @@
       <c r="D868" s="12" t="s">
         <v>1840</v>
       </c>
+      <c r="E868" s="2"/>
       <c r="F868" s="8">
         <v>28974</v>
       </c>
@@ -58509,6 +58622,7 @@
       <c r="D869" s="12" t="s">
         <v>1842</v>
       </c>
+      <c r="E869" s="2"/>
       <c r="F869" s="8">
         <v>22477</v>
       </c>
@@ -58526,6 +58640,7 @@
       <c r="D870" s="12" t="s">
         <v>1844</v>
       </c>
+      <c r="E870" s="2"/>
       <c r="F870" s="8">
         <v>22636</v>
       </c>
@@ -58543,6 +58658,7 @@
       <c r="D871" s="12" t="s">
         <v>1847</v>
       </c>
+      <c r="E871" s="2"/>
       <c r="F871" s="8">
         <v>16075</v>
       </c>
@@ -58560,6 +58676,7 @@
       <c r="D872" s="12" t="s">
         <v>1849</v>
       </c>
+      <c r="E872" s="2"/>
       <c r="F872" s="8">
         <v>15356</v>
       </c>
@@ -58577,6 +58694,7 @@
       <c r="D873" s="12" t="s">
         <v>1851</v>
       </c>
+      <c r="E873" s="2"/>
       <c r="F873" s="8">
         <v>15152</v>
       </c>
@@ -58594,6 +58712,7 @@
       <c r="D874" s="12" t="s">
         <v>1853</v>
       </c>
+      <c r="E874" s="2"/>
       <c r="F874" s="8">
         <v>15170</v>
       </c>
@@ -58611,6 +58730,7 @@
       <c r="D875" s="12" t="s">
         <v>1856</v>
       </c>
+      <c r="E875" s="2"/>
       <c r="F875" s="8">
         <v>32316</v>
       </c>
@@ -58628,6 +58748,7 @@
       <c r="D876" s="12" t="s">
         <v>1858</v>
       </c>
+      <c r="E876" s="2"/>
       <c r="F876" s="8">
         <v>26478</v>
       </c>
@@ -58645,7 +58766,8 @@
       <c r="D877" s="12" t="s">
         <v>1859</v>
       </c>
-      <c r="F877" s="2"/>
+      <c r="E877" s="2"/>
+      <c r="F877" s="3"/>
     </row>
     <row r="878" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A878" s="8" t="s">
@@ -58660,6 +58782,7 @@
       <c r="D878" s="12" t="s">
         <v>1861</v>
       </c>
+      <c r="E878" s="2"/>
       <c r="F878" s="8">
         <v>14628</v>
       </c>
@@ -58677,6 +58800,7 @@
       <c r="D879" s="12" t="s">
         <v>1864</v>
       </c>
+      <c r="E879" s="2"/>
       <c r="F879" s="8">
         <v>19418</v>
       </c>
@@ -58694,6 +58818,7 @@
       <c r="D880" s="12" t="s">
         <v>1866</v>
       </c>
+      <c r="E880" s="2"/>
       <c r="F880" s="8">
         <v>18926</v>
       </c>
@@ -58711,6 +58836,7 @@
       <c r="D881" s="12" t="s">
         <v>1868</v>
       </c>
+      <c r="E881" s="2"/>
       <c r="F881" s="8">
         <v>19680</v>
       </c>
@@ -58728,6 +58854,7 @@
       <c r="D882" s="12" t="s">
         <v>1870</v>
       </c>
+      <c r="E882" s="2"/>
       <c r="F882" s="8">
         <v>17675</v>
       </c>
@@ -58745,6 +58872,7 @@
       <c r="D883" s="12" t="s">
         <v>1872</v>
       </c>
+      <c r="E883" s="2"/>
       <c r="F883" s="8">
         <v>13811</v>
       </c>
@@ -58762,6 +58890,7 @@
       <c r="D884" s="12" t="s">
         <v>1874</v>
       </c>
+      <c r="E884" s="2"/>
       <c r="F884" s="8">
         <v>13940</v>
       </c>
@@ -58779,6 +58908,7 @@
       <c r="D885" s="12" t="s">
         <v>1876</v>
       </c>
+      <c r="E885" s="2"/>
       <c r="F885" s="8">
         <v>14131</v>
       </c>
@@ -58796,6 +58926,7 @@
       <c r="D886" s="12" t="s">
         <v>1878</v>
       </c>
+      <c r="E886" s="2"/>
       <c r="F886" s="8">
         <v>13930</v>
       </c>
@@ -58813,6 +58944,7 @@
       <c r="D887" s="12" t="s">
         <v>1880</v>
       </c>
+      <c r="E887" s="2"/>
       <c r="F887" s="8">
         <v>18333</v>
       </c>
@@ -58830,6 +58962,7 @@
       <c r="D888" s="12" t="s">
         <v>1882</v>
       </c>
+      <c r="E888" s="2"/>
       <c r="F888" s="8">
         <v>14422</v>
       </c>
@@ -58847,6 +58980,7 @@
       <c r="D889" s="12" t="s">
         <v>1885</v>
       </c>
+      <c r="E889" s="2"/>
       <c r="F889" s="8">
         <v>19428</v>
       </c>
@@ -58864,6 +58998,7 @@
       <c r="D890" s="12" t="s">
         <v>1887</v>
       </c>
+      <c r="E890" s="2"/>
       <c r="F890" s="8">
         <v>18935</v>
       </c>
@@ -58881,6 +59016,7 @@
       <c r="D891" s="12" t="s">
         <v>1889</v>
       </c>
+      <c r="E891" s="2"/>
       <c r="F891" s="8">
         <v>19145</v>
       </c>
@@ -58898,6 +59034,7 @@
       <c r="D892" s="12" t="s">
         <v>1891</v>
       </c>
+      <c r="E892" s="2"/>
       <c r="F892" s="8">
         <v>18129</v>
       </c>
@@ -58915,6 +59052,7 @@
       <c r="D893" s="12" t="s">
         <v>1893</v>
       </c>
+      <c r="E893" s="2"/>
       <c r="F893" s="8">
         <v>18089</v>
       </c>
@@ -58932,6 +59070,7 @@
       <c r="D894" s="12" t="s">
         <v>1895</v>
       </c>
+      <c r="E894" s="2"/>
       <c r="F894" s="8">
         <v>18488</v>
       </c>
@@ -58949,6 +59088,7 @@
       <c r="D895" s="12" t="s">
         <v>1897</v>
       </c>
+      <c r="E895" s="2"/>
       <c r="F895" s="8">
         <v>18084</v>
       </c>
@@ -58966,6 +59106,7 @@
       <c r="D896" s="12" t="s">
         <v>1900</v>
       </c>
+      <c r="E896" s="2"/>
       <c r="F896" s="8">
         <v>16775</v>
       </c>
@@ -58983,6 +59124,7 @@
       <c r="D897" s="12" t="s">
         <v>1902</v>
       </c>
+      <c r="E897" s="2"/>
       <c r="F897" s="8">
         <v>16249</v>
       </c>
@@ -59000,6 +59142,7 @@
       <c r="D898" s="12" t="s">
         <v>1904</v>
       </c>
+      <c r="E898" s="2"/>
       <c r="F898" s="8">
         <v>15639</v>
       </c>
@@ -59017,6 +59160,7 @@
       <c r="D899" s="12" t="s">
         <v>1906</v>
       </c>
+      <c r="E899" s="2"/>
       <c r="F899" s="8">
         <v>16040</v>
       </c>
@@ -59034,6 +59178,7 @@
       <c r="D900" s="12" t="s">
         <v>1908</v>
       </c>
+      <c r="E900" s="2"/>
       <c r="F900" s="8">
         <v>14673</v>
       </c>
@@ -59051,6 +59196,7 @@
       <c r="D901" s="12" t="s">
         <v>1910</v>
       </c>
+      <c r="E901" s="2"/>
       <c r="F901" s="8">
         <v>13874</v>
       </c>
@@ -59068,6 +59214,7 @@
       <c r="D902" s="12" t="s">
         <v>1912</v>
       </c>
+      <c r="E902" s="2"/>
       <c r="F902" s="8">
         <v>21896</v>
       </c>
@@ -59085,6 +59232,7 @@
       <c r="D903" s="12" t="s">
         <v>1914</v>
       </c>
+      <c r="E903" s="2"/>
       <c r="F903" s="8">
         <v>14592</v>
       </c>
@@ -59102,6 +59250,7 @@
       <c r="D904" s="12" t="s">
         <v>1917</v>
       </c>
+      <c r="E904" s="2"/>
       <c r="F904" s="8">
         <v>16480</v>
       </c>
@@ -59119,6 +59268,7 @@
       <c r="D905" s="12" t="s">
         <v>1919</v>
       </c>
+      <c r="E905" s="2"/>
       <c r="F905" s="8">
         <v>13426</v>
       </c>
@@ -59136,6 +59286,7 @@
       <c r="D906" s="12" t="s">
         <v>1922</v>
       </c>
+      <c r="E906" s="2"/>
       <c r="F906" s="8">
         <v>14435</v>
       </c>
@@ -59153,6 +59304,7 @@
       <c r="D907" s="12" t="s">
         <v>1924</v>
       </c>
+      <c r="E907" s="2"/>
       <c r="F907" s="8">
         <v>13723</v>
       </c>
@@ -59170,6 +59322,7 @@
       <c r="D908" s="12" t="s">
         <v>1926</v>
       </c>
+      <c r="E908" s="2"/>
       <c r="F908" s="8">
         <v>14582</v>
       </c>
@@ -59187,6 +59340,7 @@
       <c r="D909" s="12" t="s">
         <v>1928</v>
       </c>
+      <c r="E909" s="2"/>
       <c r="F909" s="8">
         <v>13565</v>
       </c>
@@ -59204,6 +59358,7 @@
       <c r="D910" s="12" t="s">
         <v>1930</v>
       </c>
+      <c r="E910" s="2"/>
       <c r="F910" s="8">
         <v>14396</v>
       </c>
@@ -59221,6 +59376,7 @@
       <c r="D911" s="12" t="s">
         <v>1932</v>
       </c>
+      <c r="E911" s="2"/>
       <c r="F911" s="8">
         <v>15550</v>
       </c>
@@ -59238,6 +59394,7 @@
       <c r="D912" s="12" t="s">
         <v>1935</v>
       </c>
+      <c r="E912" s="2"/>
       <c r="F912" s="8">
         <v>14671</v>
       </c>
@@ -59255,6 +59412,7 @@
       <c r="D913" s="12" t="s">
         <v>1937</v>
       </c>
+      <c r="E913" s="2"/>
       <c r="F913" s="8">
         <v>14681</v>
       </c>
@@ -59272,6 +59430,7 @@
       <c r="D914" s="12" t="s">
         <v>1939</v>
       </c>
+      <c r="E914" s="2"/>
       <c r="F914" s="8">
         <v>14298</v>
       </c>
@@ -59289,6 +59448,7 @@
       <c r="D915" s="12" t="s">
         <v>1941</v>
       </c>
+      <c r="E915" s="2"/>
       <c r="F915" s="8">
         <v>14410</v>
       </c>
@@ -59306,6 +59466,7 @@
       <c r="D916" s="12" t="s">
         <v>1943</v>
       </c>
+      <c r="E916" s="2"/>
       <c r="F916" s="8">
         <v>13777</v>
       </c>
@@ -59323,6 +59484,7 @@
       <c r="D917" s="12" t="s">
         <v>1945</v>
       </c>
+      <c r="E917" s="2"/>
       <c r="F917" s="8">
         <v>15456</v>
       </c>
@@ -59340,6 +59502,7 @@
       <c r="D918" s="12" t="s">
         <v>1947</v>
       </c>
+      <c r="E918" s="2"/>
       <c r="F918" s="8">
         <v>15521</v>
       </c>
@@ -59357,6 +59520,7 @@
       <c r="D919" s="12" t="s">
         <v>1949</v>
       </c>
+      <c r="E919" s="2"/>
       <c r="F919" s="8">
         <v>13543</v>
       </c>
@@ -59374,6 +59538,7 @@
       <c r="D920" s="12" t="s">
         <v>1951</v>
       </c>
+      <c r="E920" s="2"/>
       <c r="F920" s="8">
         <v>14488</v>
       </c>
@@ -59391,6 +59556,7 @@
       <c r="D921" s="12" t="s">
         <v>1953</v>
       </c>
+      <c r="E921" s="2"/>
       <c r="F921" s="8">
         <v>13524</v>
       </c>
@@ -59408,6 +59574,7 @@
       <c r="D922" s="12" t="s">
         <v>1955</v>
       </c>
+      <c r="E922" s="2"/>
       <c r="F922" s="8">
         <v>16030</v>
       </c>
@@ -59425,6 +59592,7 @@
       <c r="D923" s="12" t="s">
         <v>1958</v>
       </c>
+      <c r="E923" s="2"/>
       <c r="F923" s="8">
         <v>16957</v>
       </c>
@@ -59442,6 +59610,7 @@
       <c r="D924" s="12" t="s">
         <v>1960</v>
       </c>
+      <c r="E924" s="2"/>
       <c r="F924" s="8">
         <v>14347</v>
       </c>
@@ -59459,6 +59628,7 @@
       <c r="D925" s="12" t="s">
         <v>1962</v>
       </c>
+      <c r="E925" s="2"/>
       <c r="F925" s="8">
         <v>15675</v>
       </c>
@@ -59476,6 +59646,7 @@
       <c r="D926" s="12" t="s">
         <v>1964</v>
       </c>
+      <c r="E926" s="2"/>
       <c r="F926" s="8">
         <v>14207</v>
       </c>
@@ -59493,6 +59664,7 @@
       <c r="D927" s="12" t="s">
         <v>1967</v>
       </c>
+      <c r="E927" s="2"/>
       <c r="F927" s="8">
         <v>18055</v>
       </c>
@@ -59510,6 +59682,7 @@
       <c r="D928" s="12" t="s">
         <v>1969</v>
       </c>
+      <c r="E928" s="2"/>
       <c r="F928" s="8">
         <v>17394</v>
       </c>
@@ -59527,6 +59700,7 @@
       <c r="D929" s="12" t="s">
         <v>1971</v>
       </c>
+      <c r="E929" s="2"/>
       <c r="F929" s="8">
         <v>12512</v>
       </c>
@@ -59544,6 +59718,7 @@
       <c r="D930" s="12" t="s">
         <v>1973</v>
       </c>
+      <c r="E930" s="2"/>
       <c r="F930" s="8">
         <v>18267</v>
       </c>
@@ -59561,6 +59736,7 @@
       <c r="D931" s="12" t="s">
         <v>1976</v>
       </c>
+      <c r="E931" s="2"/>
       <c r="F931" s="8">
         <v>19217</v>
       </c>
@@ -59578,6 +59754,7 @@
       <c r="D932" s="12" t="s">
         <v>1978</v>
       </c>
+      <c r="E932" s="2"/>
       <c r="F932" s="8">
         <v>18330</v>
       </c>
@@ -59595,6 +59772,7 @@
       <c r="D933" s="12" t="s">
         <v>1980</v>
       </c>
+      <c r="E933" s="2"/>
       <c r="F933" s="8">
         <v>17001</v>
       </c>
@@ -59612,6 +59790,7 @@
       <c r="D934" s="12" t="s">
         <v>1982</v>
       </c>
+      <c r="E934" s="2"/>
       <c r="F934" s="8">
         <v>15661</v>
       </c>
@@ -59629,6 +59808,7 @@
       <c r="D935" s="12" t="s">
         <v>1984</v>
       </c>
+      <c r="E935" s="2"/>
       <c r="F935" s="8">
         <v>15214</v>
       </c>
@@ -59646,6 +59826,7 @@
       <c r="D936" s="12" t="s">
         <v>1986</v>
       </c>
+      <c r="E936" s="2"/>
       <c r="F936" s="8">
         <v>21230</v>
       </c>
@@ -59663,6 +59844,7 @@
       <c r="D937" s="12" t="s">
         <v>1988</v>
       </c>
+      <c r="E937" s="2"/>
       <c r="F937" s="8">
         <v>21388</v>
       </c>
@@ -59683,7 +59865,7 @@
       <c r="E938" s="8">
         <v>58160</v>
       </c>
-      <c r="F938" s="2"/>
+      <c r="F938" s="3"/>
     </row>
     <row r="939" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A939" s="8" t="s">
@@ -59701,7 +59883,7 @@
       <c r="E939" s="8">
         <v>53912</v>
       </c>
-      <c r="F939" s="2"/>
+      <c r="F939" s="3"/>
     </row>
     <row r="940" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A940" s="8" t="s">
@@ -59719,7 +59901,7 @@
       <c r="E940" s="8">
         <v>45916</v>
       </c>
-      <c r="F940" s="2"/>
+      <c r="F940" s="3"/>
     </row>
     <row r="941" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A941" s="8" t="s">
@@ -59937,7 +60119,7 @@
       <c r="E951" s="8">
         <v>74012</v>
       </c>
-      <c r="F951" s="2"/>
+      <c r="F951" s="3"/>
     </row>
     <row r="952" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A952" s="8" t="s">
@@ -59975,7 +60157,7 @@
       <c r="E953" s="8">
         <v>60263</v>
       </c>
-      <c r="F953" s="2"/>
+      <c r="F953" s="3"/>
     </row>
     <row r="954" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A954" s="8" t="s">
@@ -60393,7 +60575,7 @@
       <c r="E974" s="8">
         <v>49217</v>
       </c>
-      <c r="F974" s="2"/>
+      <c r="F974" s="3"/>
     </row>
     <row r="975" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A975" s="8" t="s">
@@ -60411,7 +60593,7 @@
       <c r="E975" s="8">
         <v>60100</v>
       </c>
-      <c r="F975" s="2"/>
+      <c r="F975" s="3"/>
     </row>
     <row r="976" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A976" s="8" t="s">
@@ -61349,7 +61531,7 @@
       <c r="E1022" s="8">
         <v>48313</v>
       </c>
-      <c r="F1022" s="2"/>
+      <c r="F1022" s="3"/>
     </row>
     <row r="1023" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1023" s="8" t="s">
@@ -61367,7 +61549,7 @@
       <c r="E1023" s="8">
         <v>47711</v>
       </c>
-      <c r="F1023" s="2"/>
+      <c r="F1023" s="3"/>
     </row>
     <row r="1024" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1024" s="8" t="s">
@@ -61385,7 +61567,7 @@
       <c r="E1024" s="8">
         <v>46979</v>
       </c>
-      <c r="F1024" s="2"/>
+      <c r="F1024" s="3"/>
     </row>
     <row r="1025" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1025" s="8" t="s">
@@ -61523,7 +61705,7 @@
       <c r="E1031" s="8">
         <v>44334</v>
       </c>
-      <c r="F1031" s="2"/>
+      <c r="F1031" s="3"/>
     </row>
     <row r="1032" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1032" s="8" t="s">
@@ -61701,7 +61883,7 @@
       <c r="E1040" s="8">
         <v>43845</v>
       </c>
-      <c r="F1040" s="2"/>
+      <c r="F1040" s="3"/>
     </row>
     <row r="1041" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1041" s="8" t="s">
@@ -63319,7 +63501,7 @@
       <c r="E1121" s="8">
         <v>62716</v>
       </c>
-      <c r="F1121" s="2"/>
+      <c r="F1121" s="3"/>
     </row>
     <row r="1122" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1122" s="8" t="s">
@@ -63337,7 +63519,7 @@
       <c r="E1122" s="8">
         <v>61192</v>
       </c>
-      <c r="F1122" s="2"/>
+      <c r="F1122" s="3"/>
     </row>
     <row r="1123" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1123" s="8" t="s">
@@ -63355,7 +63537,7 @@
       <c r="E1123" s="8">
         <v>55197</v>
       </c>
-      <c r="F1123" s="2"/>
+      <c r="F1123" s="3"/>
     </row>
     <row r="1124" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1124" s="8" t="s">
@@ -63553,7 +63735,7 @@
       <c r="E1133" s="8">
         <v>64634</v>
       </c>
-      <c r="F1133" s="2"/>
+      <c r="F1133" s="3"/>
     </row>
     <row r="1134" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1134" s="8" t="s">
@@ -63571,7 +63753,7 @@
       <c r="E1134" s="8">
         <v>59512</v>
       </c>
-      <c r="F1134" s="2"/>
+      <c r="F1134" s="3"/>
     </row>
     <row r="1135" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1135" s="8" t="s">
@@ -63629,7 +63811,7 @@
       <c r="E1137" s="8">
         <v>59344</v>
       </c>
-      <c r="F1137" s="2"/>
+      <c r="F1137" s="3"/>
     </row>
     <row r="1138" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1138" s="8" t="s">
@@ -64127,7 +64309,7 @@
       <c r="E1162" s="8">
         <v>52663</v>
       </c>
-      <c r="F1162" s="2"/>
+      <c r="F1162" s="3"/>
     </row>
     <row r="1163" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1163" s="8" t="s">
@@ -64405,7 +64587,7 @@
       <c r="E1176" s="8">
         <v>48099</v>
       </c>
-      <c r="F1176" s="2"/>
+      <c r="F1176" s="3"/>
     </row>
     <row r="1177" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1177" s="8" t="s">
@@ -66340,7 +66522,8 @@
       <c r="D1273" s="12" t="s">
         <v>2698</v>
       </c>
-      <c r="F1273" s="2"/>
+      <c r="E1273" s="2"/>
+      <c r="F1273" s="3"/>
     </row>
     <row r="1274" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1274" s="8" t="s">
@@ -66355,6 +66538,7 @@
       <c r="D1274" s="12" t="s">
         <v>2700</v>
       </c>
+      <c r="E1274" s="2"/>
       <c r="F1274" s="8">
         <v>15274</v>
       </c>
@@ -67255,7 +67439,7 @@
       <c r="E1319" s="8">
         <v>36639</v>
       </c>
-      <c r="F1319" s="2"/>
+      <c r="F1319" s="3"/>
     </row>
     <row r="1320" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1320" s="8" t="s">
@@ -67473,7 +67657,7 @@
       <c r="E1330" s="8">
         <v>37267</v>
       </c>
-      <c r="F1330" s="2"/>
+      <c r="F1330" s="3"/>
     </row>
     <row r="1331" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1331" s="8" t="s">
@@ -67531,7 +67715,7 @@
       <c r="E1333" s="8">
         <v>37181</v>
       </c>
-      <c r="F1333" s="2"/>
+      <c r="F1333" s="3"/>
     </row>
     <row r="1334" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1334" s="8" t="s">
@@ -67789,7 +67973,7 @@
       <c r="E1346" s="8">
         <v>37065</v>
       </c>
-      <c r="F1346" s="2"/>
+      <c r="F1346" s="3"/>
     </row>
     <row r="1347" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1347" s="8" t="s">
@@ -67804,6 +67988,7 @@
       <c r="D1347" s="12" t="s">
         <v>2853</v>
       </c>
+      <c r="E1347" s="2"/>
       <c r="F1347" s="8">
         <v>19773</v>
       </c>
@@ -68004,7 +68189,7 @@
       <c r="E1357" s="8">
         <v>34124</v>
       </c>
-      <c r="F1357" s="2"/>
+      <c r="F1357" s="3"/>
     </row>
     <row r="1358" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1358" s="8" t="s">
@@ -68019,6 +68204,7 @@
       <c r="D1358" s="12" t="s">
         <v>2877</v>
       </c>
+      <c r="E1358" s="2"/>
       <c r="F1358" s="8">
         <v>15191</v>
       </c>
@@ -69176,7 +69362,8 @@
       <c r="D1416" s="12" t="s">
         <v>3001</v>
       </c>
-      <c r="F1416" s="2"/>
+      <c r="E1416" s="2"/>
+      <c r="F1416" s="3"/>
     </row>
     <row r="1417" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1417" s="8" t="s">
@@ -69191,7 +69378,8 @@
       <c r="D1417" s="12" t="s">
         <v>3003</v>
       </c>
-      <c r="F1417" s="2"/>
+      <c r="E1417" s="2"/>
+      <c r="F1417" s="3"/>
     </row>
     <row r="1418" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1418" s="8" t="s">
@@ -69206,7 +69394,8 @@
       <c r="D1418" s="12" t="s">
         <v>3005</v>
       </c>
-      <c r="F1418" s="2"/>
+      <c r="E1418" s="2"/>
+      <c r="F1418" s="3"/>
     </row>
     <row r="1419" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1419" s="8" t="s">
@@ -69221,7 +69410,8 @@
       <c r="D1419" s="12" t="s">
         <v>3007</v>
       </c>
-      <c r="F1419" s="2"/>
+      <c r="E1419" s="2"/>
+      <c r="F1419" s="3"/>
     </row>
     <row r="1420" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1420" s="8" t="s">
@@ -69236,7 +69426,8 @@
       <c r="D1420" s="12" t="s">
         <v>3009</v>
       </c>
-      <c r="F1420" s="2"/>
+      <c r="E1420" s="2"/>
+      <c r="F1420" s="3"/>
     </row>
     <row r="1421" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1421" s="8" t="s">
@@ -69251,7 +69442,8 @@
       <c r="D1421" s="12" t="s">
         <v>3010</v>
       </c>
-      <c r="F1421" s="2"/>
+      <c r="E1421" s="2"/>
+      <c r="F1421" s="3"/>
     </row>
     <row r="1422" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1422" s="8" t="s">
@@ -69266,7 +69458,8 @@
       <c r="D1422" s="12" t="s">
         <v>3012</v>
       </c>
-      <c r="F1422" s="2"/>
+      <c r="E1422" s="2"/>
+      <c r="F1422" s="3"/>
     </row>
     <row r="1423" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1423" s="8" t="s">
@@ -69281,7 +69474,8 @@
       <c r="D1423" s="12" t="s">
         <v>3014</v>
       </c>
-      <c r="F1423" s="2"/>
+      <c r="E1423" s="2"/>
+      <c r="F1423" s="3"/>
     </row>
     <row r="1424" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1424" s="8" t="s">
@@ -69296,7 +69490,8 @@
       <c r="D1424" s="12" t="s">
         <v>3016</v>
       </c>
-      <c r="F1424" s="2"/>
+      <c r="E1424" s="2"/>
+      <c r="F1424" s="3"/>
     </row>
     <row r="1425" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1425" s="8" t="s">
@@ -69391,7 +69586,8 @@
       <c r="D1429" s="12" t="s">
         <v>3027</v>
       </c>
-      <c r="F1429" s="2"/>
+      <c r="E1429" s="2"/>
+      <c r="F1429" s="3"/>
     </row>
     <row r="1430" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1430" s="8" t="s">
@@ -69406,7 +69602,8 @@
       <c r="D1430" s="12" t="s">
         <v>3029</v>
       </c>
-      <c r="F1430" s="2"/>
+      <c r="E1430" s="2"/>
+      <c r="F1430" s="3"/>
     </row>
     <row r="1431" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1431" s="8" t="s">
@@ -69421,7 +69618,8 @@
       <c r="D1431" s="12" t="s">
         <v>3031</v>
       </c>
-      <c r="F1431" s="2"/>
+      <c r="E1431" s="2"/>
+      <c r="F1431" s="3"/>
     </row>
     <row r="1432" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1432" s="8" t="s">
@@ -69436,7 +69634,8 @@
       <c r="D1432" s="12" t="s">
         <v>3033</v>
       </c>
-      <c r="F1432" s="2"/>
+      <c r="E1432" s="2"/>
+      <c r="F1432" s="3"/>
     </row>
     <row r="1433" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1433" s="8" t="s">
@@ -69491,7 +69690,8 @@
       <c r="D1435" s="12" t="s">
         <v>3040</v>
       </c>
-      <c r="F1435" s="2"/>
+      <c r="E1435" s="2"/>
+      <c r="F1435" s="3"/>
     </row>
     <row r="1436" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1436" s="8" t="s">
@@ -69506,7 +69706,8 @@
       <c r="D1436" s="12" t="s">
         <v>3042</v>
       </c>
-      <c r="F1436" s="2"/>
+      <c r="E1436" s="2"/>
+      <c r="F1436" s="3"/>
     </row>
     <row r="1437" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1437" s="8" t="s">
@@ -69641,7 +69842,8 @@
       <c r="D1443" s="12" t="s">
         <v>3057</v>
       </c>
-      <c r="F1443" s="2"/>
+      <c r="E1443" s="2"/>
+      <c r="F1443" s="3"/>
     </row>
     <row r="1444" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1444" s="8" t="s">
@@ -69656,7 +69858,8 @@
       <c r="D1444" s="12" t="s">
         <v>3059</v>
       </c>
-      <c r="F1444" s="2"/>
+      <c r="E1444" s="2"/>
+      <c r="F1444" s="3"/>
     </row>
     <row r="1445" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1445" s="8" t="s">
@@ -69671,7 +69874,8 @@
       <c r="D1445" s="12" t="s">
         <v>3061</v>
       </c>
-      <c r="F1445" s="2"/>
+      <c r="E1445" s="2"/>
+      <c r="F1445" s="3"/>
     </row>
     <row r="1446" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1446" s="8" t="s">
@@ -69686,7 +69890,8 @@
       <c r="D1446" s="12" t="s">
         <v>3063</v>
       </c>
-      <c r="F1446" s="2"/>
+      <c r="E1446" s="2"/>
+      <c r="F1446" s="3"/>
     </row>
     <row r="1447" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1447" s="8" t="s">
@@ -69881,7 +70086,8 @@
       <c r="D1456" s="12" t="s">
         <v>3084</v>
       </c>
-      <c r="F1456" s="2"/>
+      <c r="E1456" s="2"/>
+      <c r="F1456" s="3"/>
     </row>
     <row r="1457" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1457" s="8" t="s">
@@ -69896,7 +70102,8 @@
       <c r="D1457" s="12" t="s">
         <v>3086</v>
       </c>
-      <c r="F1457" s="2"/>
+      <c r="E1457" s="2"/>
+      <c r="F1457" s="3"/>
     </row>
     <row r="1458" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1458" s="8" t="s">
@@ -70131,7 +70338,8 @@
       <c r="D1469" s="12" t="s">
         <v>3112</v>
       </c>
-      <c r="F1469" s="2"/>
+      <c r="E1469" s="2"/>
+      <c r="F1469" s="3"/>
     </row>
     <row r="1470" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1470" s="8" t="s">
@@ -70346,7 +70554,8 @@
       <c r="D1480" s="12" t="s">
         <v>3136</v>
       </c>
-      <c r="F1480" s="2"/>
+      <c r="E1480" s="2"/>
+      <c r="F1480" s="3"/>
     </row>
     <row r="1481" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1481" s="8" t="s">
@@ -71061,10 +71270,10 @@
       <c r="D1516" s="12" t="s">
         <v>3213</v>
       </c>
-      <c r="E1516" s="1">
+      <c r="E1516" s="2">
         <v>32202.94</v>
       </c>
-      <c r="F1516" s="1">
+      <c r="F1516" s="2">
         <v>11416.8</v>
       </c>
     </row>
@@ -71081,10 +71290,10 @@
       <c r="D1517" s="12" t="s">
         <v>3215</v>
       </c>
-      <c r="E1517" s="1">
+      <c r="E1517" s="2">
         <v>33622.82</v>
       </c>
-      <c r="F1517" s="1">
+      <c r="F1517" s="2">
         <v>18948.17</v>
       </c>
     </row>
@@ -71101,10 +71310,10 @@
       <c r="D1518" s="12" t="s">
         <v>3217</v>
       </c>
-      <c r="E1518" s="1">
+      <c r="E1518" s="2">
         <v>35749.9</v>
       </c>
-      <c r="F1518" s="1">
+      <c r="F1518" s="2">
         <v>20646.9</v>
       </c>
     </row>
@@ -71124,7 +71333,7 @@
       <c r="E1519" s="8">
         <v>61985</v>
       </c>
-      <c r="F1519" s="2"/>
+      <c r="F1519" s="3"/>
     </row>
     <row r="1520" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1520" s="8" t="s">
@@ -71142,7 +71351,7 @@
       <c r="E1520" s="8">
         <v>62293</v>
       </c>
-      <c r="F1520" s="2"/>
+      <c r="F1520" s="3"/>
     </row>
     <row r="1521" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1521" s="8" t="s">
@@ -71160,7 +71369,7 @@
       <c r="E1521" s="8">
         <v>61835</v>
       </c>
-      <c r="F1521" s="2"/>
+      <c r="F1521" s="3"/>
     </row>
     <row r="1522" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1522" s="8" t="s">
@@ -71178,7 +71387,7 @@
       <c r="E1522" s="8">
         <v>61075</v>
       </c>
-      <c r="F1522" s="2"/>
+      <c r="F1522" s="3"/>
     </row>
     <row r="1523" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1523" s="8" t="s">
@@ -71196,7 +71405,7 @@
       <c r="E1523" s="8">
         <v>62403</v>
       </c>
-      <c r="F1523" s="2"/>
+      <c r="F1523" s="3"/>
     </row>
     <row r="1524" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1524" s="8" t="s">
@@ -71294,7 +71503,7 @@
       <c r="E1528" s="8">
         <v>51491</v>
       </c>
-      <c r="F1528" s="2"/>
+      <c r="F1528" s="3"/>
     </row>
     <row r="1529" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1529" s="8" t="s">
@@ -71312,7 +71521,7 @@
       <c r="E1529" s="8">
         <v>54138</v>
       </c>
-      <c r="F1529" s="2"/>
+      <c r="F1529" s="3"/>
     </row>
     <row r="1530" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1530" s="8" t="s">
@@ -71330,7 +71539,7 @@
       <c r="E1530" s="8">
         <v>52069</v>
       </c>
-      <c r="F1530" s="2"/>
+      <c r="F1530" s="3"/>
     </row>
     <row r="1531" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1531" s="8" t="s">
@@ -71348,7 +71557,7 @@
       <c r="E1531" s="8">
         <v>59331</v>
       </c>
-      <c r="F1531" s="2"/>
+      <c r="F1531" s="3"/>
     </row>
     <row r="1532" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1532" s="8" t="s">
@@ -71566,7 +71775,7 @@
       <c r="E1542" s="8">
         <v>41042</v>
       </c>
-      <c r="F1542" s="2"/>
+      <c r="F1542" s="3"/>
     </row>
     <row r="1543" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1543" s="8" t="s">
@@ -71584,7 +71793,7 @@
       <c r="E1543" s="8">
         <v>40015</v>
       </c>
-      <c r="F1543" s="2"/>
+      <c r="F1543" s="3"/>
     </row>
     <row r="1544" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1544" s="8" t="s">
@@ -71602,7 +71811,7 @@
       <c r="E1544" s="8">
         <v>42312</v>
       </c>
-      <c r="F1544" s="2"/>
+      <c r="F1544" s="3"/>
     </row>
     <row r="1545" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1545" s="8" t="s">
@@ -71620,7 +71829,7 @@
       <c r="E1545" s="8">
         <v>41151</v>
       </c>
-      <c r="F1545" s="2"/>
+      <c r="F1545" s="3"/>
     </row>
     <row r="1546" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1546" s="8" t="s">
@@ -71638,7 +71847,7 @@
       <c r="E1546" s="8">
         <v>45574</v>
       </c>
-      <c r="F1546" s="2"/>
+      <c r="F1546" s="3"/>
     </row>
     <row r="1547" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1547" s="8" t="s">
@@ -72036,7 +72245,7 @@
       <c r="E1566" s="8">
         <v>40542</v>
       </c>
-      <c r="F1566" s="2"/>
+      <c r="F1566" s="3"/>
     </row>
     <row r="1567" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1567" s="8" t="s">
@@ -72054,7 +72263,7 @@
       <c r="E1567" s="8">
         <v>42506</v>
       </c>
-      <c r="F1567" s="2"/>
+      <c r="F1567" s="3"/>
     </row>
     <row r="1568" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1568" s="8" t="s">
@@ -73852,7 +74061,7 @@
       <c r="E1657" s="8">
         <v>55140</v>
       </c>
-      <c r="F1657" s="2"/>
+      <c r="F1657" s="3"/>
     </row>
     <row r="1658" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1658" s="8" t="s">
@@ -73890,7 +74099,7 @@
       <c r="E1659" s="8">
         <v>61485</v>
       </c>
-      <c r="F1659" s="2"/>
+      <c r="F1659" s="3"/>
     </row>
     <row r="1660" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1660" s="8" t="s">
@@ -77125,7 +77334,8 @@
       <c r="D1821" s="12" t="s">
         <v>3873</v>
       </c>
-      <c r="F1821" s="2"/>
+      <c r="E1821" s="2"/>
+      <c r="F1821" s="3"/>
     </row>
     <row r="1822" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1822" s="8" t="s">
@@ -77140,7 +77350,8 @@
       <c r="D1822" s="12" t="s">
         <v>3875</v>
       </c>
-      <c r="F1822" s="2"/>
+      <c r="E1822" s="2"/>
+      <c r="F1822" s="3"/>
     </row>
     <row r="1823" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1823" s="8" t="s">
@@ -77478,7 +77689,7 @@
       <c r="E1839" s="8">
         <v>46994</v>
       </c>
-      <c r="F1839" s="2"/>
+      <c r="F1839" s="3"/>
     </row>
     <row r="1840" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1840" s="8" t="s">
@@ -78193,7 +78404,8 @@
       <c r="D1875" s="12" t="s">
         <v>3983</v>
       </c>
-      <c r="F1875" s="2"/>
+      <c r="E1875" s="2"/>
+      <c r="F1875" s="3"/>
     </row>
     <row r="1876" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1876" s="8" t="s">
@@ -78208,7 +78420,8 @@
       <c r="D1876" s="12" t="s">
         <v>3985</v>
       </c>
-      <c r="F1876" s="2"/>
+      <c r="E1876" s="2"/>
+      <c r="F1876" s="3"/>
     </row>
     <row r="1877" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1877" s="8" t="s">
@@ -78223,7 +78436,8 @@
       <c r="D1877" s="12" t="s">
         <v>3987</v>
       </c>
-      <c r="F1877" s="2"/>
+      <c r="E1877" s="2"/>
+      <c r="F1877" s="3"/>
     </row>
     <row r="1878" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1878" s="8" t="s">
@@ -78238,7 +78452,8 @@
       <c r="D1878" s="12" t="s">
         <v>3989</v>
       </c>
-      <c r="F1878" s="2"/>
+      <c r="E1878" s="2"/>
+      <c r="F1878" s="3"/>
     </row>
     <row r="1879" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1879" s="8" t="s">
@@ -78253,7 +78468,8 @@
       <c r="D1879" s="12" t="s">
         <v>3991</v>
       </c>
-      <c r="F1879" s="2"/>
+      <c r="E1879" s="2"/>
+      <c r="F1879" s="3"/>
     </row>
     <row r="1880" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1880" s="8" t="s">
@@ -78268,7 +78484,8 @@
       <c r="D1880" s="12" t="s">
         <v>3993</v>
       </c>
-      <c r="F1880" s="2"/>
+      <c r="E1880" s="2"/>
+      <c r="F1880" s="3"/>
     </row>
     <row r="1881" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1881" s="8" t="s">
@@ -78283,7 +78500,8 @@
       <c r="D1881" s="12" t="s">
         <v>3995</v>
       </c>
-      <c r="F1881" s="2"/>
+      <c r="E1881" s="2"/>
+      <c r="F1881" s="3"/>
     </row>
     <row r="1882" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1882" s="8" t="s">
@@ -78298,7 +78516,8 @@
       <c r="D1882" s="12" t="s">
         <v>3997</v>
       </c>
-      <c r="F1882" s="2"/>
+      <c r="E1882" s="2"/>
+      <c r="F1882" s="3"/>
     </row>
     <row r="1883" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1883" s="8" t="s">
@@ -78313,7 +78532,8 @@
       <c r="D1883" s="12" t="s">
         <v>3999</v>
       </c>
-      <c r="F1883" s="2"/>
+      <c r="E1883" s="2"/>
+      <c r="F1883" s="3"/>
     </row>
     <row r="1884" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1884" s="8" t="s">
@@ -78328,7 +78548,8 @@
       <c r="D1884" s="12" t="s">
         <v>4001</v>
       </c>
-      <c r="F1884" s="2"/>
+      <c r="E1884" s="2"/>
+      <c r="F1884" s="3"/>
     </row>
     <row r="1885" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1885" s="8" t="s">
@@ -78343,7 +78564,8 @@
       <c r="D1885" s="12" t="s">
         <v>4003</v>
       </c>
-      <c r="F1885" s="2"/>
+      <c r="E1885" s="2"/>
+      <c r="F1885" s="3"/>
     </row>
     <row r="1886" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1886" s="8" t="s">
@@ -78358,7 +78580,8 @@
       <c r="D1886" s="12" t="s">
         <v>4005</v>
       </c>
-      <c r="F1886" s="2"/>
+      <c r="E1886" s="2"/>
+      <c r="F1886" s="3"/>
     </row>
     <row r="1887" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1887" s="8" t="s">
@@ -78373,7 +78596,8 @@
       <c r="D1887" s="12" t="s">
         <v>4007</v>
       </c>
-      <c r="F1887" s="2"/>
+      <c r="E1887" s="2"/>
+      <c r="F1887" s="3"/>
     </row>
     <row r="1888" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1888" s="8" t="s">
@@ -78388,7 +78612,8 @@
       <c r="D1888" s="12" t="s">
         <v>4009</v>
       </c>
-      <c r="F1888" s="2"/>
+      <c r="E1888" s="2"/>
+      <c r="F1888" s="3"/>
     </row>
     <row r="1889" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1889" s="8" t="s">
@@ -78403,7 +78628,8 @@
       <c r="D1889" s="12" t="s">
         <v>4011</v>
       </c>
-      <c r="F1889" s="2"/>
+      <c r="E1889" s="2"/>
+      <c r="F1889" s="3"/>
     </row>
     <row r="1890" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1890" s="8" t="s">
@@ -78418,7 +78644,8 @@
       <c r="D1890" s="12" t="s">
         <v>4013</v>
       </c>
-      <c r="F1890" s="2"/>
+      <c r="E1890" s="2"/>
+      <c r="F1890" s="3"/>
     </row>
     <row r="1891" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1891" s="8" t="s">
@@ -78433,7 +78660,8 @@
       <c r="D1891" s="12" t="s">
         <v>4015</v>
       </c>
-      <c r="F1891" s="2"/>
+      <c r="E1891" s="2"/>
+      <c r="F1891" s="3"/>
     </row>
     <row r="1892" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1892" s="8" t="s">
@@ -78448,7 +78676,8 @@
       <c r="D1892" s="12" t="s">
         <v>4017</v>
       </c>
-      <c r="F1892" s="2"/>
+      <c r="E1892" s="2"/>
+      <c r="F1892" s="3"/>
     </row>
     <row r="1893" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1893" s="8" t="s">
@@ -78463,7 +78692,8 @@
       <c r="D1893" s="12" t="s">
         <v>4019</v>
       </c>
-      <c r="F1893" s="2"/>
+      <c r="E1893" s="2"/>
+      <c r="F1893" s="3"/>
     </row>
     <row r="1894" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1894" s="8" t="s">
@@ -78478,7 +78708,8 @@
       <c r="D1894" s="12" t="s">
         <v>4021</v>
       </c>
-      <c r="F1894" s="2"/>
+      <c r="E1894" s="2"/>
+      <c r="F1894" s="3"/>
     </row>
     <row r="1895" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1895" s="8" t="s">
@@ -78493,7 +78724,8 @@
       <c r="D1895" s="12" t="s">
         <v>4024</v>
       </c>
-      <c r="F1895" s="2"/>
+      <c r="E1895" s="2"/>
+      <c r="F1895" s="3"/>
     </row>
     <row r="1896" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1896" s="8" t="s">
@@ -78508,7 +78740,8 @@
       <c r="D1896" s="12" t="s">
         <v>4026</v>
       </c>
-      <c r="F1896" s="2"/>
+      <c r="E1896" s="2"/>
+      <c r="F1896" s="3"/>
     </row>
     <row r="1897" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1897" s="8" t="s">
@@ -78523,7 +78756,8 @@
       <c r="D1897" s="12" t="s">
         <v>4028</v>
       </c>
-      <c r="F1897" s="2"/>
+      <c r="E1897" s="2"/>
+      <c r="F1897" s="3"/>
     </row>
     <row r="1898" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1898" s="8" t="s">
@@ -78538,7 +78772,8 @@
       <c r="D1898" s="12" t="s">
         <v>4030</v>
       </c>
-      <c r="F1898" s="2"/>
+      <c r="E1898" s="2"/>
+      <c r="F1898" s="3"/>
     </row>
     <row r="1899" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1899" s="8" t="s">
@@ -78553,7 +78788,8 @@
       <c r="D1899" s="12" t="s">
         <v>4032</v>
       </c>
-      <c r="F1899" s="2"/>
+      <c r="E1899" s="2"/>
+      <c r="F1899" s="3"/>
     </row>
     <row r="1900" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1900" s="8" t="s">
@@ -78568,7 +78804,8 @@
       <c r="D1900" s="12" t="s">
         <v>4034</v>
       </c>
-      <c r="F1900" s="2"/>
+      <c r="E1900" s="2"/>
+      <c r="F1900" s="3"/>
     </row>
     <row r="1901" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1901" s="8" t="s">
@@ -78583,7 +78820,8 @@
       <c r="D1901" s="12" t="s">
         <v>4037</v>
       </c>
-      <c r="F1901" s="2"/>
+      <c r="E1901" s="2"/>
+      <c r="F1901" s="3"/>
     </row>
     <row r="1902" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1902" s="8" t="s">
@@ -78598,7 +78836,8 @@
       <c r="D1902" s="12" t="s">
         <v>4039</v>
       </c>
-      <c r="F1902" s="2"/>
+      <c r="E1902" s="2"/>
+      <c r="F1902" s="3"/>
     </row>
     <row r="1903" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1903" s="8" t="s">
@@ -78613,7 +78852,8 @@
       <c r="D1903" s="12" t="s">
         <v>4041</v>
       </c>
-      <c r="F1903" s="2"/>
+      <c r="E1903" s="2"/>
+      <c r="F1903" s="3"/>
     </row>
     <row r="1904" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1904" s="8" t="s">
@@ -78628,7 +78868,8 @@
       <c r="D1904" s="12" t="s">
         <v>4043</v>
       </c>
-      <c r="F1904" s="2"/>
+      <c r="E1904" s="2"/>
+      <c r="F1904" s="3"/>
     </row>
     <row r="1905" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1905" s="8" t="s">
@@ -78643,7 +78884,8 @@
       <c r="D1905" s="12" t="s">
         <v>4045</v>
       </c>
-      <c r="F1905" s="2"/>
+      <c r="E1905" s="2"/>
+      <c r="F1905" s="3"/>
     </row>
     <row r="1906" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1906" s="8" t="s">
@@ -78658,7 +78900,8 @@
       <c r="D1906" s="12" t="s">
         <v>4048</v>
       </c>
-      <c r="F1906" s="2"/>
+      <c r="E1906" s="2"/>
+      <c r="F1906" s="3"/>
     </row>
     <row r="1907" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1907" s="8" t="s">
@@ -78673,7 +78916,8 @@
       <c r="D1907" s="12" t="s">
         <v>4050</v>
       </c>
-      <c r="F1907" s="2"/>
+      <c r="E1907" s="2"/>
+      <c r="F1907" s="3"/>
     </row>
     <row r="1908" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1908" s="8" t="s">
@@ -78688,7 +78932,8 @@
       <c r="D1908" s="12" t="s">
         <v>4052</v>
       </c>
-      <c r="F1908" s="2"/>
+      <c r="E1908" s="2"/>
+      <c r="F1908" s="3"/>
     </row>
     <row r="1909" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1909" s="8" t="s">
@@ -78703,7 +78948,8 @@
       <c r="D1909" s="12" t="s">
         <v>4054</v>
       </c>
-      <c r="F1909" s="2"/>
+      <c r="E1909" s="2"/>
+      <c r="F1909" s="3"/>
     </row>
     <row r="1910" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1910" s="8" t="s">
@@ -78718,7 +78964,8 @@
       <c r="D1910" s="12" t="s">
         <v>4056</v>
       </c>
-      <c r="F1910" s="2"/>
+      <c r="E1910" s="2"/>
+      <c r="F1910" s="3"/>
     </row>
     <row r="1911" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1911" s="8" t="s">
@@ -78733,7 +78980,8 @@
       <c r="D1911" s="12" t="s">
         <v>4058</v>
       </c>
-      <c r="F1911" s="2"/>
+      <c r="E1911" s="2"/>
+      <c r="F1911" s="3"/>
     </row>
     <row r="1912" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1912" s="8" t="s">
@@ -78748,7 +78996,8 @@
       <c r="D1912" s="12" t="s">
         <v>4060</v>
       </c>
-      <c r="F1912" s="2"/>
+      <c r="E1912" s="2"/>
+      <c r="F1912" s="3"/>
     </row>
     <row r="1913" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1913" s="8" t="s">
@@ -78763,7 +79012,8 @@
       <c r="D1913" s="12" t="s">
         <v>4063</v>
       </c>
-      <c r="F1913" s="2"/>
+      <c r="E1913" s="2"/>
+      <c r="F1913" s="3"/>
     </row>
     <row r="1914" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1914" s="8" t="s">
@@ -78778,7 +79028,8 @@
       <c r="D1914" s="12" t="s">
         <v>4065</v>
       </c>
-      <c r="F1914" s="2"/>
+      <c r="E1914" s="2"/>
+      <c r="F1914" s="3"/>
     </row>
     <row r="1915" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1915" s="8" t="s">
@@ -78793,7 +79044,8 @@
       <c r="D1915" s="12" t="s">
         <v>4067</v>
       </c>
-      <c r="F1915" s="2"/>
+      <c r="E1915" s="2"/>
+      <c r="F1915" s="3"/>
     </row>
     <row r="1916" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1916" s="8" t="s">
@@ -78808,7 +79060,8 @@
       <c r="D1916" s="12" t="s">
         <v>4069</v>
       </c>
-      <c r="F1916" s="2"/>
+      <c r="E1916" s="2"/>
+      <c r="F1916" s="3"/>
     </row>
     <row r="1917" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1917" s="8" t="s">
@@ -78823,7 +79076,8 @@
       <c r="D1917" s="12" t="s">
         <v>4071</v>
       </c>
-      <c r="F1917" s="2"/>
+      <c r="E1917" s="2"/>
+      <c r="F1917" s="3"/>
     </row>
     <row r="1918" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1918" s="8" t="s">
@@ -78838,7 +79092,8 @@
       <c r="D1918" s="12" t="s">
         <v>4073</v>
       </c>
-      <c r="F1918" s="2"/>
+      <c r="E1918" s="2"/>
+      <c r="F1918" s="3"/>
     </row>
     <row r="1919" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1919" s="8" t="s">
@@ -78853,7 +79108,8 @@
       <c r="D1919" s="12" t="s">
         <v>4076</v>
       </c>
-      <c r="F1919" s="2"/>
+      <c r="E1919" s="2"/>
+      <c r="F1919" s="3"/>
     </row>
     <row r="1920" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1920" s="8" t="s">
@@ -78868,7 +79124,8 @@
       <c r="D1920" s="12" t="s">
         <v>4078</v>
       </c>
-      <c r="F1920" s="2"/>
+      <c r="E1920" s="2"/>
+      <c r="F1920" s="3"/>
     </row>
     <row r="1921" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1921" s="8" t="s">
@@ -78883,7 +79140,8 @@
       <c r="D1921" s="12" t="s">
         <v>4080</v>
       </c>
-      <c r="F1921" s="2"/>
+      <c r="E1921" s="2"/>
+      <c r="F1921" s="3"/>
     </row>
     <row r="1922" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1922" s="8" t="s">
@@ -78898,7 +79156,8 @@
       <c r="D1922" s="12" t="s">
         <v>4082</v>
       </c>
-      <c r="F1922" s="2"/>
+      <c r="E1922" s="2"/>
+      <c r="F1922" s="3"/>
     </row>
     <row r="1923" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1923" s="8" t="s">
@@ -78913,7 +79172,8 @@
       <c r="D1923" s="12" t="s">
         <v>4084</v>
       </c>
-      <c r="F1923" s="2"/>
+      <c r="E1923" s="2"/>
+      <c r="F1923" s="3"/>
     </row>
     <row r="1924" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1924" s="8" t="s">
@@ -78928,7 +79188,8 @@
       <c r="D1924" s="12" t="s">
         <v>4086</v>
       </c>
-      <c r="F1924" s="2"/>
+      <c r="E1924" s="2"/>
+      <c r="F1924" s="3"/>
     </row>
     <row r="1925" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1925" s="8" t="s">
@@ -78943,7 +79204,8 @@
       <c r="D1925" s="12" t="s">
         <v>4088</v>
       </c>
-      <c r="F1925" s="2"/>
+      <c r="E1925" s="2"/>
+      <c r="F1925" s="3"/>
     </row>
     <row r="1926" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1926" s="8" t="s">
@@ -78958,7 +79220,8 @@
       <c r="D1926" s="12" t="s">
         <v>4090</v>
       </c>
-      <c r="F1926" s="2"/>
+      <c r="E1926" s="2"/>
+      <c r="F1926" s="3"/>
     </row>
     <row r="1927" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1927" s="8" t="s">
@@ -78973,7 +79236,8 @@
       <c r="D1927" s="12" t="s">
         <v>4092</v>
       </c>
-      <c r="F1927" s="2"/>
+      <c r="E1927" s="2"/>
+      <c r="F1927" s="3"/>
     </row>
     <row r="1928" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1928" s="8" t="s">
@@ -78988,7 +79252,8 @@
       <c r="D1928" s="12" t="s">
         <v>4095</v>
       </c>
-      <c r="F1928" s="2"/>
+      <c r="E1928" s="2"/>
+      <c r="F1928" s="3"/>
     </row>
     <row r="1929" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1929" s="8" t="s">
@@ -79003,7 +79268,8 @@
       <c r="D1929" s="12" t="s">
         <v>4097</v>
       </c>
-      <c r="F1929" s="2"/>
+      <c r="E1929" s="2"/>
+      <c r="F1929" s="3"/>
     </row>
     <row r="1930" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1930" s="8" t="s">
@@ -79018,7 +79284,8 @@
       <c r="D1930" s="12" t="s">
         <v>4099</v>
       </c>
-      <c r="F1930" s="2"/>
+      <c r="E1930" s="2"/>
+      <c r="F1930" s="3"/>
     </row>
     <row r="1931" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1931" s="8" t="s">
@@ -79033,7 +79300,8 @@
       <c r="D1931" s="12" t="s">
         <v>4101</v>
       </c>
-      <c r="F1931" s="2"/>
+      <c r="E1931" s="2"/>
+      <c r="F1931" s="3"/>
     </row>
     <row r="1932" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1932" s="8" t="s">
@@ -79048,7 +79316,8 @@
       <c r="D1932" s="12" t="s">
         <v>4103</v>
       </c>
-      <c r="F1932" s="2"/>
+      <c r="E1932" s="2"/>
+      <c r="F1932" s="3"/>
     </row>
     <row r="1933" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1933" s="8" t="s">
@@ -79063,7 +79332,8 @@
       <c r="D1933" s="12" t="s">
         <v>4105</v>
       </c>
-      <c r="F1933" s="2"/>
+      <c r="E1933" s="2"/>
+      <c r="F1933" s="3"/>
     </row>
     <row r="1934" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1934" s="8" t="s">
@@ -79078,7 +79348,8 @@
       <c r="D1934" s="12" t="s">
         <v>4107</v>
       </c>
-      <c r="F1934" s="2"/>
+      <c r="E1934" s="2"/>
+      <c r="F1934" s="3"/>
     </row>
     <row r="1935" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1935" s="8" t="s">
@@ -79093,7 +79364,8 @@
       <c r="D1935" s="12" t="s">
         <v>4110</v>
       </c>
-      <c r="F1935" s="2"/>
+      <c r="E1935" s="2"/>
+      <c r="F1935" s="3"/>
     </row>
     <row r="1936" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1936" s="8" t="s">
@@ -79108,7 +79380,8 @@
       <c r="D1936" s="12" t="s">
         <v>4112</v>
       </c>
-      <c r="F1936" s="2"/>
+      <c r="E1936" s="2"/>
+      <c r="F1936" s="3"/>
     </row>
     <row r="1937" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1937" s="8" t="s">
@@ -79123,7 +79396,8 @@
       <c r="D1937" s="12" t="s">
         <v>4114</v>
       </c>
-      <c r="F1937" s="2"/>
+      <c r="E1937" s="2"/>
+      <c r="F1937" s="3"/>
     </row>
     <row r="1938" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1938" s="8" t="s">
@@ -79138,7 +79412,8 @@
       <c r="D1938" s="12" t="s">
         <v>4116</v>
       </c>
-      <c r="F1938" s="2"/>
+      <c r="E1938" s="2"/>
+      <c r="F1938" s="3"/>
     </row>
     <row r="1939" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1939" s="8" t="s">
@@ -79153,7 +79428,8 @@
       <c r="D1939" s="12" t="s">
         <v>4118</v>
       </c>
-      <c r="F1939" s="2"/>
+      <c r="E1939" s="2"/>
+      <c r="F1939" s="3"/>
     </row>
     <row r="1940" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1940" s="8" t="s">
@@ -79168,7 +79444,8 @@
       <c r="D1940" s="12" t="s">
         <v>4120</v>
       </c>
-      <c r="F1940" s="2"/>
+      <c r="E1940" s="2"/>
+      <c r="F1940" s="3"/>
     </row>
     <row r="1941" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1941" s="8" t="s">
@@ -79183,7 +79460,8 @@
       <c r="D1941" s="12" t="s">
         <v>4122</v>
       </c>
-      <c r="F1941" s="2"/>
+      <c r="E1941" s="2"/>
+      <c r="F1941" s="3"/>
     </row>
     <row r="1942" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1942" s="8" t="s">
@@ -79198,7 +79476,8 @@
       <c r="D1942" s="12" t="s">
         <v>4124</v>
       </c>
-      <c r="F1942" s="2"/>
+      <c r="E1942" s="2"/>
+      <c r="F1942" s="3"/>
     </row>
     <row r="1943" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1943" s="8" t="s">
@@ -79213,7 +79492,8 @@
       <c r="D1943" s="12" t="s">
         <v>4126</v>
       </c>
-      <c r="F1943" s="2"/>
+      <c r="E1943" s="2"/>
+      <c r="F1943" s="3"/>
     </row>
     <row r="1944" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1944" s="8" t="s">
@@ -79228,7 +79508,8 @@
       <c r="D1944" s="12" t="s">
         <v>4128</v>
       </c>
-      <c r="F1944" s="2"/>
+      <c r="E1944" s="2"/>
+      <c r="F1944" s="3"/>
     </row>
     <row r="1945" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1945" s="8" t="s">
@@ -79243,7 +79524,8 @@
       <c r="D1945" s="12" t="s">
         <v>4130</v>
       </c>
-      <c r="F1945" s="2"/>
+      <c r="E1945" s="2"/>
+      <c r="F1945" s="3"/>
     </row>
     <row r="1946" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1946" s="8" t="s">
@@ -79258,7 +79540,8 @@
       <c r="D1946" s="12" t="s">
         <v>4132</v>
       </c>
-      <c r="F1946" s="2"/>
+      <c r="E1946" s="2"/>
+      <c r="F1946" s="3"/>
     </row>
     <row r="1947" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1947" s="8" t="s">
@@ -79273,7 +79556,8 @@
       <c r="D1947" s="12" t="s">
         <v>4134</v>
       </c>
-      <c r="F1947" s="2"/>
+      <c r="E1947" s="2"/>
+      <c r="F1947" s="3"/>
     </row>
     <row r="1948" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1948" s="8" t="s">
@@ -79288,7 +79572,8 @@
       <c r="D1948" s="12" t="s">
         <v>4136</v>
       </c>
-      <c r="F1948" s="2"/>
+      <c r="E1948" s="2"/>
+      <c r="F1948" s="3"/>
     </row>
     <row r="1949" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1949" s="8" t="s">
@@ -79303,7 +79588,8 @@
       <c r="D1949" s="12" t="s">
         <v>4138</v>
       </c>
-      <c r="F1949" s="2"/>
+      <c r="E1949" s="2"/>
+      <c r="F1949" s="3"/>
     </row>
     <row r="1950" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1950" s="8" t="s">
@@ -79318,7 +79604,8 @@
       <c r="D1950" s="12" t="s">
         <v>4140</v>
       </c>
-      <c r="F1950" s="2"/>
+      <c r="E1950" s="2"/>
+      <c r="F1950" s="3"/>
     </row>
     <row r="1951" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1951" s="8" t="s">
@@ -79333,7 +79620,8 @@
       <c r="D1951" s="12" t="s">
         <v>4142</v>
       </c>
-      <c r="F1951" s="2"/>
+      <c r="E1951" s="2"/>
+      <c r="F1951" s="3"/>
     </row>
     <row r="1952" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1952" s="8" t="s">
@@ -79348,7 +79636,8 @@
       <c r="D1952" s="12" t="s">
         <v>4144</v>
       </c>
-      <c r="F1952" s="2"/>
+      <c r="E1952" s="2"/>
+      <c r="F1952" s="3"/>
     </row>
     <row r="1953" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1953" s="8" t="s">
@@ -79363,7 +79652,8 @@
       <c r="D1953" s="12" t="s">
         <v>4146</v>
       </c>
-      <c r="F1953" s="2"/>
+      <c r="E1953" s="2"/>
+      <c r="F1953" s="3"/>
     </row>
     <row r="1954" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1954" s="8" t="s">
@@ -79378,7 +79668,8 @@
       <c r="D1954" s="12" t="s">
         <v>4148</v>
       </c>
-      <c r="F1954" s="2"/>
+      <c r="E1954" s="2"/>
+      <c r="F1954" s="3"/>
     </row>
     <row r="1955" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1955" s="8" t="s">
@@ -79393,7 +79684,8 @@
       <c r="D1955" s="12" t="s">
         <v>4150</v>
       </c>
-      <c r="F1955" s="2"/>
+      <c r="E1955" s="2"/>
+      <c r="F1955" s="3"/>
     </row>
     <row r="1956" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1956" s="8" t="s">
@@ -79408,7 +79700,8 @@
       <c r="D1956" s="12" t="s">
         <v>4153</v>
       </c>
-      <c r="F1956" s="2"/>
+      <c r="E1956" s="2"/>
+      <c r="F1956" s="3"/>
     </row>
     <row r="1957" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1957" s="8" t="s">
@@ -79423,7 +79716,8 @@
       <c r="D1957" s="12" t="s">
         <v>4155</v>
       </c>
-      <c r="F1957" s="2"/>
+      <c r="E1957" s="2"/>
+      <c r="F1957" s="3"/>
     </row>
     <row r="1958" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1958" s="8" t="s">
@@ -79438,7 +79732,8 @@
       <c r="D1958" s="12" t="s">
         <v>4157</v>
       </c>
-      <c r="F1958" s="2"/>
+      <c r="E1958" s="2"/>
+      <c r="F1958" s="3"/>
     </row>
     <row r="1959" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1959" s="8" t="s">
@@ -79453,7 +79748,8 @@
       <c r="D1959" s="12" t="s">
         <v>4159</v>
       </c>
-      <c r="F1959" s="2"/>
+      <c r="E1959" s="2"/>
+      <c r="F1959" s="3"/>
     </row>
     <row r="1960" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1960" s="8" t="s">
@@ -79468,7 +79764,8 @@
       <c r="D1960" s="12" t="s">
         <v>4161</v>
       </c>
-      <c r="F1960" s="2"/>
+      <c r="E1960" s="2"/>
+      <c r="F1960" s="3"/>
     </row>
     <row r="1961" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1961" s="8" t="s">
@@ -79483,7 +79780,8 @@
       <c r="D1961" s="12" t="s">
         <v>4163</v>
       </c>
-      <c r="F1961" s="2"/>
+      <c r="E1961" s="2"/>
+      <c r="F1961" s="3"/>
     </row>
     <row r="1962" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1962" s="8" t="s">
@@ -79498,7 +79796,8 @@
       <c r="D1962" s="12" t="s">
         <v>4165</v>
       </c>
-      <c r="F1962" s="2"/>
+      <c r="E1962" s="2"/>
+      <c r="F1962" s="3"/>
     </row>
     <row r="1963" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1963" s="8" t="s">
@@ -79513,7 +79812,8 @@
       <c r="D1963" s="12" t="s">
         <v>4167</v>
       </c>
-      <c r="F1963" s="2"/>
+      <c r="E1963" s="2"/>
+      <c r="F1963" s="3"/>
     </row>
     <row r="1964" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1964" s="8" t="s">
@@ -79528,7 +79828,8 @@
       <c r="D1964" s="12" t="s">
         <v>4169</v>
       </c>
-      <c r="F1964" s="2"/>
+      <c r="E1964" s="2"/>
+      <c r="F1964" s="3"/>
     </row>
     <row r="1965" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1965" s="8" t="s">
@@ -79543,7 +79844,8 @@
       <c r="D1965" s="12" t="s">
         <v>4172</v>
       </c>
-      <c r="F1965" s="2"/>
+      <c r="E1965" s="2"/>
+      <c r="F1965" s="3"/>
     </row>
     <row r="1966" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1966" s="8" t="s">
@@ -79558,7 +79860,8 @@
       <c r="D1966" s="12" t="s">
         <v>4174</v>
       </c>
-      <c r="F1966" s="2"/>
+      <c r="E1966" s="2"/>
+      <c r="F1966" s="3"/>
     </row>
     <row r="1967" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1967" s="8" t="s">
@@ -79573,7 +79876,8 @@
       <c r="D1967" s="12" t="s">
         <v>4176</v>
       </c>
-      <c r="F1967" s="2"/>
+      <c r="E1967" s="2"/>
+      <c r="F1967" s="3"/>
     </row>
     <row r="1968" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1968" s="8" t="s">
@@ -79588,7 +79892,8 @@
       <c r="D1968" s="12" t="s">
         <v>4178</v>
       </c>
-      <c r="F1968" s="2"/>
+      <c r="E1968" s="2"/>
+      <c r="F1968" s="3"/>
     </row>
     <row r="1969" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1969" s="8" t="s">
@@ -79603,7 +79908,8 @@
       <c r="D1969" s="12" t="s">
         <v>4180</v>
       </c>
-      <c r="F1969" s="2"/>
+      <c r="E1969" s="2"/>
+      <c r="F1969" s="3"/>
     </row>
     <row r="1970" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1970" s="8" t="s">
@@ -79618,7 +79924,8 @@
       <c r="D1970" s="12" t="s">
         <v>4182</v>
       </c>
-      <c r="F1970" s="2"/>
+      <c r="E1970" s="2"/>
+      <c r="F1970" s="3"/>
     </row>
     <row r="1971" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1971" s="8" t="s">
@@ -79633,7 +79940,8 @@
       <c r="D1971" s="12" t="s">
         <v>4185</v>
       </c>
-      <c r="F1971" s="2"/>
+      <c r="E1971" s="2"/>
+      <c r="F1971" s="3"/>
     </row>
     <row r="1972" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1972" s="8" t="s">
@@ -79648,7 +79956,8 @@
       <c r="D1972" s="12" t="s">
         <v>4187</v>
       </c>
-      <c r="F1972" s="2"/>
+      <c r="E1972" s="2"/>
+      <c r="F1972" s="3"/>
     </row>
     <row r="1973" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1973" s="8" t="s">
@@ -79663,7 +79972,8 @@
       <c r="D1973" s="12" t="s">
         <v>4189</v>
       </c>
-      <c r="F1973" s="2"/>
+      <c r="E1973" s="2"/>
+      <c r="F1973" s="3"/>
     </row>
     <row r="1974" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1974" s="8" t="s">
@@ -79678,7 +79988,8 @@
       <c r="D1974" s="12" t="s">
         <v>4191</v>
       </c>
-      <c r="F1974" s="2"/>
+      <c r="E1974" s="2"/>
+      <c r="F1974" s="3"/>
     </row>
     <row r="1975" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1975" s="8" t="s">
@@ -79693,7 +80004,8 @@
       <c r="D1975" s="12" t="s">
         <v>4193</v>
       </c>
-      <c r="F1975" s="2"/>
+      <c r="E1975" s="2"/>
+      <c r="F1975" s="3"/>
     </row>
     <row r="1976" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1976" s="8" t="s">
@@ -79708,7 +80020,8 @@
       <c r="D1976" s="12" t="s">
         <v>4195</v>
       </c>
-      <c r="F1976" s="2"/>
+      <c r="E1976" s="2"/>
+      <c r="F1976" s="3"/>
     </row>
     <row r="1977" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1977" s="8" t="s">
@@ -79723,7 +80036,8 @@
       <c r="D1977" s="12" t="s">
         <v>4197</v>
       </c>
-      <c r="F1977" s="2"/>
+      <c r="E1977" s="2"/>
+      <c r="F1977" s="3"/>
     </row>
     <row r="1978" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1978" s="8" t="s">
@@ -79738,7 +80052,8 @@
       <c r="D1978" s="12" t="s">
         <v>4199</v>
       </c>
-      <c r="F1978" s="2"/>
+      <c r="E1978" s="2"/>
+      <c r="F1978" s="3"/>
     </row>
     <row r="1979" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1979" s="8" t="s">
@@ -79753,7 +80068,8 @@
       <c r="D1979" s="12" t="s">
         <v>4201</v>
       </c>
-      <c r="F1979" s="2"/>
+      <c r="E1979" s="2"/>
+      <c r="F1979" s="3"/>
     </row>
     <row r="1980" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1980" s="8" t="s">
@@ -79768,7 +80084,8 @@
       <c r="D1980" s="12" t="s">
         <v>4203</v>
       </c>
-      <c r="F1980" s="2"/>
+      <c r="E1980" s="2"/>
+      <c r="F1980" s="3"/>
     </row>
     <row r="1981" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1981" s="8" t="s">
@@ -79783,7 +80100,8 @@
       <c r="D1981" s="12" t="s">
         <v>4206</v>
       </c>
-      <c r="F1981" s="2"/>
+      <c r="E1981" s="2"/>
+      <c r="F1981" s="3"/>
     </row>
     <row r="1982" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1982" s="8" t="s">
@@ -79798,7 +80116,8 @@
       <c r="D1982" s="12" t="s">
         <v>4208</v>
       </c>
-      <c r="F1982" s="2"/>
+      <c r="E1982" s="2"/>
+      <c r="F1982" s="3"/>
     </row>
     <row r="1983" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1983" s="8" t="s">
@@ -79813,7 +80132,8 @@
       <c r="D1983" s="12" t="s">
         <v>4210</v>
       </c>
-      <c r="F1983" s="2"/>
+      <c r="E1983" s="2"/>
+      <c r="F1983" s="3"/>
     </row>
     <row r="1984" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1984" s="8" t="s">
@@ -79828,7 +80148,8 @@
       <c r="D1984" s="12" t="s">
         <v>4212</v>
       </c>
-      <c r="F1984" s="2"/>
+      <c r="E1984" s="2"/>
+      <c r="F1984" s="3"/>
     </row>
     <row r="1985" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1985" s="8" t="s">
@@ -79843,7 +80164,8 @@
       <c r="D1985" s="12" t="s">
         <v>4214</v>
       </c>
-      <c r="F1985" s="2"/>
+      <c r="E1985" s="2"/>
+      <c r="F1985" s="3"/>
     </row>
     <row r="1986" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1986" s="8" t="s">
@@ -79858,7 +80180,8 @@
       <c r="D1986" s="12" t="s">
         <v>4216</v>
       </c>
-      <c r="F1986" s="2"/>
+      <c r="E1986" s="2"/>
+      <c r="F1986" s="3"/>
     </row>
     <row r="1987" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1987" s="8" t="s">
@@ -79873,7 +80196,8 @@
       <c r="D1987" s="12" t="s">
         <v>4219</v>
       </c>
-      <c r="F1987" s="2"/>
+      <c r="E1987" s="2"/>
+      <c r="F1987" s="3"/>
     </row>
     <row r="1988" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1988" s="8" t="s">
@@ -79888,7 +80212,8 @@
       <c r="D1988" s="12" t="s">
         <v>4221</v>
       </c>
-      <c r="F1988" s="2"/>
+      <c r="E1988" s="2"/>
+      <c r="F1988" s="3"/>
     </row>
     <row r="1989" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1989" s="8" t="s">
@@ -79903,7 +80228,8 @@
       <c r="D1989" s="12" t="s">
         <v>4223</v>
       </c>
-      <c r="F1989" s="2"/>
+      <c r="E1989" s="2"/>
+      <c r="F1989" s="3"/>
     </row>
     <row r="1990" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1990" s="8" t="s">
@@ -79918,7 +80244,8 @@
       <c r="D1990" s="12" t="s">
         <v>4225</v>
       </c>
-      <c r="F1990" s="2"/>
+      <c r="E1990" s="2"/>
+      <c r="F1990" s="3"/>
     </row>
     <row r="1991" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1991" s="8" t="s">
@@ -79933,7 +80260,8 @@
       <c r="D1991" s="12" t="s">
         <v>4227</v>
       </c>
-      <c r="F1991" s="2"/>
+      <c r="E1991" s="2"/>
+      <c r="F1991" s="3"/>
     </row>
     <row r="1992" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1992" s="8" t="s">
@@ -79948,7 +80276,8 @@
       <c r="D1992" s="12" t="s">
         <v>4229</v>
       </c>
-      <c r="F1992" s="2"/>
+      <c r="E1992" s="2"/>
+      <c r="F1992" s="3"/>
     </row>
     <row r="1993" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1993" s="8" t="s">
@@ -79963,7 +80292,8 @@
       <c r="D1993" s="12" t="s">
         <v>4231</v>
       </c>
-      <c r="F1993" s="2"/>
+      <c r="E1993" s="2"/>
+      <c r="F1993" s="3"/>
     </row>
     <row r="1994" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1994" s="8" t="s">
@@ -79978,7 +80308,8 @@
       <c r="D1994" s="12" t="s">
         <v>4234</v>
       </c>
-      <c r="F1994" s="2"/>
+      <c r="E1994" s="2"/>
+      <c r="F1994" s="3"/>
     </row>
     <row r="1995" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1995" s="8" t="s">
@@ -79993,7 +80324,8 @@
       <c r="D1995" s="12" t="s">
         <v>4236</v>
       </c>
-      <c r="F1995" s="2"/>
+      <c r="E1995" s="2"/>
+      <c r="F1995" s="3"/>
     </row>
     <row r="1996" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1996" s="8" t="s">
@@ -80008,7 +80340,8 @@
       <c r="D1996" s="12" t="s">
         <v>4238</v>
       </c>
-      <c r="F1996" s="2"/>
+      <c r="E1996" s="2"/>
+      <c r="F1996" s="3"/>
     </row>
     <row r="1997" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1997" s="8" t="s">
@@ -80023,7 +80356,8 @@
       <c r="D1997" s="12" t="s">
         <v>4240</v>
       </c>
-      <c r="F1997" s="2"/>
+      <c r="E1997" s="2"/>
+      <c r="F1997" s="3"/>
     </row>
     <row r="1998" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1998" s="8" t="s">
@@ -80038,7 +80372,8 @@
       <c r="D1998" s="12" t="s">
         <v>4242</v>
       </c>
-      <c r="F1998" s="2"/>
+      <c r="E1998" s="2"/>
+      <c r="F1998" s="3"/>
     </row>
     <row r="1999" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A1999" s="8" t="s">
@@ -80053,7 +80388,8 @@
       <c r="D1999" s="12" t="s">
         <v>4244</v>
       </c>
-      <c r="F1999" s="2"/>
+      <c r="E1999" s="2"/>
+      <c r="F1999" s="3"/>
     </row>
     <row r="2000" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2000" s="8" t="s">
@@ -80068,7 +80404,8 @@
       <c r="D2000" s="12" t="s">
         <v>4246</v>
       </c>
-      <c r="F2000" s="2"/>
+      <c r="E2000" s="2"/>
+      <c r="F2000" s="3"/>
     </row>
     <row r="2001" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2001" s="8" t="s">
@@ -80083,7 +80420,8 @@
       <c r="D2001" s="12" t="s">
         <v>4248</v>
       </c>
-      <c r="F2001" s="2"/>
+      <c r="E2001" s="2"/>
+      <c r="F2001" s="3"/>
     </row>
     <row r="2002" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2002" s="8" t="s">
@@ -80098,7 +80436,8 @@
       <c r="D2002" s="12" t="s">
         <v>4251</v>
       </c>
-      <c r="F2002" s="2"/>
+      <c r="E2002" s="2"/>
+      <c r="F2002" s="3"/>
     </row>
     <row r="2003" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2003" s="8" t="s">
@@ -80113,7 +80452,8 @@
       <c r="D2003" s="12" t="s">
         <v>4253</v>
       </c>
-      <c r="F2003" s="2"/>
+      <c r="E2003" s="2"/>
+      <c r="F2003" s="3"/>
     </row>
     <row r="2004" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2004" s="8" t="s">
@@ -80128,7 +80468,8 @@
       <c r="D2004" s="12" t="s">
         <v>4255</v>
       </c>
-      <c r="F2004" s="2"/>
+      <c r="E2004" s="2"/>
+      <c r="F2004" s="3"/>
     </row>
     <row r="2005" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2005" s="8" t="s">
@@ -80143,7 +80484,8 @@
       <c r="D2005" s="12" t="s">
         <v>4257</v>
       </c>
-      <c r="F2005" s="2"/>
+      <c r="E2005" s="2"/>
+      <c r="F2005" s="3"/>
     </row>
     <row r="2006" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2006" s="8" t="s">
@@ -80158,7 +80500,8 @@
       <c r="D2006" s="12" t="s">
         <v>4259</v>
       </c>
-      <c r="F2006" s="2"/>
+      <c r="E2006" s="2"/>
+      <c r="F2006" s="3"/>
     </row>
     <row r="2007" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2007" s="8" t="s">
@@ -80173,7 +80516,8 @@
       <c r="D2007" s="12" t="s">
         <v>4262</v>
       </c>
-      <c r="F2007" s="2"/>
+      <c r="E2007" s="2"/>
+      <c r="F2007" s="3"/>
     </row>
     <row r="2008" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2008" s="8" t="s">
@@ -80188,7 +80532,8 @@
       <c r="D2008" s="12" t="s">
         <v>4264</v>
       </c>
-      <c r="F2008" s="2"/>
+      <c r="E2008" s="2"/>
+      <c r="F2008" s="3"/>
     </row>
     <row r="2009" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2009" s="8" t="s">
@@ -80203,7 +80548,8 @@
       <c r="D2009" s="12" t="s">
         <v>4266</v>
       </c>
-      <c r="F2009" s="2"/>
+      <c r="E2009" s="2"/>
+      <c r="F2009" s="3"/>
     </row>
     <row r="2010" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2010" s="8" t="s">
@@ -80218,7 +80564,8 @@
       <c r="D2010" s="12" t="s">
         <v>4269</v>
       </c>
-      <c r="F2010" s="2"/>
+      <c r="E2010" s="2"/>
+      <c r="F2010" s="3"/>
     </row>
     <row r="2011" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2011" s="8" t="s">
@@ -80233,7 +80580,8 @@
       <c r="D2011" s="12" t="s">
         <v>4271</v>
       </c>
-      <c r="F2011" s="2"/>
+      <c r="E2011" s="2"/>
+      <c r="F2011" s="3"/>
     </row>
     <row r="2012" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2012" s="8" t="s">
@@ -80248,7 +80596,8 @@
       <c r="D2012" s="12" t="s">
         <v>4273</v>
       </c>
-      <c r="F2012" s="2"/>
+      <c r="E2012" s="2"/>
+      <c r="F2012" s="3"/>
     </row>
     <row r="2013" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2013" s="8" t="s">
@@ -80263,7 +80612,8 @@
       <c r="D2013" s="12" t="s">
         <v>4275</v>
       </c>
-      <c r="F2013" s="2"/>
+      <c r="E2013" s="2"/>
+      <c r="F2013" s="3"/>
     </row>
     <row r="2014" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2014" s="8" t="s">
@@ -80278,7 +80628,8 @@
       <c r="D2014" s="12" t="s">
         <v>4277</v>
       </c>
-      <c r="F2014" s="2"/>
+      <c r="E2014" s="2"/>
+      <c r="F2014" s="3"/>
     </row>
     <row r="2015" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2015" s="8" t="s">
@@ -80293,7 +80644,8 @@
       <c r="D2015" s="12" t="s">
         <v>4279</v>
       </c>
-      <c r="F2015" s="2"/>
+      <c r="E2015" s="2"/>
+      <c r="F2015" s="3"/>
     </row>
     <row r="2016" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2016" s="8" t="s">
@@ -80308,7 +80660,8 @@
       <c r="D2016" s="12" t="s">
         <v>4281</v>
       </c>
-      <c r="F2016" s="2"/>
+      <c r="E2016" s="2"/>
+      <c r="F2016" s="3"/>
     </row>
     <row r="2017" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2017" s="8" t="s">
@@ -80323,7 +80676,8 @@
       <c r="D2017" s="12" t="s">
         <v>4283</v>
       </c>
-      <c r="F2017" s="2"/>
+      <c r="E2017" s="2"/>
+      <c r="F2017" s="3"/>
     </row>
     <row r="2018" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2018" s="8" t="s">
@@ -80338,7 +80692,8 @@
       <c r="D2018" s="12" t="s">
         <v>4285</v>
       </c>
-      <c r="F2018" s="2"/>
+      <c r="E2018" s="2"/>
+      <c r="F2018" s="3"/>
     </row>
     <row r="2019" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2019" s="8" t="s">
@@ -80353,7 +80708,8 @@
       <c r="D2019" s="12" t="s">
         <v>4287</v>
       </c>
-      <c r="F2019" s="2"/>
+      <c r="E2019" s="2"/>
+      <c r="F2019" s="3"/>
     </row>
     <row r="2020" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2020" s="8" t="s">
@@ -80368,7 +80724,8 @@
       <c r="D2020" s="12" t="s">
         <v>4289</v>
       </c>
-      <c r="F2020" s="2"/>
+      <c r="E2020" s="2"/>
+      <c r="F2020" s="3"/>
     </row>
     <row r="2021" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2021" s="8" t="s">
@@ -80383,7 +80740,8 @@
       <c r="D2021" s="12" t="s">
         <v>4291</v>
       </c>
-      <c r="F2021" s="2"/>
+      <c r="E2021" s="2"/>
+      <c r="F2021" s="3"/>
     </row>
     <row r="2022" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2022" s="8" t="s">
@@ -80398,7 +80756,8 @@
       <c r="D2022" s="12" t="s">
         <v>4293</v>
       </c>
-      <c r="F2022" s="2"/>
+      <c r="E2022" s="2"/>
+      <c r="F2022" s="3"/>
     </row>
     <row r="2023" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2023" s="8" t="s">
@@ -80413,7 +80772,8 @@
       <c r="D2023" s="12" t="s">
         <v>4296</v>
       </c>
-      <c r="F2023" s="2"/>
+      <c r="E2023" s="2"/>
+      <c r="F2023" s="3"/>
     </row>
     <row r="2024" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2024" s="8" t="s">
@@ -80428,7 +80788,8 @@
       <c r="D2024" s="12" t="s">
         <v>4298</v>
       </c>
-      <c r="F2024" s="2"/>
+      <c r="E2024" s="2"/>
+      <c r="F2024" s="3"/>
     </row>
     <row r="2025" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2025" s="8" t="s">
@@ -80443,7 +80804,8 @@
       <c r="D2025" s="12" t="s">
         <v>4300</v>
       </c>
-      <c r="F2025" s="2"/>
+      <c r="E2025" s="2"/>
+      <c r="F2025" s="3"/>
     </row>
     <row r="2026" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2026" s="8" t="s">
@@ -80458,7 +80820,8 @@
       <c r="D2026" s="12" t="s">
         <v>4302</v>
       </c>
-      <c r="F2026" s="2"/>
+      <c r="E2026" s="2"/>
+      <c r="F2026" s="3"/>
     </row>
     <row r="2027" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2027" s="8" t="s">
@@ -80473,7 +80836,8 @@
       <c r="D2027" s="12" t="s">
         <v>4304</v>
       </c>
-      <c r="F2027" s="2"/>
+      <c r="E2027" s="2"/>
+      <c r="F2027" s="3"/>
     </row>
     <row r="2028" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2028" s="8" t="s">
@@ -80488,7 +80852,8 @@
       <c r="D2028" s="12" t="s">
         <v>4306</v>
       </c>
-      <c r="F2028" s="2"/>
+      <c r="E2028" s="2"/>
+      <c r="F2028" s="3"/>
     </row>
     <row r="2029" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2029" s="8" t="s">
@@ -80503,7 +80868,8 @@
       <c r="D2029" s="12" t="s">
         <v>4308</v>
       </c>
-      <c r="F2029" s="2"/>
+      <c r="E2029" s="2"/>
+      <c r="F2029" s="3"/>
     </row>
     <row r="2030" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2030" s="8" t="s">
@@ -80518,7 +80884,8 @@
       <c r="D2030" s="12" t="s">
         <v>4310</v>
       </c>
-      <c r="F2030" s="2"/>
+      <c r="E2030" s="2"/>
+      <c r="F2030" s="3"/>
     </row>
     <row r="2031" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2031" s="8" t="s">
@@ -80533,7 +80900,8 @@
       <c r="D2031" s="12" t="s">
         <v>4312</v>
       </c>
-      <c r="F2031" s="2"/>
+      <c r="E2031" s="2"/>
+      <c r="F2031" s="3"/>
     </row>
     <row r="2032" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2032" s="8" t="s">
@@ -80548,7 +80916,8 @@
       <c r="D2032" s="12" t="s">
         <v>4314</v>
       </c>
-      <c r="F2032" s="2"/>
+      <c r="E2032" s="2"/>
+      <c r="F2032" s="3"/>
     </row>
     <row r="2033" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2033" s="8" t="s">
@@ -80563,7 +80932,8 @@
       <c r="D2033" s="12" t="s">
         <v>4316</v>
       </c>
-      <c r="F2033" s="2"/>
+      <c r="E2033" s="2"/>
+      <c r="F2033" s="3"/>
     </row>
     <row r="2034" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2034" s="8" t="s">
@@ -80578,7 +80948,8 @@
       <c r="D2034" s="12" t="s">
         <v>4318</v>
       </c>
-      <c r="F2034" s="2"/>
+      <c r="E2034" s="2"/>
+      <c r="F2034" s="3"/>
     </row>
     <row r="2035" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2035" s="8" t="s">
@@ -80593,7 +80964,8 @@
       <c r="D2035" s="12" t="s">
         <v>4320</v>
       </c>
-      <c r="F2035" s="2"/>
+      <c r="E2035" s="2"/>
+      <c r="F2035" s="3"/>
     </row>
     <row r="2036" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2036" s="8" t="s">
@@ -80608,7 +80980,8 @@
       <c r="D2036" s="12" t="s">
         <v>4322</v>
       </c>
-      <c r="F2036" s="2"/>
+      <c r="E2036" s="2"/>
+      <c r="F2036" s="3"/>
     </row>
     <row r="2037" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2037" s="8" t="s">
@@ -80623,7 +80996,8 @@
       <c r="D2037" s="12" t="s">
         <v>4324</v>
       </c>
-      <c r="F2037" s="2"/>
+      <c r="E2037" s="2"/>
+      <c r="F2037" s="3"/>
     </row>
     <row r="2038" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2038" s="8" t="s">
@@ -80638,7 +81012,8 @@
       <c r="D2038" s="12" t="s">
         <v>4326</v>
       </c>
-      <c r="F2038" s="2"/>
+      <c r="E2038" s="2"/>
+      <c r="F2038" s="3"/>
     </row>
     <row r="2039" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2039" s="8" t="s">
@@ -80653,7 +81028,8 @@
       <c r="D2039" s="12" t="s">
         <v>4328</v>
       </c>
-      <c r="F2039" s="2"/>
+      <c r="E2039" s="2"/>
+      <c r="F2039" s="3"/>
     </row>
     <row r="2040" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2040" s="8" t="s">
@@ -80668,7 +81044,8 @@
       <c r="D2040" s="12" t="s">
         <v>4330</v>
       </c>
-      <c r="F2040" s="2"/>
+      <c r="E2040" s="2"/>
+      <c r="F2040" s="3"/>
     </row>
     <row r="2041" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2041" s="8" t="s">
@@ -80683,7 +81060,8 @@
       <c r="D2041" s="12" t="s">
         <v>4333</v>
       </c>
-      <c r="F2041" s="2"/>
+      <c r="E2041" s="2"/>
+      <c r="F2041" s="3"/>
     </row>
     <row r="2042" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2042" s="8" t="s">
@@ -80698,7 +81076,8 @@
       <c r="D2042" s="12" t="s">
         <v>4335</v>
       </c>
-      <c r="F2042" s="2"/>
+      <c r="E2042" s="2"/>
+      <c r="F2042" s="3"/>
     </row>
     <row r="2043" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2043" s="8" t="s">
@@ -80713,7 +81092,8 @@
       <c r="D2043" s="12" t="s">
         <v>4337</v>
       </c>
-      <c r="F2043" s="2"/>
+      <c r="E2043" s="2"/>
+      <c r="F2043" s="3"/>
     </row>
     <row r="2044" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2044" s="8" t="s">
@@ -80728,7 +81108,8 @@
       <c r="D2044" s="12" t="s">
         <v>4339</v>
       </c>
-      <c r="F2044" s="2"/>
+      <c r="E2044" s="2"/>
+      <c r="F2044" s="3"/>
     </row>
     <row r="2045" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2045" s="8" t="s">
@@ -80743,7 +81124,8 @@
       <c r="D2045" s="12" t="s">
         <v>4341</v>
       </c>
-      <c r="F2045" s="2"/>
+      <c r="E2045" s="2"/>
+      <c r="F2045" s="3"/>
     </row>
     <row r="2046" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2046" s="8" t="s">
@@ -80758,7 +81140,8 @@
       <c r="D2046" s="12" t="s">
         <v>4343</v>
       </c>
-      <c r="F2046" s="2"/>
+      <c r="E2046" s="2"/>
+      <c r="F2046" s="3"/>
     </row>
     <row r="2047" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2047" s="8" t="s">
@@ -80773,7 +81156,8 @@
       <c r="D2047" s="12" t="s">
         <v>4345</v>
       </c>
-      <c r="F2047" s="2"/>
+      <c r="E2047" s="2"/>
+      <c r="F2047" s="3"/>
     </row>
     <row r="2048" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2048" s="8" t="s">
@@ -80788,7 +81172,8 @@
       <c r="D2048" s="12" t="s">
         <v>4347</v>
       </c>
-      <c r="F2048" s="2"/>
+      <c r="E2048" s="2"/>
+      <c r="F2048" s="3"/>
     </row>
     <row r="2049" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2049" s="8" t="s">
@@ -80803,7 +81188,8 @@
       <c r="D2049" s="12" t="s">
         <v>4349</v>
       </c>
-      <c r="F2049" s="2"/>
+      <c r="E2049" s="2"/>
+      <c r="F2049" s="3"/>
     </row>
     <row r="2050" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2050" s="8" t="s">
@@ -80818,7 +81204,8 @@
       <c r="D2050" s="12" t="s">
         <v>4351</v>
       </c>
-      <c r="F2050" s="2"/>
+      <c r="E2050" s="2"/>
+      <c r="F2050" s="3"/>
     </row>
     <row r="2051" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2051" s="8" t="s">
@@ -80833,7 +81220,8 @@
       <c r="D2051" s="12" t="s">
         <v>4353</v>
       </c>
-      <c r="F2051" s="2"/>
+      <c r="E2051" s="2"/>
+      <c r="F2051" s="3"/>
     </row>
     <row r="2052" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2052" s="8" t="s">
@@ -80848,7 +81236,8 @@
       <c r="D2052" s="12" t="s">
         <v>4355</v>
       </c>
-      <c r="F2052" s="2"/>
+      <c r="E2052" s="2"/>
+      <c r="F2052" s="3"/>
     </row>
     <row r="2053" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2053" s="8" t="s">
@@ -80863,7 +81252,8 @@
       <c r="D2053" s="12" t="s">
         <v>4357</v>
       </c>
-      <c r="F2053" s="2"/>
+      <c r="E2053" s="2"/>
+      <c r="F2053" s="3"/>
     </row>
     <row r="2054" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2054" s="8" t="s">
@@ -80878,7 +81268,8 @@
       <c r="D2054" s="12" t="s">
         <v>4359</v>
       </c>
-      <c r="F2054" s="2"/>
+      <c r="E2054" s="2"/>
+      <c r="F2054" s="3"/>
     </row>
     <row r="2055" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2055" s="8" t="s">
@@ -80893,7 +81284,8 @@
       <c r="D2055" s="12" t="s">
         <v>4361</v>
       </c>
-      <c r="F2055" s="2"/>
+      <c r="E2055" s="2"/>
+      <c r="F2055" s="3"/>
     </row>
     <row r="2056" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2056" s="8" t="s">
@@ -80908,7 +81300,8 @@
       <c r="D2056" s="12" t="s">
         <v>4363</v>
       </c>
-      <c r="F2056" s="2"/>
+      <c r="E2056" s="2"/>
+      <c r="F2056" s="3"/>
     </row>
     <row r="2057" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2057" s="8" t="s">
@@ -80923,7 +81316,8 @@
       <c r="D2057" s="12" t="s">
         <v>4365</v>
       </c>
-      <c r="F2057" s="2"/>
+      <c r="E2057" s="2"/>
+      <c r="F2057" s="3"/>
     </row>
     <row r="2058" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2058" s="8" t="s">
@@ -80941,7 +81335,7 @@
       <c r="E2058" s="8">
         <v>40906</v>
       </c>
-      <c r="F2058" s="2"/>
+      <c r="F2058" s="3"/>
     </row>
     <row r="2059" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2059" s="8" t="s">
@@ -80959,7 +81353,7 @@
       <c r="E2059" s="8">
         <v>40985</v>
       </c>
-      <c r="F2059" s="2"/>
+      <c r="F2059" s="3"/>
     </row>
     <row r="2060" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2060" s="8" t="s">
@@ -82694,6 +83088,7 @@
       <c r="D2146" s="12" t="s">
         <v>4555</v>
       </c>
+      <c r="E2146" s="2"/>
       <c r="F2146" s="8">
         <v>22790</v>
       </c>
@@ -82711,6 +83106,7 @@
       <c r="D2147" s="12" t="s">
         <v>4557</v>
       </c>
+      <c r="E2147" s="2"/>
       <c r="F2147" s="8">
         <v>22954</v>
       </c>
@@ -82728,6 +83124,7 @@
       <c r="D2148" s="12" t="s">
         <v>4559</v>
       </c>
+      <c r="E2148" s="2"/>
       <c r="F2148" s="8">
         <v>24073</v>
       </c>
@@ -82745,6 +83142,7 @@
       <c r="D2149" s="12" t="s">
         <v>4561</v>
       </c>
+      <c r="E2149" s="2"/>
       <c r="F2149" s="8">
         <v>23595</v>
       </c>
@@ -82762,6 +83160,7 @@
       <c r="D2150" s="12" t="s">
         <v>4563</v>
       </c>
+      <c r="E2150" s="2"/>
       <c r="F2150" s="8">
         <v>10243</v>
       </c>
@@ -82779,6 +83178,7 @@
       <c r="D2151" s="12" t="s">
         <v>4565</v>
       </c>
+      <c r="E2151" s="2"/>
       <c r="F2151" s="8">
         <v>23298</v>
       </c>
@@ -82796,6 +83196,7 @@
       <c r="D2152" s="12" t="s">
         <v>4567</v>
       </c>
+      <c r="E2152" s="2"/>
       <c r="F2152" s="8">
         <v>18679</v>
       </c>
@@ -82813,6 +83214,7 @@
       <c r="D2153" s="12" t="s">
         <v>4569</v>
       </c>
+      <c r="E2153" s="2"/>
       <c r="F2153" s="8">
         <v>17374</v>
       </c>
@@ -82830,6 +83232,7 @@
       <c r="D2154" s="12" t="s">
         <v>4571</v>
       </c>
+      <c r="E2154" s="2"/>
       <c r="F2154" s="8">
         <v>17701</v>
       </c>
@@ -82847,6 +83250,7 @@
       <c r="D2155" s="12" t="s">
         <v>4573</v>
       </c>
+      <c r="E2155" s="2"/>
       <c r="F2155" s="8">
         <v>17440</v>
       </c>
@@ -82864,6 +83268,7 @@
       <c r="D2156" s="12" t="s">
         <v>4575</v>
       </c>
+      <c r="E2156" s="2"/>
       <c r="F2156" s="8">
         <v>17239</v>
       </c>
@@ -82881,6 +83286,7 @@
       <c r="D2157" s="12" t="s">
         <v>4577</v>
       </c>
+      <c r="E2157" s="2"/>
       <c r="F2157" s="8">
         <v>10553</v>
       </c>
@@ -82898,6 +83304,7 @@
       <c r="D2158" s="12" t="s">
         <v>4579</v>
       </c>
+      <c r="E2158" s="2"/>
       <c r="F2158" s="8">
         <v>10847</v>
       </c>
@@ -82915,6 +83322,7 @@
       <c r="D2159" s="12" t="s">
         <v>4581</v>
       </c>
+      <c r="E2159" s="2"/>
       <c r="F2159" s="8">
         <v>21410</v>
       </c>
@@ -82932,6 +83340,7 @@
       <c r="D2160" s="12" t="s">
         <v>4584</v>
       </c>
+      <c r="E2160" s="2"/>
       <c r="F2160" s="8">
         <v>19728</v>
       </c>
@@ -82949,6 +83358,7 @@
       <c r="D2161" s="12" t="s">
         <v>4586</v>
       </c>
+      <c r="E2161" s="2"/>
       <c r="F2161" s="8">
         <v>16673</v>
       </c>
@@ -82966,6 +83376,7 @@
       <c r="D2162" s="12" t="s">
         <v>4588</v>
       </c>
+      <c r="E2162" s="2"/>
       <c r="F2162" s="8">
         <v>13512</v>
       </c>
@@ -82983,6 +83394,7 @@
       <c r="D2163" s="12" t="s">
         <v>4590</v>
       </c>
+      <c r="E2163" s="2"/>
       <c r="F2163" s="8">
         <v>17518</v>
       </c>
@@ -83000,6 +83412,7 @@
       <c r="D2164" s="12" t="s">
         <v>4592</v>
       </c>
+      <c r="E2164" s="2"/>
       <c r="F2164" s="8">
         <v>14066</v>
       </c>
@@ -83017,6 +83430,7 @@
       <c r="D2165" s="12" t="s">
         <v>4594</v>
       </c>
+      <c r="E2165" s="2"/>
       <c r="F2165" s="8">
         <v>17502</v>
       </c>
@@ -83034,6 +83448,7 @@
       <c r="D2166" s="12" t="s">
         <v>4596</v>
       </c>
+      <c r="E2166" s="2"/>
       <c r="F2166" s="8">
         <v>14804</v>
       </c>
@@ -83051,6 +83466,7 @@
       <c r="D2167" s="12" t="s">
         <v>4598</v>
       </c>
+      <c r="E2167" s="2"/>
       <c r="F2167" s="8">
         <v>12298</v>
       </c>
@@ -83068,6 +83484,7 @@
       <c r="D2168" s="12" t="s">
         <v>4600</v>
       </c>
+      <c r="E2168" s="2"/>
       <c r="F2168" s="8">
         <v>14442</v>
       </c>
@@ -83085,6 +83502,7 @@
       <c r="D2169" s="12" t="s">
         <v>4603</v>
       </c>
+      <c r="E2169" s="2"/>
       <c r="F2169" s="8">
         <v>19988</v>
       </c>
@@ -83102,6 +83520,7 @@
       <c r="D2170" s="12" t="s">
         <v>4605</v>
       </c>
+      <c r="E2170" s="2"/>
       <c r="F2170" s="8">
         <v>15701</v>
       </c>
@@ -83119,6 +83538,7 @@
       <c r="D2171" s="12" t="s">
         <v>4607</v>
       </c>
+      <c r="E2171" s="2"/>
       <c r="F2171" s="8">
         <v>19397</v>
       </c>
@@ -83136,6 +83556,7 @@
       <c r="D2172" s="12" t="s">
         <v>4609</v>
       </c>
+      <c r="E2172" s="2"/>
       <c r="F2172" s="8">
         <v>16535</v>
       </c>
@@ -83153,6 +83574,7 @@
       <c r="D2173" s="12" t="s">
         <v>4611</v>
       </c>
+      <c r="E2173" s="2"/>
       <c r="F2173" s="8">
         <v>16220</v>
       </c>
@@ -83170,6 +83592,7 @@
       <c r="D2174" s="12" t="s">
         <v>4613</v>
       </c>
+      <c r="E2174" s="2"/>
       <c r="F2174" s="8">
         <v>15441</v>
       </c>
@@ -83187,6 +83610,7 @@
       <c r="D2175" s="12" t="s">
         <v>4615</v>
       </c>
+      <c r="E2175" s="2"/>
       <c r="F2175" s="8">
         <v>15858</v>
       </c>
@@ -83204,6 +83628,7 @@
       <c r="D2176" s="12" t="s">
         <v>4617</v>
       </c>
+      <c r="E2176" s="2"/>
       <c r="F2176" s="8">
         <v>15128</v>
       </c>
@@ -83221,6 +83646,7 @@
       <c r="D2177" s="12" t="s">
         <v>4619</v>
       </c>
+      <c r="E2177" s="2"/>
       <c r="F2177" s="8">
         <v>17966</v>
       </c>
@@ -83238,6 +83664,7 @@
       <c r="D2178" s="12" t="s">
         <v>4622</v>
       </c>
+      <c r="E2178" s="2"/>
       <c r="F2178" s="8">
         <v>14854</v>
       </c>
@@ -83255,6 +83682,7 @@
       <c r="D2179" s="12" t="s">
         <v>4624</v>
       </c>
+      <c r="E2179" s="2"/>
       <c r="F2179" s="8">
         <v>12255</v>
       </c>
@@ -83272,6 +83700,7 @@
       <c r="D2180" s="12" t="s">
         <v>4626</v>
       </c>
+      <c r="E2180" s="2"/>
       <c r="F2180" s="8">
         <v>12626</v>
       </c>
@@ -83289,6 +83718,7 @@
       <c r="D2181" s="12" t="s">
         <v>4628</v>
       </c>
+      <c r="E2181" s="2"/>
       <c r="F2181" s="8">
         <v>12992</v>
       </c>
@@ -83306,6 +83736,7 @@
       <c r="D2182" s="12" t="s">
         <v>4630</v>
       </c>
+      <c r="E2182" s="2"/>
       <c r="F2182" s="8">
         <v>13463</v>
       </c>
@@ -83323,6 +83754,7 @@
       <c r="D2183" s="12" t="s">
         <v>4633</v>
       </c>
+      <c r="E2183" s="2"/>
       <c r="F2183" s="8">
         <v>12657</v>
       </c>
@@ -83340,6 +83772,7 @@
       <c r="D2184" s="12" t="s">
         <v>4635</v>
       </c>
+      <c r="E2184" s="2"/>
       <c r="F2184" s="8">
         <v>11335</v>
       </c>
@@ -83357,6 +83790,7 @@
       <c r="D2185" s="12" t="s">
         <v>4637</v>
       </c>
+      <c r="E2185" s="2"/>
       <c r="F2185" s="8">
         <v>11195</v>
       </c>
@@ -83374,6 +83808,7 @@
       <c r="D2186" s="12" t="s">
         <v>4639</v>
       </c>
+      <c r="E2186" s="2"/>
       <c r="F2186" s="8">
         <v>11357</v>
       </c>
@@ -83391,6 +83826,7 @@
       <c r="D2187" s="12" t="s">
         <v>4641</v>
       </c>
+      <c r="E2187" s="2"/>
       <c r="F2187" s="8">
         <v>10738</v>
       </c>
@@ -83408,6 +83844,7 @@
       <c r="D2188" s="12" t="s">
         <v>4643</v>
       </c>
+      <c r="E2188" s="2"/>
       <c r="F2188" s="8">
         <v>11148</v>
       </c>
@@ -83425,6 +83862,7 @@
       <c r="D2189" s="12" t="s">
         <v>4645</v>
       </c>
+      <c r="E2189" s="2"/>
       <c r="F2189" s="8">
         <v>11305</v>
       </c>
@@ -83442,6 +83880,7 @@
       <c r="D2190" s="12" t="s">
         <v>4647</v>
       </c>
+      <c r="E2190" s="2"/>
       <c r="F2190" s="8">
         <v>11490</v>
       </c>
@@ -83459,6 +83898,7 @@
       <c r="D2191" s="12" t="s">
         <v>4649</v>
       </c>
+      <c r="E2191" s="2"/>
       <c r="F2191" s="8">
         <v>10467</v>
       </c>
@@ -83476,6 +83916,7 @@
       <c r="D2192" s="12" t="s">
         <v>4651</v>
       </c>
+      <c r="E2192" s="2"/>
       <c r="F2192" s="8">
         <v>11041</v>
       </c>
@@ -83493,6 +83934,7 @@
       <c r="D2193" s="12" t="s">
         <v>4653</v>
       </c>
+      <c r="E2193" s="2"/>
       <c r="F2193" s="8">
         <v>13022</v>
       </c>
@@ -83510,6 +83952,7 @@
       <c r="D2194" s="12" t="s">
         <v>4656</v>
       </c>
+      <c r="E2194" s="2"/>
       <c r="F2194" s="8">
         <v>20632</v>
       </c>
@@ -83527,6 +83970,7 @@
       <c r="D2195" s="12" t="s">
         <v>4658</v>
       </c>
+      <c r="E2195" s="2"/>
       <c r="F2195" s="8">
         <v>13413</v>
       </c>
@@ -83544,6 +83988,7 @@
       <c r="D2196" s="12" t="s">
         <v>4660</v>
       </c>
+      <c r="E2196" s="2"/>
       <c r="F2196" s="8">
         <v>13174</v>
       </c>
@@ -83561,6 +84006,7 @@
       <c r="D2197" s="12" t="s">
         <v>4662</v>
       </c>
+      <c r="E2197" s="2"/>
       <c r="F2197" s="8">
         <v>14345</v>
       </c>
@@ -83578,6 +84024,7 @@
       <c r="D2198" s="12" t="s">
         <v>4664</v>
       </c>
+      <c r="E2198" s="2"/>
       <c r="F2198" s="8">
         <v>8972</v>
       </c>
@@ -83595,6 +84042,7 @@
       <c r="D2199" s="12" t="s">
         <v>4667</v>
       </c>
+      <c r="E2199" s="2"/>
       <c r="F2199" s="8">
         <v>13236</v>
       </c>
@@ -83612,6 +84060,7 @@
       <c r="D2200" s="12" t="s">
         <v>4669</v>
       </c>
+      <c r="E2200" s="2"/>
       <c r="F2200" s="8">
         <v>12949</v>
       </c>
@@ -83629,6 +84078,7 @@
       <c r="D2201" s="12" t="s">
         <v>4671</v>
       </c>
+      <c r="E2201" s="2"/>
       <c r="F2201" s="8">
         <v>12142</v>
       </c>
@@ -83646,6 +84096,7 @@
       <c r="D2202" s="12" t="s">
         <v>4673</v>
       </c>
+      <c r="E2202" s="2"/>
       <c r="F2202" s="8">
         <v>12835</v>
       </c>
@@ -83663,6 +84114,7 @@
       <c r="D2203" s="12" t="s">
         <v>4675</v>
       </c>
+      <c r="E2203" s="2"/>
       <c r="F2203" s="8">
         <v>13143</v>
       </c>
@@ -83680,6 +84132,7 @@
       <c r="D2204" s="12" t="s">
         <v>4677</v>
       </c>
+      <c r="E2204" s="2"/>
       <c r="F2204" s="8">
         <v>13141</v>
       </c>
@@ -83697,6 +84150,7 @@
       <c r="D2205" s="12" t="s">
         <v>4679</v>
       </c>
+      <c r="E2205" s="2"/>
       <c r="F2205" s="8">
         <v>11879</v>
       </c>
@@ -83714,6 +84168,7 @@
       <c r="D2206" s="12" t="s">
         <v>4681</v>
       </c>
+      <c r="E2206" s="2"/>
       <c r="F2206" s="8">
         <v>11934</v>
       </c>
@@ -83731,6 +84186,7 @@
       <c r="D2207" s="12" t="s">
         <v>4683</v>
       </c>
+      <c r="E2207" s="2"/>
       <c r="F2207" s="8">
         <v>11779</v>
       </c>
@@ -83748,6 +84204,7 @@
       <c r="D2208" s="12" t="s">
         <v>4685</v>
       </c>
+      <c r="E2208" s="2"/>
       <c r="F2208" s="8">
         <v>11736</v>
       </c>
@@ -83765,6 +84222,7 @@
       <c r="D2209" s="12" t="s">
         <v>4688</v>
       </c>
+      <c r="E2209" s="2"/>
       <c r="F2209" s="8">
         <v>12869</v>
       </c>
@@ -83782,6 +84240,7 @@
       <c r="D2210" s="12" t="s">
         <v>4690</v>
       </c>
+      <c r="E2210" s="2"/>
       <c r="F2210" s="8">
         <v>13034</v>
       </c>
@@ -83799,6 +84258,7 @@
       <c r="D2211" s="12" t="s">
         <v>4692</v>
       </c>
+      <c r="E2211" s="2"/>
       <c r="F2211" s="8">
         <v>13561</v>
       </c>
@@ -83816,6 +84276,7 @@
       <c r="D2212" s="12" t="s">
         <v>4694</v>
       </c>
+      <c r="E2212" s="2"/>
       <c r="F2212" s="8">
         <v>12918</v>
       </c>
@@ -83833,6 +84294,7 @@
       <c r="D2213" s="12" t="s">
         <v>4696</v>
       </c>
+      <c r="E2213" s="2"/>
       <c r="F2213" s="8">
         <v>12571</v>
       </c>
@@ -83850,6 +84312,7 @@
       <c r="D2214" s="12" t="s">
         <v>4698</v>
       </c>
+      <c r="E2214" s="2"/>
       <c r="F2214" s="8">
         <v>12863</v>
       </c>
@@ -83867,6 +84330,7 @@
       <c r="D2215" s="12" t="s">
         <v>4700</v>
       </c>
+      <c r="E2215" s="2"/>
       <c r="F2215" s="8">
         <v>13484</v>
       </c>
@@ -83884,6 +84348,7 @@
       <c r="D2216" s="12" t="s">
         <v>4702</v>
       </c>
+      <c r="E2216" s="2"/>
       <c r="F2216" s="8">
         <v>12401</v>
       </c>
@@ -83901,6 +84366,7 @@
       <c r="D2217" s="12" t="s">
         <v>4705</v>
       </c>
+      <c r="E2217" s="2"/>
       <c r="F2217" s="8">
         <v>13751</v>
       </c>
@@ -83918,6 +84384,7 @@
       <c r="D2218" s="12" t="s">
         <v>4707</v>
       </c>
+      <c r="E2218" s="2"/>
       <c r="F2218" s="8">
         <v>12095</v>
       </c>
@@ -83935,6 +84402,7 @@
       <c r="D2219" s="12" t="s">
         <v>4709</v>
       </c>
+      <c r="E2219" s="2"/>
       <c r="F2219" s="8">
         <v>12243</v>
       </c>
@@ -83952,6 +84420,7 @@
       <c r="D2220" s="12" t="s">
         <v>4711</v>
       </c>
+      <c r="E2220" s="2"/>
       <c r="F2220" s="8">
         <v>12564</v>
       </c>
@@ -83969,6 +84438,7 @@
       <c r="D2221" s="12" t="s">
         <v>4713</v>
       </c>
+      <c r="E2221" s="2"/>
       <c r="F2221" s="8">
         <v>12890</v>
       </c>
@@ -83986,6 +84456,7 @@
       <c r="D2222" s="12" t="s">
         <v>4715</v>
       </c>
+      <c r="E2222" s="2"/>
       <c r="F2222" s="8">
         <v>12484</v>
       </c>
@@ -84003,6 +84474,7 @@
       <c r="D2223" s="12" t="s">
         <v>4717</v>
       </c>
+      <c r="E2223" s="2"/>
       <c r="F2223" s="8">
         <v>11922</v>
       </c>
@@ -84020,6 +84492,7 @@
       <c r="D2224" s="12" t="s">
         <v>4719</v>
       </c>
+      <c r="E2224" s="2"/>
       <c r="F2224" s="8">
         <v>14671</v>
       </c>
@@ -84037,6 +84510,7 @@
       <c r="D2225" s="12" t="s">
         <v>4721</v>
       </c>
+      <c r="E2225" s="2"/>
       <c r="F2225" s="8">
         <v>11916</v>
       </c>
@@ -84054,6 +84528,7 @@
       <c r="D2226" s="12" t="s">
         <v>4723</v>
       </c>
+      <c r="E2226" s="2"/>
       <c r="F2226" s="8">
         <v>14035</v>
       </c>
@@ -84071,6 +84546,7 @@
       <c r="D2227" s="12" t="s">
         <v>4726</v>
       </c>
+      <c r="E2227" s="2"/>
       <c r="F2227" s="8">
         <v>18382</v>
       </c>
@@ -84088,6 +84564,7 @@
       <c r="D2228" s="12" t="s">
         <v>4728</v>
       </c>
+      <c r="E2228" s="2"/>
       <c r="F2228" s="8">
         <v>18229</v>
       </c>
@@ -84105,6 +84582,7 @@
       <c r="D2229" s="12" t="s">
         <v>4730</v>
       </c>
+      <c r="E2229" s="2"/>
       <c r="F2229" s="8">
         <v>16559</v>
       </c>
@@ -84122,6 +84600,7 @@
       <c r="D2230" s="12" t="s">
         <v>4732</v>
       </c>
+      <c r="E2230" s="2"/>
       <c r="F2230" s="8">
         <v>16061</v>
       </c>
@@ -84139,6 +84618,7 @@
       <c r="D2231" s="12" t="s">
         <v>4734</v>
       </c>
+      <c r="E2231" s="2"/>
       <c r="F2231" s="8">
         <v>10474</v>
       </c>
@@ -84156,6 +84636,7 @@
       <c r="D2232" s="12" t="s">
         <v>4736</v>
       </c>
+      <c r="E2232" s="2"/>
       <c r="F2232" s="8">
         <v>16560</v>
       </c>
@@ -84173,6 +84654,7 @@
       <c r="D2233" s="12" t="s">
         <v>4738</v>
       </c>
+      <c r="E2233" s="2"/>
       <c r="F2233" s="8">
         <v>15137</v>
       </c>
@@ -84190,6 +84672,7 @@
       <c r="D2234" s="12" t="s">
         <v>4740</v>
       </c>
+      <c r="E2234" s="2"/>
       <c r="F2234" s="8">
         <v>14825</v>
       </c>
@@ -84207,6 +84690,7 @@
       <c r="D2235" s="12" t="s">
         <v>4742</v>
       </c>
+      <c r="E2235" s="2"/>
       <c r="F2235" s="8">
         <v>10251</v>
       </c>
@@ -84224,6 +84708,7 @@
       <c r="D2236" s="12" t="s">
         <v>4744</v>
       </c>
+      <c r="E2236" s="2"/>
       <c r="F2236" s="8">
         <v>10430</v>
       </c>
@@ -84241,6 +84726,7 @@
       <c r="D2237" s="12" t="s">
         <v>4746</v>
       </c>
+      <c r="E2237" s="2"/>
       <c r="F2237" s="8">
         <v>10311</v>
       </c>
@@ -84258,6 +84744,7 @@
       <c r="D2238" s="12" t="s">
         <v>4748</v>
       </c>
+      <c r="E2238" s="2"/>
       <c r="F2238" s="8">
         <v>10266</v>
       </c>
@@ -84275,6 +84762,7 @@
       <c r="D2239" s="12" t="s">
         <v>4750</v>
       </c>
+      <c r="E2239" s="2"/>
       <c r="F2239" s="8">
         <v>14973</v>
       </c>
@@ -84292,6 +84780,7 @@
       <c r="D2240" s="12" t="s">
         <v>4753</v>
       </c>
+      <c r="E2240" s="2"/>
       <c r="F2240" s="8">
         <v>13321</v>
       </c>
@@ -84309,6 +84798,7 @@
       <c r="D2241" s="12" t="s">
         <v>4755</v>
       </c>
+      <c r="E2241" s="2"/>
       <c r="F2241" s="8">
         <v>12705</v>
       </c>
@@ -84326,6 +84816,7 @@
       <c r="D2242" s="12" t="s">
         <v>4757</v>
       </c>
+      <c r="E2242" s="2"/>
       <c r="F2242" s="8">
         <v>11495</v>
       </c>
@@ -84343,6 +84834,7 @@
       <c r="D2243" s="12" t="s">
         <v>4759</v>
       </c>
+      <c r="E2243" s="2"/>
       <c r="F2243" s="8">
         <v>11984</v>
       </c>
@@ -84360,6 +84852,7 @@
       <c r="D2244" s="12" t="s">
         <v>4761</v>
       </c>
+      <c r="E2244" s="2"/>
       <c r="F2244" s="8">
         <v>12054</v>
       </c>
@@ -84377,6 +84870,7 @@
       <c r="D2245" s="12" t="s">
         <v>4763</v>
       </c>
+      <c r="E2245" s="2"/>
       <c r="F2245" s="8">
         <v>12318</v>
       </c>
@@ -84394,6 +84888,7 @@
       <c r="D2246" s="12" t="s">
         <v>4765</v>
       </c>
+      <c r="E2246" s="2"/>
       <c r="F2246" s="8">
         <v>11435</v>
       </c>
@@ -84411,6 +84906,7 @@
       <c r="D2247" s="12" t="s">
         <v>4767</v>
       </c>
+      <c r="E2247" s="2"/>
       <c r="F2247" s="8">
         <v>12453</v>
       </c>
@@ -84428,6 +84924,7 @@
       <c r="D2248" s="12" t="s">
         <v>4770</v>
       </c>
+      <c r="E2248" s="2"/>
       <c r="F2248" s="8">
         <v>17615</v>
       </c>
@@ -84445,6 +84942,7 @@
       <c r="D2249" s="12" t="s">
         <v>4772</v>
       </c>
+      <c r="E2249" s="2"/>
       <c r="F2249" s="8">
         <v>13951</v>
       </c>
@@ -84462,6 +84960,7 @@
       <c r="D2250" s="12" t="s">
         <v>4774</v>
       </c>
+      <c r="E2250" s="2"/>
       <c r="F2250" s="8">
         <v>12777</v>
       </c>
@@ -84479,6 +84978,7 @@
       <c r="D2251" s="12" t="s">
         <v>4777</v>
       </c>
+      <c r="E2251" s="2"/>
       <c r="F2251" s="8">
         <v>18968</v>
       </c>
@@ -84496,6 +84996,7 @@
       <c r="D2252" s="12" t="s">
         <v>4779</v>
       </c>
+      <c r="E2252" s="2"/>
       <c r="F2252" s="8">
         <v>12855</v>
       </c>
@@ -84513,6 +85014,7 @@
       <c r="D2253" s="12" t="s">
         <v>4781</v>
       </c>
+      <c r="E2253" s="2"/>
       <c r="F2253" s="8">
         <v>14121</v>
       </c>
@@ -84530,6 +85032,7 @@
       <c r="D2254" s="12" t="s">
         <v>4783</v>
       </c>
+      <c r="E2254" s="2"/>
       <c r="F2254" s="8">
         <v>18181</v>
       </c>
@@ -84547,6 +85050,7 @@
       <c r="D2255" s="12" t="s">
         <v>4785</v>
       </c>
+      <c r="E2255" s="2"/>
       <c r="F2255" s="8">
         <v>11981</v>
       </c>
@@ -84564,6 +85068,7 @@
       <c r="D2256" s="12" t="s">
         <v>4787</v>
       </c>
+      <c r="E2256" s="2"/>
       <c r="F2256" s="8">
         <v>10969</v>
       </c>
@@ -84581,6 +85086,7 @@
       <c r="D2257" s="12" t="s">
         <v>4789</v>
       </c>
+      <c r="E2257" s="2"/>
       <c r="F2257" s="8">
         <v>12092</v>
       </c>
@@ -84598,6 +85104,7 @@
       <c r="D2258" s="12" t="s">
         <v>4791</v>
       </c>
+      <c r="E2258" s="2"/>
       <c r="F2258" s="8">
         <v>12203</v>
       </c>
@@ -84615,6 +85122,7 @@
       <c r="D2259" s="12" t="s">
         <v>4793</v>
       </c>
+      <c r="E2259" s="2"/>
       <c r="F2259" s="8">
         <v>11751</v>
       </c>
@@ -84632,6 +85140,7 @@
       <c r="D2260" s="12" t="s">
         <v>4795</v>
       </c>
+      <c r="E2260" s="2"/>
       <c r="F2260" s="8">
         <v>12733</v>
       </c>
@@ -84649,6 +85158,7 @@
       <c r="D2261" s="12" t="s">
         <v>4797</v>
       </c>
+      <c r="E2261" s="2"/>
       <c r="F2261" s="8">
         <v>10728</v>
       </c>
@@ -84666,6 +85176,7 @@
       <c r="D2262" s="12" t="s">
         <v>4799</v>
       </c>
+      <c r="E2262" s="2"/>
       <c r="F2262" s="8">
         <v>12457</v>
       </c>
@@ -84683,6 +85194,7 @@
       <c r="D2263" s="12" t="s">
         <v>4802</v>
       </c>
+      <c r="E2263" s="2"/>
       <c r="F2263" s="8">
         <v>13955</v>
       </c>
@@ -84700,6 +85212,7 @@
       <c r="D2264" s="12" t="s">
         <v>4804</v>
       </c>
+      <c r="E2264" s="2"/>
       <c r="F2264" s="8">
         <v>13618</v>
       </c>
@@ -84717,6 +85230,7 @@
       <c r="D2265" s="12" t="s">
         <v>4806</v>
       </c>
+      <c r="E2265" s="2"/>
       <c r="F2265" s="8">
         <v>10375</v>
       </c>
@@ -84734,6 +85248,7 @@
       <c r="D2266" s="12" t="s">
         <v>4808</v>
       </c>
+      <c r="E2266" s="2"/>
       <c r="F2266" s="8">
         <v>12679</v>
       </c>
@@ -84751,6 +85266,7 @@
       <c r="D2267" s="12" t="s">
         <v>4810</v>
       </c>
+      <c r="E2267" s="2"/>
       <c r="F2267" s="8">
         <v>11434</v>
       </c>
@@ -84768,6 +85284,7 @@
       <c r="D2268" s="12" t="s">
         <v>4813</v>
       </c>
+      <c r="E2268" s="2"/>
       <c r="F2268" s="8">
         <v>7973</v>
       </c>
@@ -84785,6 +85302,7 @@
       <c r="D2269" s="12" t="s">
         <v>4815</v>
       </c>
+      <c r="E2269" s="2"/>
       <c r="F2269" s="8">
         <v>7557</v>
       </c>
@@ -84802,6 +85320,7 @@
       <c r="D2270" s="12" t="s">
         <v>4817</v>
       </c>
+      <c r="E2270" s="2"/>
       <c r="F2270" s="8">
         <v>7681</v>
       </c>
@@ -84819,6 +85338,7 @@
       <c r="D2271" s="12" t="s">
         <v>4819</v>
       </c>
+      <c r="E2271" s="2"/>
       <c r="F2271" s="8">
         <v>7920</v>
       </c>
@@ -84836,6 +85356,7 @@
       <c r="D2272" s="12" t="s">
         <v>4822</v>
       </c>
+      <c r="E2272" s="2"/>
       <c r="F2272" s="8">
         <v>10139</v>
       </c>
@@ -84853,6 +85374,7 @@
       <c r="D2273" s="12" t="s">
         <v>4824</v>
       </c>
+      <c r="E2273" s="2"/>
       <c r="F2273" s="8">
         <v>10045</v>
       </c>
@@ -84870,6 +85392,7 @@
       <c r="D2274" s="12" t="s">
         <v>4826</v>
       </c>
+      <c r="E2274" s="2"/>
       <c r="F2274" s="8">
         <v>10076</v>
       </c>
@@ -84887,7 +85410,8 @@
       <c r="D2275" s="12" t="s">
         <v>4830</v>
       </c>
-      <c r="F2275" s="2"/>
+      <c r="E2275" s="2"/>
+      <c r="F2275" s="3"/>
     </row>
     <row r="2276" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2276" s="8" t="s">
@@ -84902,7 +85426,8 @@
       <c r="D2276" s="12" t="s">
         <v>4832</v>
       </c>
-      <c r="F2276" s="2"/>
+      <c r="E2276" s="2"/>
+      <c r="F2276" s="3"/>
     </row>
     <row r="2277" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2277" s="8" t="s">
@@ -84917,7 +85442,8 @@
       <c r="D2277" s="12" t="s">
         <v>4834</v>
       </c>
-      <c r="F2277" s="2"/>
+      <c r="E2277" s="2"/>
+      <c r="F2277" s="3"/>
     </row>
     <row r="2278" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2278" s="8" t="s">
@@ -84932,7 +85458,8 @@
       <c r="D2278" s="12" t="s">
         <v>4836</v>
       </c>
-      <c r="F2278" s="2"/>
+      <c r="E2278" s="2"/>
+      <c r="F2278" s="3"/>
     </row>
     <row r="2279" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2279" s="8" t="s">
@@ -84947,7 +85474,8 @@
       <c r="D2279" s="12" t="s">
         <v>4838</v>
       </c>
-      <c r="F2279" s="2"/>
+      <c r="E2279" s="2"/>
+      <c r="F2279" s="3"/>
     </row>
     <row r="2280" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2280" s="8" t="s">
@@ -84962,7 +85490,8 @@
       <c r="D2280" s="12" t="s">
         <v>4840</v>
       </c>
-      <c r="F2280" s="2"/>
+      <c r="E2280" s="2"/>
+      <c r="F2280" s="3"/>
     </row>
     <row r="2281" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2281" s="8" t="s">
@@ -84977,7 +85506,8 @@
       <c r="D2281" s="12" t="s">
         <v>4842</v>
       </c>
-      <c r="F2281" s="2"/>
+      <c r="E2281" s="2"/>
+      <c r="F2281" s="3"/>
     </row>
     <row r="2282" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2282" s="8" t="s">
@@ -84992,7 +85522,8 @@
       <c r="D2282" s="12" t="s">
         <v>4844</v>
       </c>
-      <c r="F2282" s="2"/>
+      <c r="E2282" s="2"/>
+      <c r="F2282" s="3"/>
     </row>
     <row r="2283" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2283" s="8" t="s">
@@ -85007,7 +85538,8 @@
       <c r="D2283" s="12" t="s">
         <v>4847</v>
       </c>
-      <c r="F2283" s="2"/>
+      <c r="E2283" s="2"/>
+      <c r="F2283" s="3"/>
     </row>
     <row r="2284" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2284" s="8" t="s">
@@ -85022,7 +85554,8 @@
       <c r="D2284" s="12" t="s">
         <v>4849</v>
       </c>
-      <c r="F2284" s="2"/>
+      <c r="E2284" s="2"/>
+      <c r="F2284" s="3"/>
     </row>
     <row r="2285" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2285" s="8" t="s">
@@ -85037,7 +85570,8 @@
       <c r="D2285" s="12" t="s">
         <v>4851</v>
       </c>
-      <c r="F2285" s="2"/>
+      <c r="E2285" s="2"/>
+      <c r="F2285" s="3"/>
     </row>
     <row r="2286" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2286" s="8" t="s">
@@ -85052,7 +85586,8 @@
       <c r="D2286" s="12" t="s">
         <v>4853</v>
       </c>
-      <c r="F2286" s="2"/>
+      <c r="E2286" s="2"/>
+      <c r="F2286" s="3"/>
     </row>
     <row r="2287" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2287" s="8" t="s">
@@ -85067,7 +85602,8 @@
       <c r="D2287" s="12" t="s">
         <v>4855</v>
       </c>
-      <c r="F2287" s="2"/>
+      <c r="E2287" s="2"/>
+      <c r="F2287" s="3"/>
     </row>
     <row r="2288" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2288" s="8" t="s">
@@ -85082,7 +85618,8 @@
       <c r="D2288" s="12" t="s">
         <v>4857</v>
       </c>
-      <c r="F2288" s="2"/>
+      <c r="E2288" s="2"/>
+      <c r="F2288" s="3"/>
     </row>
     <row r="2289" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2289" s="8" t="s">
@@ -85097,7 +85634,8 @@
       <c r="D2289" s="12" t="s">
         <v>4859</v>
       </c>
-      <c r="F2289" s="2"/>
+      <c r="E2289" s="2"/>
+      <c r="F2289" s="3"/>
     </row>
     <row r="2290" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2290" s="8" t="s">
@@ -85112,7 +85650,8 @@
       <c r="D2290" s="12" t="s">
         <v>4861</v>
       </c>
-      <c r="F2290" s="2"/>
+      <c r="E2290" s="2"/>
+      <c r="F2290" s="3"/>
     </row>
     <row r="2291" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2291" s="8" t="s">
@@ -85127,7 +85666,8 @@
       <c r="D2291" s="12" t="s">
         <v>4863</v>
       </c>
-      <c r="F2291" s="2"/>
+      <c r="E2291" s="2"/>
+      <c r="F2291" s="3"/>
     </row>
     <row r="2292" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2292" s="8" t="s">
@@ -85142,7 +85682,8 @@
       <c r="D2292" s="12" t="s">
         <v>4865</v>
       </c>
-      <c r="F2292" s="2"/>
+      <c r="E2292" s="2"/>
+      <c r="F2292" s="3"/>
     </row>
     <row r="2293" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2293" s="8" t="s">
@@ -85157,7 +85698,8 @@
       <c r="D2293" s="12" t="s">
         <v>4867</v>
       </c>
-      <c r="F2293" s="2"/>
+      <c r="E2293" s="2"/>
+      <c r="F2293" s="3"/>
     </row>
     <row r="2294" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2294" s="8" t="s">
@@ -85172,7 +85714,8 @@
       <c r="D2294" s="12" t="s">
         <v>4869</v>
       </c>
-      <c r="F2294" s="2"/>
+      <c r="E2294" s="2"/>
+      <c r="F2294" s="3"/>
     </row>
     <row r="2295" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2295" s="8" t="s">
@@ -85187,7 +85730,8 @@
       <c r="D2295" s="12" t="s">
         <v>4871</v>
       </c>
-      <c r="F2295" s="2"/>
+      <c r="E2295" s="2"/>
+      <c r="F2295" s="3"/>
     </row>
     <row r="2296" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2296" s="8" t="s">
@@ -85202,7 +85746,8 @@
       <c r="D2296" s="12" t="s">
         <v>4873</v>
       </c>
-      <c r="F2296" s="2"/>
+      <c r="E2296" s="2"/>
+      <c r="F2296" s="3"/>
     </row>
     <row r="2297" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2297" s="8" t="s">
@@ -85217,7 +85762,8 @@
       <c r="D2297" s="12" t="s">
         <v>4875</v>
       </c>
-      <c r="F2297" s="2"/>
+      <c r="E2297" s="2"/>
+      <c r="F2297" s="3"/>
     </row>
     <row r="2298" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2298" s="8" t="s">
@@ -85232,7 +85778,8 @@
       <c r="D2298" s="12" t="s">
         <v>4877</v>
       </c>
-      <c r="F2298" s="2"/>
+      <c r="E2298" s="2"/>
+      <c r="F2298" s="3"/>
     </row>
     <row r="2299" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2299" s="8" t="s">
@@ -85247,7 +85794,8 @@
       <c r="D2299" s="12" t="s">
         <v>4879</v>
       </c>
-      <c r="F2299" s="2"/>
+      <c r="E2299" s="2"/>
+      <c r="F2299" s="3"/>
     </row>
     <row r="2300" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2300" s="8" t="s">
@@ -85262,7 +85810,8 @@
       <c r="D2300" s="12" t="s">
         <v>4881</v>
       </c>
-      <c r="F2300" s="2"/>
+      <c r="E2300" s="2"/>
+      <c r="F2300" s="3"/>
     </row>
     <row r="2301" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2301" s="8" t="s">
@@ -85277,7 +85826,8 @@
       <c r="D2301" s="12" t="s">
         <v>4884</v>
       </c>
-      <c r="F2301" s="2"/>
+      <c r="E2301" s="2"/>
+      <c r="F2301" s="3"/>
     </row>
     <row r="2302" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2302" s="8" t="s">
@@ -85292,7 +85842,8 @@
       <c r="D2302" s="12" t="s">
         <v>4886</v>
       </c>
-      <c r="F2302" s="2"/>
+      <c r="E2302" s="2"/>
+      <c r="F2302" s="3"/>
     </row>
     <row r="2303" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2303" s="8" t="s">
@@ -85307,7 +85858,8 @@
       <c r="D2303" s="12" t="s">
         <v>4888</v>
       </c>
-      <c r="F2303" s="2"/>
+      <c r="E2303" s="2"/>
+      <c r="F2303" s="3"/>
     </row>
     <row r="2304" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2304" s="8" t="s">
@@ -85322,7 +85874,8 @@
       <c r="D2304" s="12" t="s">
         <v>4890</v>
       </c>
-      <c r="F2304" s="2"/>
+      <c r="E2304" s="2"/>
+      <c r="F2304" s="3"/>
     </row>
     <row r="2305" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2305" s="8" t="s">
@@ -85337,7 +85890,8 @@
       <c r="D2305" s="12" t="s">
         <v>4892</v>
       </c>
-      <c r="F2305" s="2"/>
+      <c r="E2305" s="2"/>
+      <c r="F2305" s="3"/>
     </row>
     <row r="2306" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2306" s="8" t="s">
@@ -85352,7 +85906,8 @@
       <c r="D2306" s="12" t="s">
         <v>4894</v>
       </c>
-      <c r="F2306" s="2"/>
+      <c r="E2306" s="2"/>
+      <c r="F2306" s="3"/>
     </row>
     <row r="2307" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2307" s="8" t="s">
@@ -85367,7 +85922,8 @@
       <c r="D2307" s="12" t="s">
         <v>4896</v>
       </c>
-      <c r="F2307" s="2"/>
+      <c r="E2307" s="2"/>
+      <c r="F2307" s="3"/>
     </row>
     <row r="2308" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2308" s="8" t="s">
@@ -85382,7 +85938,8 @@
       <c r="D2308" s="12" t="s">
         <v>4898</v>
       </c>
-      <c r="F2308" s="2"/>
+      <c r="E2308" s="2"/>
+      <c r="F2308" s="3"/>
     </row>
     <row r="2309" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2309" s="8" t="s">
@@ -85397,7 +85954,8 @@
       <c r="D2309" s="12" t="s">
         <v>4900</v>
       </c>
-      <c r="F2309" s="2"/>
+      <c r="E2309" s="2"/>
+      <c r="F2309" s="3"/>
     </row>
     <row r="2310" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2310" s="8" t="s">
@@ -85412,7 +85970,8 @@
       <c r="D2310" s="12" t="s">
         <v>4902</v>
       </c>
-      <c r="F2310" s="2"/>
+      <c r="E2310" s="2"/>
+      <c r="F2310" s="3"/>
     </row>
     <row r="2311" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2311" s="8" t="s">
@@ -85427,7 +85986,8 @@
       <c r="D2311" s="12" t="s">
         <v>4904</v>
       </c>
-      <c r="F2311" s="2"/>
+      <c r="E2311" s="2"/>
+      <c r="F2311" s="3"/>
     </row>
     <row r="2312" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2312" s="8" t="s">
@@ -85442,7 +86002,8 @@
       <c r="D2312" s="12" t="s">
         <v>4907</v>
       </c>
-      <c r="F2312" s="2"/>
+      <c r="E2312" s="2"/>
+      <c r="F2312" s="3"/>
     </row>
     <row r="2313" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2313" s="8" t="s">
@@ -85457,7 +86018,8 @@
       <c r="D2313" s="12" t="s">
         <v>4909</v>
       </c>
-      <c r="F2313" s="2"/>
+      <c r="E2313" s="2"/>
+      <c r="F2313" s="3"/>
     </row>
     <row r="2314" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2314" s="8" t="s">
@@ -85472,7 +86034,8 @@
       <c r="D2314" s="12" t="s">
         <v>4911</v>
       </c>
-      <c r="F2314" s="2"/>
+      <c r="E2314" s="2"/>
+      <c r="F2314" s="3"/>
     </row>
     <row r="2315" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2315" s="8" t="s">
@@ -85487,7 +86050,8 @@
       <c r="D2315" s="12" t="s">
         <v>4913</v>
       </c>
-      <c r="F2315" s="2"/>
+      <c r="E2315" s="2"/>
+      <c r="F2315" s="3"/>
     </row>
     <row r="2316" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2316" s="8" t="s">
@@ -85502,7 +86066,8 @@
       <c r="D2316" s="12" t="s">
         <v>4915</v>
       </c>
-      <c r="F2316" s="2"/>
+      <c r="E2316" s="2"/>
+      <c r="F2316" s="3"/>
     </row>
     <row r="2317" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2317" s="8" t="s">
@@ -85517,7 +86082,8 @@
       <c r="D2317" s="12" t="s">
         <v>4917</v>
       </c>
-      <c r="F2317" s="2"/>
+      <c r="E2317" s="2"/>
+      <c r="F2317" s="3"/>
     </row>
     <row r="2318" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2318" s="8" t="s">
@@ -85532,7 +86098,8 @@
       <c r="D2318" s="12" t="s">
         <v>4919</v>
       </c>
-      <c r="F2318" s="2"/>
+      <c r="E2318" s="2"/>
+      <c r="F2318" s="3"/>
     </row>
     <row r="2319" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2319" s="8" t="s">
@@ -85547,7 +86114,8 @@
       <c r="D2319" s="12" t="s">
         <v>4922</v>
       </c>
-      <c r="F2319" s="2"/>
+      <c r="E2319" s="2"/>
+      <c r="F2319" s="3"/>
     </row>
     <row r="2320" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2320" s="8" t="s">
@@ -85562,7 +86130,8 @@
       <c r="D2320" s="12" t="s">
         <v>4924</v>
       </c>
-      <c r="F2320" s="2"/>
+      <c r="E2320" s="2"/>
+      <c r="F2320" s="3"/>
     </row>
     <row r="2321" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2321" s="8" t="s">
@@ -85577,7 +86146,8 @@
       <c r="D2321" s="12" t="s">
         <v>4926</v>
       </c>
-      <c r="F2321" s="2"/>
+      <c r="E2321" s="2"/>
+      <c r="F2321" s="3"/>
     </row>
     <row r="2322" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2322" s="8" t="s">
@@ -85592,7 +86162,8 @@
       <c r="D2322" s="12" t="s">
         <v>4928</v>
       </c>
-      <c r="F2322" s="2"/>
+      <c r="E2322" s="2"/>
+      <c r="F2322" s="3"/>
     </row>
     <row r="2323" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2323" s="8" t="s">
@@ -85607,7 +86178,8 @@
       <c r="D2323" s="12" t="s">
         <v>4930</v>
       </c>
-      <c r="F2323" s="2"/>
+      <c r="E2323" s="2"/>
+      <c r="F2323" s="3"/>
     </row>
     <row r="2324" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2324" s="8" t="s">
@@ -85622,7 +86194,8 @@
       <c r="D2324" s="12" t="s">
         <v>4932</v>
       </c>
-      <c r="F2324" s="2"/>
+      <c r="E2324" s="2"/>
+      <c r="F2324" s="3"/>
     </row>
     <row r="2325" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2325" s="8" t="s">
@@ -85637,7 +86210,8 @@
       <c r="D2325" s="12" t="s">
         <v>4934</v>
       </c>
-      <c r="F2325" s="2"/>
+      <c r="E2325" s="2"/>
+      <c r="F2325" s="3"/>
     </row>
     <row r="2326" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2326" s="8" t="s">
@@ -85652,7 +86226,8 @@
       <c r="D2326" s="12" t="s">
         <v>4936</v>
       </c>
-      <c r="F2326" s="2"/>
+      <c r="E2326" s="2"/>
+      <c r="F2326" s="3"/>
     </row>
     <row r="2327" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2327" s="8" t="s">
@@ -85667,7 +86242,8 @@
       <c r="D2327" s="12" t="s">
         <v>4938</v>
       </c>
-      <c r="F2327" s="2"/>
+      <c r="E2327" s="2"/>
+      <c r="F2327" s="3"/>
     </row>
     <row r="2328" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2328" s="8" t="s">
@@ -85682,7 +86258,8 @@
       <c r="D2328" s="12" t="s">
         <v>4940</v>
       </c>
-      <c r="F2328" s="2"/>
+      <c r="E2328" s="2"/>
+      <c r="F2328" s="3"/>
     </row>
     <row r="2329" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2329" s="8" t="s">
@@ -85697,7 +86274,8 @@
       <c r="D2329" s="12" t="s">
         <v>4942</v>
       </c>
-      <c r="F2329" s="2"/>
+      <c r="E2329" s="2"/>
+      <c r="F2329" s="3"/>
     </row>
     <row r="2330" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2330" s="8" t="s">
@@ -85712,7 +86290,8 @@
       <c r="D2330" s="12" t="s">
         <v>4944</v>
       </c>
-      <c r="F2330" s="2"/>
+      <c r="E2330" s="2"/>
+      <c r="F2330" s="3"/>
     </row>
     <row r="2331" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2331" s="8" t="s">
@@ -85727,7 +86306,8 @@
       <c r="D2331" s="12" t="s">
         <v>4947</v>
       </c>
-      <c r="F2331" s="2"/>
+      <c r="E2331" s="2"/>
+      <c r="F2331" s="3"/>
     </row>
     <row r="2332" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2332" s="8" t="s">
@@ -85742,7 +86322,8 @@
       <c r="D2332" s="12" t="s">
         <v>4949</v>
       </c>
-      <c r="F2332" s="2"/>
+      <c r="E2332" s="2"/>
+      <c r="F2332" s="3"/>
     </row>
     <row r="2333" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2333" s="8" t="s">
@@ -85757,7 +86338,8 @@
       <c r="D2333" s="12" t="s">
         <v>4951</v>
       </c>
-      <c r="F2333" s="2"/>
+      <c r="E2333" s="2"/>
+      <c r="F2333" s="3"/>
     </row>
     <row r="2334" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2334" s="8" t="s">
@@ -85772,7 +86354,8 @@
       <c r="D2334" s="12" t="s">
         <v>4953</v>
       </c>
-      <c r="F2334" s="2"/>
+      <c r="E2334" s="2"/>
+      <c r="F2334" s="3"/>
     </row>
     <row r="2335" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2335" s="8" t="s">
@@ -85787,7 +86370,8 @@
       <c r="D2335" s="12" t="s">
         <v>4955</v>
       </c>
-      <c r="F2335" s="2"/>
+      <c r="E2335" s="2"/>
+      <c r="F2335" s="3"/>
     </row>
     <row r="2336" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2336" s="8" t="s">
@@ -85802,7 +86386,8 @@
       <c r="D2336" s="12" t="s">
         <v>4957</v>
       </c>
-      <c r="F2336" s="2"/>
+      <c r="E2336" s="2"/>
+      <c r="F2336" s="3"/>
     </row>
     <row r="2337" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2337" s="8" t="s">
@@ -85817,7 +86402,8 @@
       <c r="D2337" s="12" t="s">
         <v>4959</v>
       </c>
-      <c r="F2337" s="2"/>
+      <c r="E2337" s="2"/>
+      <c r="F2337" s="3"/>
     </row>
     <row r="2338" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2338" s="8" t="s">
@@ -85832,7 +86418,8 @@
       <c r="D2338" s="12" t="s">
         <v>4961</v>
       </c>
-      <c r="F2338" s="2"/>
+      <c r="E2338" s="2"/>
+      <c r="F2338" s="3"/>
     </row>
     <row r="2339" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2339" s="8" t="s">
@@ -85847,7 +86434,8 @@
       <c r="D2339" s="12" t="s">
         <v>4963</v>
       </c>
-      <c r="F2339" s="2"/>
+      <c r="E2339" s="2"/>
+      <c r="F2339" s="3"/>
     </row>
     <row r="2340" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2340" s="8" t="s">
@@ -85862,7 +86450,8 @@
       <c r="D2340" s="12" t="s">
         <v>4965</v>
       </c>
-      <c r="F2340" s="2"/>
+      <c r="E2340" s="2"/>
+      <c r="F2340" s="3"/>
     </row>
     <row r="2341" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2341" s="8" t="s">
@@ -85877,7 +86466,8 @@
       <c r="D2341" s="12" t="s">
         <v>4967</v>
       </c>
-      <c r="F2341" s="2"/>
+      <c r="E2341" s="2"/>
+      <c r="F2341" s="3"/>
     </row>
     <row r="2342" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2342" s="8" t="s">
@@ -85892,7 +86482,8 @@
       <c r="D2342" s="12" t="s">
         <v>4970</v>
       </c>
-      <c r="F2342" s="2"/>
+      <c r="E2342" s="2"/>
+      <c r="F2342" s="3"/>
     </row>
     <row r="2343" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2343" s="8" t="s">
@@ -85907,7 +86498,8 @@
       <c r="D2343" s="12" t="s">
         <v>4972</v>
       </c>
-      <c r="F2343" s="2"/>
+      <c r="E2343" s="2"/>
+      <c r="F2343" s="3"/>
     </row>
     <row r="2344" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2344" s="8" t="s">
@@ -85922,7 +86514,8 @@
       <c r="D2344" s="12" t="s">
         <v>4974</v>
       </c>
-      <c r="F2344" s="2"/>
+      <c r="E2344" s="2"/>
+      <c r="F2344" s="3"/>
     </row>
     <row r="2345" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2345" s="8" t="s">
@@ -85937,7 +86530,8 @@
       <c r="D2345" s="12" t="s">
         <v>4976</v>
       </c>
-      <c r="F2345" s="2"/>
+      <c r="E2345" s="2"/>
+      <c r="F2345" s="3"/>
     </row>
     <row r="2346" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2346" s="8" t="s">
@@ -85952,7 +86546,8 @@
       <c r="D2346" s="12" t="s">
         <v>4978</v>
       </c>
-      <c r="F2346" s="2"/>
+      <c r="E2346" s="2"/>
+      <c r="F2346" s="3"/>
     </row>
     <row r="2347" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2347" s="8" t="s">
@@ -85967,7 +86562,8 @@
       <c r="D2347" s="12" t="s">
         <v>4980</v>
       </c>
-      <c r="F2347" s="2"/>
+      <c r="E2347" s="2"/>
+      <c r="F2347" s="3"/>
     </row>
     <row r="2348" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2348" s="8" t="s">
@@ -85982,7 +86578,8 @@
       <c r="D2348" s="12" t="s">
         <v>4982</v>
       </c>
-      <c r="F2348" s="2"/>
+      <c r="E2348" s="2"/>
+      <c r="F2348" s="3"/>
     </row>
     <row r="2349" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2349" s="7" t="s">
@@ -85997,7 +86594,8 @@
       <c r="D2349" s="12" t="s">
         <v>4985</v>
       </c>
-      <c r="F2349" s="2"/>
+      <c r="E2349" s="2"/>
+      <c r="F2349" s="3"/>
     </row>
     <row r="2350" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2350" s="8" t="s">
@@ -86012,7 +86610,8 @@
       <c r="D2350" s="12" t="s">
         <v>4988</v>
       </c>
-      <c r="F2350" s="2"/>
+      <c r="E2350" s="2"/>
+      <c r="F2350" s="3"/>
     </row>
     <row r="2351" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2351" s="8" t="s">
@@ -86027,7 +86626,8 @@
       <c r="D2351" s="12" t="s">
         <v>4990</v>
       </c>
-      <c r="F2351" s="2"/>
+      <c r="E2351" s="2"/>
+      <c r="F2351" s="3"/>
     </row>
     <row r="2352" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2352" s="8" t="s">
@@ -86042,7 +86642,8 @@
       <c r="D2352" s="12" t="s">
         <v>4992</v>
       </c>
-      <c r="F2352" s="2">
+      <c r="E2352" s="2"/>
+      <c r="F2352" s="3">
         <v>19353</v>
       </c>
     </row>
@@ -86059,7 +86660,8 @@
       <c r="D2353" s="12" t="s">
         <v>4994</v>
       </c>
-      <c r="F2353" s="2"/>
+      <c r="E2353" s="2"/>
+      <c r="F2353" s="3"/>
     </row>
     <row r="2354" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2354" s="8" t="s">
@@ -86074,7 +86676,8 @@
       <c r="D2354" s="12" t="s">
         <v>4996</v>
       </c>
-      <c r="F2354" s="2"/>
+      <c r="E2354" s="2"/>
+      <c r="F2354" s="3"/>
     </row>
     <row r="2355" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2355" s="8" t="s">
@@ -86089,7 +86692,8 @@
       <c r="D2355" s="12" t="s">
         <v>4998</v>
       </c>
-      <c r="F2355" s="2">
+      <c r="E2355" s="2"/>
+      <c r="F2355" s="3">
         <v>17104</v>
       </c>
     </row>
@@ -86106,7 +86710,8 @@
       <c r="D2356" s="12" t="s">
         <v>5000</v>
       </c>
-      <c r="F2356" s="2">
+      <c r="E2356" s="2"/>
+      <c r="F2356" s="3">
         <v>15802</v>
       </c>
     </row>
@@ -86123,7 +86728,8 @@
       <c r="D2357" s="12" t="s">
         <v>5001</v>
       </c>
-      <c r="F2357" s="2">
+      <c r="E2357" s="2"/>
+      <c r="F2357" s="3">
         <v>17186</v>
       </c>
     </row>
@@ -86140,7 +86746,8 @@
       <c r="D2358" s="12" t="s">
         <v>5003</v>
       </c>
-      <c r="F2358" s="2">
+      <c r="E2358" s="2"/>
+      <c r="F2358" s="3">
         <v>17696</v>
       </c>
     </row>
@@ -86157,7 +86764,8 @@
       <c r="D2359" s="12" t="s">
         <v>5005</v>
       </c>
-      <c r="F2359" s="2">
+      <c r="E2359" s="2"/>
+      <c r="F2359" s="3">
         <v>14723</v>
       </c>
     </row>
@@ -86174,7 +86782,8 @@
       <c r="D2360" s="12" t="s">
         <v>5007</v>
       </c>
-      <c r="F2360" s="2">
+      <c r="E2360" s="2"/>
+      <c r="F2360" s="3">
         <v>15851</v>
       </c>
     </row>
@@ -86191,7 +86800,8 @@
       <c r="D2361" s="12" t="s">
         <v>5009</v>
       </c>
-      <c r="F2361" s="2">
+      <c r="E2361" s="2"/>
+      <c r="F2361" s="3">
         <v>14162</v>
       </c>
     </row>
@@ -86208,7 +86818,8 @@
       <c r="D2362" s="12" t="s">
         <v>5012</v>
       </c>
-      <c r="F2362" s="2"/>
+      <c r="E2362" s="2"/>
+      <c r="F2362" s="3"/>
     </row>
     <row r="2363" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2363" s="8" t="s">
@@ -86223,7 +86834,8 @@
       <c r="D2363" s="12" t="s">
         <v>5014</v>
       </c>
-      <c r="F2363" s="2"/>
+      <c r="E2363" s="2"/>
+      <c r="F2363" s="3"/>
     </row>
     <row r="2364" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2364" s="8" t="s">
@@ -86238,7 +86850,8 @@
       <c r="D2364" s="12" t="s">
         <v>5016</v>
       </c>
-      <c r="F2364" s="2"/>
+      <c r="E2364" s="2"/>
+      <c r="F2364" s="3"/>
     </row>
     <row r="2365" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2365" s="8" t="s">
@@ -86253,7 +86866,8 @@
       <c r="D2365" s="12" t="s">
         <v>5018</v>
       </c>
-      <c r="F2365" s="2"/>
+      <c r="E2365" s="2"/>
+      <c r="F2365" s="3"/>
     </row>
     <row r="2366" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2366" s="8" t="s">
@@ -86268,7 +86882,8 @@
       <c r="D2366" s="12" t="s">
         <v>5021</v>
       </c>
-      <c r="F2366" s="2"/>
+      <c r="E2366" s="2"/>
+      <c r="F2366" s="3"/>
     </row>
     <row r="2367" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2367" s="8" t="s">
@@ -86283,7 +86898,8 @@
       <c r="D2367" s="12" t="s">
         <v>5023</v>
       </c>
-      <c r="F2367" s="2"/>
+      <c r="E2367" s="2"/>
+      <c r="F2367" s="3"/>
     </row>
     <row r="2368" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2368" s="8" t="s">
@@ -86298,7 +86914,8 @@
       <c r="D2368" s="12" t="s">
         <v>5025</v>
       </c>
-      <c r="F2368" s="2"/>
+      <c r="E2368" s="2"/>
+      <c r="F2368" s="3"/>
     </row>
     <row r="2369" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2369" s="8" t="s">
@@ -86313,7 +86930,8 @@
       <c r="D2369" s="12" t="s">
         <v>5027</v>
       </c>
-      <c r="F2369" s="2"/>
+      <c r="E2369" s="2"/>
+      <c r="F2369" s="3"/>
     </row>
     <row r="2370" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2370" s="8" t="s">
@@ -86328,7 +86946,8 @@
       <c r="D2370" s="12" t="s">
         <v>5029</v>
       </c>
-      <c r="F2370" s="2"/>
+      <c r="E2370" s="2"/>
+      <c r="F2370" s="3"/>
     </row>
     <row r="2371" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2371" s="8" t="s">
@@ -86343,7 +86962,8 @@
       <c r="D2371" s="12" t="s">
         <v>5031</v>
       </c>
-      <c r="F2371" s="2"/>
+      <c r="E2371" s="2"/>
+      <c r="F2371" s="3"/>
     </row>
     <row r="2372" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2372" s="8" t="s">
@@ -86358,7 +86978,8 @@
       <c r="D2372" s="12" t="s">
         <v>5033</v>
       </c>
-      <c r="F2372" s="2"/>
+      <c r="E2372" s="2"/>
+      <c r="F2372" s="3"/>
     </row>
     <row r="2373" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2373" s="8" t="s">
@@ -86373,7 +86994,8 @@
       <c r="D2373" s="12" t="s">
         <v>5035</v>
       </c>
-      <c r="F2373" s="2"/>
+      <c r="E2373" s="2"/>
+      <c r="F2373" s="3"/>
     </row>
     <row r="2374" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2374" s="8" t="s">
@@ -86388,7 +87010,8 @@
       <c r="D2374" s="12" t="s">
         <v>5037</v>
       </c>
-      <c r="F2374" s="2"/>
+      <c r="E2374" s="2"/>
+      <c r="F2374" s="3"/>
     </row>
     <row r="2375" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2375" s="8" t="s">
@@ -86403,7 +87026,8 @@
       <c r="D2375" s="12" t="s">
         <v>5039</v>
       </c>
-      <c r="F2375" s="2"/>
+      <c r="E2375" s="2"/>
+      <c r="F2375" s="3"/>
     </row>
     <row r="2376" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2376" s="8" t="s">
@@ -86418,7 +87042,8 @@
       <c r="D2376" s="12" t="s">
         <v>5041</v>
       </c>
-      <c r="F2376" s="2"/>
+      <c r="E2376" s="2"/>
+      <c r="F2376" s="3"/>
     </row>
     <row r="2377" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2377" s="8" t="s">
@@ -86433,7 +87058,8 @@
       <c r="D2377" s="12" t="s">
         <v>5043</v>
       </c>
-      <c r="F2377" s="2"/>
+      <c r="E2377" s="2"/>
+      <c r="F2377" s="3"/>
     </row>
     <row r="2378" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2378" s="8" t="s">
@@ -86448,7 +87074,8 @@
       <c r="D2378" s="12" t="s">
         <v>5046</v>
       </c>
-      <c r="F2378" s="2"/>
+      <c r="E2378" s="2"/>
+      <c r="F2378" s="3"/>
     </row>
     <row r="2379" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2379" s="8" t="s">
@@ -86463,7 +87090,8 @@
       <c r="D2379" s="12" t="s">
         <v>5048</v>
       </c>
-      <c r="F2379" s="2"/>
+      <c r="E2379" s="2"/>
+      <c r="F2379" s="3"/>
     </row>
     <row r="2380" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2380" s="8" t="s">
@@ -86478,7 +87106,8 @@
       <c r="D2380" s="12" t="s">
         <v>5050</v>
       </c>
-      <c r="F2380" s="2"/>
+      <c r="E2380" s="2"/>
+      <c r="F2380" s="3"/>
     </row>
     <row r="2381" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2381" s="8" t="s">
@@ -86493,7 +87122,8 @@
       <c r="D2381" s="12" t="s">
         <v>5052</v>
       </c>
-      <c r="F2381" s="2"/>
+      <c r="E2381" s="2"/>
+      <c r="F2381" s="3"/>
     </row>
     <row r="2382" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2382" s="8" t="s">
@@ -86508,7 +87138,8 @@
       <c r="D2382" s="12" t="s">
         <v>5054</v>
       </c>
-      <c r="F2382" s="2"/>
+      <c r="E2382" s="2"/>
+      <c r="F2382" s="3"/>
     </row>
     <row r="2383" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2383" s="8" t="s">
@@ -86523,7 +87154,8 @@
       <c r="D2383" s="12" t="s">
         <v>5056</v>
       </c>
-      <c r="F2383" s="2"/>
+      <c r="E2383" s="2"/>
+      <c r="F2383" s="3"/>
     </row>
     <row r="2384" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2384" s="8" t="s">
@@ -86538,7 +87170,8 @@
       <c r="D2384" s="12" t="s">
         <v>5058</v>
       </c>
-      <c r="F2384" s="2"/>
+      <c r="E2384" s="2"/>
+      <c r="F2384" s="3"/>
     </row>
     <row r="2385" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2385" s="8" t="s">
@@ -86553,7 +87186,8 @@
       <c r="D2385" s="12" t="s">
         <v>5060</v>
       </c>
-      <c r="F2385" s="2"/>
+      <c r="E2385" s="2"/>
+      <c r="F2385" s="3"/>
     </row>
     <row r="2386" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2386" s="8" t="s">
@@ -86568,7 +87202,8 @@
       <c r="D2386" s="12" t="s">
         <v>5062</v>
       </c>
-      <c r="F2386" s="2"/>
+      <c r="E2386" s="2"/>
+      <c r="F2386" s="3"/>
     </row>
     <row r="2387" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2387" s="8" t="s">
@@ -86583,7 +87218,8 @@
       <c r="D2387" s="12" t="s">
         <v>5064</v>
       </c>
-      <c r="F2387" s="2"/>
+      <c r="E2387" s="2"/>
+      <c r="F2387" s="3"/>
     </row>
     <row r="2388" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2388" s="8" t="s">
@@ -86598,7 +87234,8 @@
       <c r="D2388" s="12" t="s">
         <v>5066</v>
       </c>
-      <c r="F2388" s="2"/>
+      <c r="E2388" s="2"/>
+      <c r="F2388" s="3"/>
     </row>
     <row r="2389" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2389" s="8" t="s">
@@ -86613,7 +87250,8 @@
       <c r="D2389" s="12" t="s">
         <v>5068</v>
       </c>
-      <c r="F2389" s="2"/>
+      <c r="E2389" s="2"/>
+      <c r="F2389" s="3"/>
     </row>
     <row r="2390" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2390" s="8" t="s">
@@ -86628,7 +87266,8 @@
       <c r="D2390" s="12" t="s">
         <v>5070</v>
       </c>
-      <c r="F2390" s="2"/>
+      <c r="E2390" s="2"/>
+      <c r="F2390" s="3"/>
     </row>
     <row r="2391" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2391" s="8" t="s">
@@ -86643,7 +87282,8 @@
       <c r="D2391" s="12" t="s">
         <v>5072</v>
       </c>
-      <c r="F2391" s="2"/>
+      <c r="E2391" s="2"/>
+      <c r="F2391" s="3"/>
     </row>
     <row r="2392" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2392" s="8" t="s">
@@ -86658,7 +87298,8 @@
       <c r="D2392" s="12" t="s">
         <v>5075</v>
       </c>
-      <c r="F2392" s="2"/>
+      <c r="E2392" s="2"/>
+      <c r="F2392" s="3"/>
     </row>
     <row r="2393" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2393" s="8" t="s">
@@ -86673,7 +87314,8 @@
       <c r="D2393" s="12" t="s">
         <v>5077</v>
       </c>
-      <c r="F2393" s="2"/>
+      <c r="E2393" s="2"/>
+      <c r="F2393" s="3"/>
     </row>
     <row r="2394" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2394" s="8" t="s">
@@ -86688,7 +87330,8 @@
       <c r="D2394" s="12" t="s">
         <v>5079</v>
       </c>
-      <c r="F2394" s="2"/>
+      <c r="E2394" s="2"/>
+      <c r="F2394" s="3"/>
     </row>
     <row r="2395" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2395" s="8" t="s">
@@ -86703,7 +87346,8 @@
       <c r="D2395" s="12" t="s">
         <v>5081</v>
       </c>
-      <c r="F2395" s="2"/>
+      <c r="E2395" s="2"/>
+      <c r="F2395" s="3"/>
     </row>
     <row r="2396" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2396" s="8" t="s">
@@ -86718,7 +87362,8 @@
       <c r="D2396" s="12" t="s">
         <v>5083</v>
       </c>
-      <c r="F2396" s="2"/>
+      <c r="E2396" s="2"/>
+      <c r="F2396" s="3"/>
     </row>
     <row r="2397" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2397" s="8" t="s">
@@ -86733,7 +87378,8 @@
       <c r="D2397" s="12" t="s">
         <v>5085</v>
       </c>
-      <c r="F2397" s="2"/>
+      <c r="E2397" s="2"/>
+      <c r="F2397" s="3"/>
     </row>
     <row r="2398" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2398" s="8" t="s">
@@ -86748,7 +87394,8 @@
       <c r="D2398" s="12" t="s">
         <v>5087</v>
       </c>
-      <c r="F2398" s="2"/>
+      <c r="E2398" s="2"/>
+      <c r="F2398" s="3"/>
     </row>
     <row r="2399" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2399" s="8" t="s">
@@ -86763,7 +87410,8 @@
       <c r="D2399" s="12" t="s">
         <v>5089</v>
       </c>
-      <c r="F2399" s="2"/>
+      <c r="E2399" s="2"/>
+      <c r="F2399" s="3"/>
     </row>
     <row r="2400" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2400" s="8" t="s">
@@ -86778,7 +87426,8 @@
       <c r="D2400" s="12" t="s">
         <v>5091</v>
       </c>
-      <c r="F2400" s="2"/>
+      <c r="E2400" s="2"/>
+      <c r="F2400" s="3"/>
     </row>
     <row r="2401" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2401" s="8" t="s">
@@ -86793,7 +87442,8 @@
       <c r="D2401" s="12" t="s">
         <v>5093</v>
       </c>
-      <c r="F2401" s="2"/>
+      <c r="E2401" s="2"/>
+      <c r="F2401" s="3"/>
     </row>
     <row r="2402" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2402" s="8" t="s">
@@ -86808,7 +87458,8 @@
       <c r="D2402" s="12" t="s">
         <v>5095</v>
       </c>
-      <c r="F2402" s="2"/>
+      <c r="E2402" s="2"/>
+      <c r="F2402" s="3"/>
     </row>
     <row r="2403" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2403" s="8" t="s">
@@ -86823,7 +87474,8 @@
       <c r="D2403" s="12" t="s">
         <v>5098</v>
       </c>
-      <c r="F2403" s="2"/>
+      <c r="E2403" s="2"/>
+      <c r="F2403" s="3"/>
     </row>
     <row r="2404" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2404" s="8" t="s">
@@ -86838,7 +87490,8 @@
       <c r="D2404" s="12" t="s">
         <v>5100</v>
       </c>
-      <c r="F2404" s="2"/>
+      <c r="E2404" s="2"/>
+      <c r="F2404" s="3"/>
     </row>
     <row r="2405" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2405" s="8" t="s">
@@ -86853,7 +87506,8 @@
       <c r="D2405" s="12" t="s">
         <v>5102</v>
       </c>
-      <c r="F2405" s="2"/>
+      <c r="E2405" s="2"/>
+      <c r="F2405" s="3"/>
     </row>
     <row r="2406" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2406" s="8" t="s">
@@ -86868,7 +87522,8 @@
       <c r="D2406" s="12" t="s">
         <v>5104</v>
       </c>
-      <c r="F2406" s="2"/>
+      <c r="E2406" s="2"/>
+      <c r="F2406" s="3"/>
     </row>
     <row r="2407" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2407" s="8" t="s">
@@ -86883,7 +87538,8 @@
       <c r="D2407" s="12" t="s">
         <v>5106</v>
       </c>
-      <c r="F2407" s="2"/>
+      <c r="E2407" s="2"/>
+      <c r="F2407" s="3"/>
     </row>
     <row r="2408" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2408" s="8" t="s">
@@ -86898,7 +87554,8 @@
       <c r="D2408" s="12" t="s">
         <v>5108</v>
       </c>
-      <c r="F2408" s="2"/>
+      <c r="E2408" s="2"/>
+      <c r="F2408" s="3"/>
     </row>
     <row r="2409" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2409" s="8" t="s">
@@ -86913,7 +87570,8 @@
       <c r="D2409" s="12" t="s">
         <v>5110</v>
       </c>
-      <c r="F2409" s="2"/>
+      <c r="E2409" s="2"/>
+      <c r="F2409" s="3"/>
     </row>
     <row r="2410" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2410" s="8" t="s">
@@ -86928,7 +87586,8 @@
       <c r="D2410" s="12" t="s">
         <v>5112</v>
       </c>
-      <c r="F2410" s="2"/>
+      <c r="E2410" s="2"/>
+      <c r="F2410" s="3"/>
     </row>
     <row r="2411" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2411" s="8" t="s">
@@ -86943,7 +87602,8 @@
       <c r="D2411" s="12" t="s">
         <v>5114</v>
       </c>
-      <c r="F2411" s="2"/>
+      <c r="E2411" s="2"/>
+      <c r="F2411" s="3"/>
     </row>
     <row r="2412" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2412" s="8" t="s">
@@ -86958,7 +87618,8 @@
       <c r="D2412" s="12" t="s">
         <v>5116</v>
       </c>
-      <c r="F2412" s="2"/>
+      <c r="E2412" s="2"/>
+      <c r="F2412" s="3"/>
     </row>
     <row r="2413" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2413" s="8" t="s">
@@ -86973,7 +87634,8 @@
       <c r="D2413" s="12" t="s">
         <v>5118</v>
       </c>
-      <c r="F2413" s="2"/>
+      <c r="E2413" s="2"/>
+      <c r="F2413" s="3"/>
     </row>
     <row r="2414" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2414" s="8" t="s">
@@ -86988,7 +87650,8 @@
       <c r="D2414" s="12" t="s">
         <v>5120</v>
       </c>
-      <c r="F2414" s="2"/>
+      <c r="E2414" s="2"/>
+      <c r="F2414" s="3"/>
     </row>
     <row r="2415" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2415" s="8" t="s">
@@ -87003,7 +87666,8 @@
       <c r="D2415" s="12" t="s">
         <v>5122</v>
       </c>
-      <c r="F2415" s="2"/>
+      <c r="E2415" s="2"/>
+      <c r="F2415" s="3"/>
     </row>
     <row r="2416" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2416" s="8" t="s">
@@ -87018,7 +87682,8 @@
       <c r="D2416" s="12" t="s">
         <v>5125</v>
       </c>
-      <c r="F2416" s="2"/>
+      <c r="E2416" s="2"/>
+      <c r="F2416" s="3"/>
     </row>
     <row r="2417" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2417" s="8" t="s">
@@ -87033,7 +87698,8 @@
       <c r="D2417" s="12" t="s">
         <v>5127</v>
       </c>
-      <c r="F2417" s="2"/>
+      <c r="E2417" s="2"/>
+      <c r="F2417" s="3"/>
     </row>
     <row r="2418" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2418" s="8" t="s">
@@ -87048,7 +87714,8 @@
       <c r="D2418" s="12" t="s">
         <v>5129</v>
       </c>
-      <c r="F2418" s="2"/>
+      <c r="E2418" s="2"/>
+      <c r="F2418" s="3"/>
     </row>
     <row r="2419" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2419" s="8" t="s">
@@ -87063,7 +87730,8 @@
       <c r="D2419" s="12" t="s">
         <v>5131</v>
       </c>
-      <c r="F2419" s="2"/>
+      <c r="E2419" s="2"/>
+      <c r="F2419" s="3"/>
     </row>
     <row r="2420" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2420" s="8" t="s">
@@ -87078,7 +87746,8 @@
       <c r="D2420" s="12" t="s">
         <v>5133</v>
       </c>
-      <c r="F2420" s="2"/>
+      <c r="E2420" s="2"/>
+      <c r="F2420" s="3"/>
     </row>
     <row r="2421" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2421" s="8" t="s">
@@ -87093,7 +87762,8 @@
       <c r="D2421" s="12" t="s">
         <v>5135</v>
       </c>
-      <c r="F2421" s="2"/>
+      <c r="E2421" s="2"/>
+      <c r="F2421" s="3"/>
     </row>
     <row r="2422" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2422" s="8" t="s">
@@ -87108,7 +87778,8 @@
       <c r="D2422" s="12" t="s">
         <v>5137</v>
       </c>
-      <c r="F2422" s="2"/>
+      <c r="E2422" s="2"/>
+      <c r="F2422" s="3"/>
     </row>
     <row r="2423" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2423" s="8" t="s">
@@ -87123,7 +87794,8 @@
       <c r="D2423" s="12" t="s">
         <v>5139</v>
       </c>
-      <c r="F2423" s="2"/>
+      <c r="E2423" s="2"/>
+      <c r="F2423" s="3"/>
     </row>
     <row r="2424" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2424" s="8" t="s">
@@ -87138,7 +87810,8 @@
       <c r="D2424" s="12" t="s">
         <v>5141</v>
       </c>
-      <c r="F2424" s="2"/>
+      <c r="E2424" s="2"/>
+      <c r="F2424" s="3"/>
     </row>
     <row r="2425" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2425" s="8" t="s">
@@ -87153,7 +87826,8 @@
       <c r="D2425" s="12" t="s">
         <v>5143</v>
       </c>
-      <c r="F2425" s="2"/>
+      <c r="E2425" s="2"/>
+      <c r="F2425" s="3"/>
     </row>
     <row r="2426" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2426" s="8" t="s">
@@ -87168,7 +87842,8 @@
       <c r="D2426" s="12" t="s">
         <v>5145</v>
       </c>
-      <c r="F2426" s="2"/>
+      <c r="E2426" s="2"/>
+      <c r="F2426" s="3"/>
     </row>
     <row r="2427" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2427" s="8" t="s">
@@ -87183,7 +87858,8 @@
       <c r="D2427" s="12" t="s">
         <v>5148</v>
       </c>
-      <c r="F2427" s="2"/>
+      <c r="E2427" s="2"/>
+      <c r="F2427" s="3"/>
     </row>
     <row r="2428" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2428" s="8" t="s">
@@ -87198,7 +87874,8 @@
       <c r="D2428" s="12" t="s">
         <v>5150</v>
       </c>
-      <c r="F2428" s="2"/>
+      <c r="E2428" s="2"/>
+      <c r="F2428" s="3"/>
     </row>
     <row r="2429" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2429" s="8" t="s">
@@ -87213,7 +87890,8 @@
       <c r="D2429" s="12" t="s">
         <v>5152</v>
       </c>
-      <c r="F2429" s="2"/>
+      <c r="E2429" s="2"/>
+      <c r="F2429" s="3"/>
     </row>
     <row r="2430" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2430" s="8" t="s">
@@ -87228,7 +87906,8 @@
       <c r="D2430" s="12" t="s">
         <v>5154</v>
       </c>
-      <c r="F2430" s="2"/>
+      <c r="E2430" s="2"/>
+      <c r="F2430" s="3"/>
     </row>
     <row r="2431" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2431" s="8" t="s">
@@ -87243,7 +87922,8 @@
       <c r="D2431" s="12" t="s">
         <v>5156</v>
       </c>
-      <c r="F2431" s="2"/>
+      <c r="E2431" s="2"/>
+      <c r="F2431" s="3"/>
     </row>
     <row r="2432" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2432" s="8" t="s">
@@ -87258,7 +87938,8 @@
       <c r="D2432" s="12" t="s">
         <v>5158</v>
       </c>
-      <c r="F2432" s="2"/>
+      <c r="E2432" s="2"/>
+      <c r="F2432" s="3"/>
     </row>
     <row r="2433" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2433" s="8" t="s">
@@ -87273,7 +87954,8 @@
       <c r="D2433" s="12" t="s">
         <v>5160</v>
       </c>
-      <c r="F2433" s="2"/>
+      <c r="E2433" s="2"/>
+      <c r="F2433" s="3"/>
     </row>
     <row r="2434" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2434" s="8" t="s">
@@ -87288,7 +87970,8 @@
       <c r="D2434" s="12" t="s">
         <v>5162</v>
       </c>
-      <c r="F2434" s="2"/>
+      <c r="E2434" s="2"/>
+      <c r="F2434" s="3"/>
     </row>
     <row r="2435" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2435" s="8" t="s">
@@ -87303,7 +87986,8 @@
       <c r="D2435" s="12" t="s">
         <v>5164</v>
       </c>
-      <c r="F2435" s="2"/>
+      <c r="E2435" s="2"/>
+      <c r="F2435" s="3"/>
     </row>
     <row r="2436" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2436" s="8" t="s">
@@ -87318,7 +88002,8 @@
       <c r="D2436" s="12" t="s">
         <v>5166</v>
       </c>
-      <c r="F2436" s="2"/>
+      <c r="E2436" s="2"/>
+      <c r="F2436" s="3"/>
     </row>
     <row r="2437" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2437" s="8" t="s">
@@ -87333,7 +88018,8 @@
       <c r="D2437" s="12" t="s">
         <v>5168</v>
       </c>
-      <c r="F2437" s="2"/>
+      <c r="E2437" s="2"/>
+      <c r="F2437" s="3"/>
     </row>
     <row r="2438" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2438" s="8" t="s">
@@ -87348,7 +88034,8 @@
       <c r="D2438" s="12" t="s">
         <v>5170</v>
       </c>
-      <c r="F2438" s="2"/>
+      <c r="E2438" s="2"/>
+      <c r="F2438" s="3"/>
     </row>
     <row r="2439" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2439" s="8" t="s">
@@ -87363,7 +88050,8 @@
       <c r="D2439" s="12" t="s">
         <v>5173</v>
       </c>
-      <c r="F2439" s="2"/>
+      <c r="E2439" s="2"/>
+      <c r="F2439" s="3"/>
     </row>
     <row r="2440" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2440" s="8" t="s">
@@ -87378,7 +88066,8 @@
       <c r="D2440" s="12" t="s">
         <v>5175</v>
       </c>
-      <c r="F2440" s="2"/>
+      <c r="E2440" s="2"/>
+      <c r="F2440" s="3"/>
     </row>
     <row r="2441" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2441" s="8" t="s">
@@ -87393,7 +88082,8 @@
       <c r="D2441" s="12" t="s">
         <v>5177</v>
       </c>
-      <c r="F2441" s="2"/>
+      <c r="E2441" s="2"/>
+      <c r="F2441" s="3"/>
     </row>
     <row r="2442" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2442" s="8" t="s">
@@ -87408,7 +88098,8 @@
       <c r="D2442" s="12" t="s">
         <v>5179</v>
       </c>
-      <c r="F2442" s="2"/>
+      <c r="E2442" s="2"/>
+      <c r="F2442" s="3"/>
     </row>
     <row r="2443" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2443" s="8" t="s">
@@ -87423,7 +88114,8 @@
       <c r="D2443" s="12" t="s">
         <v>5181</v>
       </c>
-      <c r="F2443" s="2"/>
+      <c r="E2443" s="2"/>
+      <c r="F2443" s="3"/>
     </row>
     <row r="2444" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2444" s="8" t="s">
@@ -87438,7 +88130,8 @@
       <c r="D2444" s="12" t="s">
         <v>5183</v>
       </c>
-      <c r="F2444" s="2"/>
+      <c r="E2444" s="2"/>
+      <c r="F2444" s="3"/>
     </row>
     <row r="2445" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2445" s="8" t="s">
@@ -87453,7 +88146,8 @@
       <c r="D2445" s="12" t="s">
         <v>5185</v>
       </c>
-      <c r="F2445" s="2"/>
+      <c r="E2445" s="2"/>
+      <c r="F2445" s="3"/>
     </row>
     <row r="2446" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2446" s="8" t="s">
@@ -87468,7 +88162,8 @@
       <c r="D2446" s="12" t="s">
         <v>5187</v>
       </c>
-      <c r="F2446" s="2"/>
+      <c r="E2446" s="2"/>
+      <c r="F2446" s="3"/>
     </row>
     <row r="2447" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2447" s="8" t="s">
@@ -87483,7 +88178,8 @@
       <c r="D2447" s="12" t="s">
         <v>5189</v>
       </c>
-      <c r="F2447" s="2"/>
+      <c r="E2447" s="2"/>
+      <c r="F2447" s="3"/>
     </row>
     <row r="2448" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2448" s="8" t="s">
@@ -87498,7 +88194,8 @@
       <c r="D2448" s="12" t="s">
         <v>5191</v>
       </c>
-      <c r="F2448" s="2"/>
+      <c r="E2448" s="2"/>
+      <c r="F2448" s="3"/>
     </row>
     <row r="2449" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2449" s="8" t="s">
@@ -87513,7 +88210,8 @@
       <c r="D2449" s="12" t="s">
         <v>5194</v>
       </c>
-      <c r="F2449" s="2"/>
+      <c r="E2449" s="2"/>
+      <c r="F2449" s="3"/>
     </row>
     <row r="2450" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2450" s="8" t="s">
@@ -87528,7 +88226,8 @@
       <c r="D2450" s="12" t="s">
         <v>5196</v>
       </c>
-      <c r="F2450" s="2"/>
+      <c r="E2450" s="2"/>
+      <c r="F2450" s="3"/>
     </row>
     <row r="2451" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2451" s="8" t="s">
@@ -87543,7 +88242,8 @@
       <c r="D2451" s="12" t="s">
         <v>5198</v>
       </c>
-      <c r="F2451" s="2"/>
+      <c r="E2451" s="2"/>
+      <c r="F2451" s="3"/>
     </row>
     <row r="2452" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2452" s="8" t="s">
@@ -87558,7 +88258,8 @@
       <c r="D2452" s="12" t="s">
         <v>5200</v>
       </c>
-      <c r="F2452" s="2"/>
+      <c r="E2452" s="2"/>
+      <c r="F2452" s="3"/>
     </row>
     <row r="2453" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2453" s="8" t="s">
@@ -87573,7 +88274,8 @@
       <c r="D2453" s="12" t="s">
         <v>5202</v>
       </c>
-      <c r="F2453" s="2"/>
+      <c r="E2453" s="2"/>
+      <c r="F2453" s="3"/>
     </row>
     <row r="2454" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2454" s="8" t="s">
@@ -87588,7 +88290,8 @@
       <c r="D2454" s="12" t="s">
         <v>5204</v>
       </c>
-      <c r="F2454" s="2"/>
+      <c r="E2454" s="2"/>
+      <c r="F2454" s="3"/>
     </row>
     <row r="2455" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2455" s="8" t="s">
@@ -87603,7 +88306,8 @@
       <c r="D2455" s="12" t="s">
         <v>5206</v>
       </c>
-      <c r="F2455" s="2"/>
+      <c r="E2455" s="2"/>
+      <c r="F2455" s="3"/>
     </row>
     <row r="2456" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2456" s="8" t="s">
@@ -87681,7 +88385,7 @@
       <c r="E2459" s="8">
         <v>40669</v>
       </c>
-      <c r="F2459" s="2"/>
+      <c r="F2459" s="3"/>
     </row>
     <row r="2460" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2460" s="8" t="s">
@@ -89316,7 +90020,8 @@
       <c r="D2541" s="12" t="s">
         <v>5393</v>
       </c>
-      <c r="F2541" s="2"/>
+      <c r="E2541" s="2"/>
+      <c r="F2541" s="3"/>
     </row>
     <row r="2542" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2542" s="8" t="s">
@@ -89331,7 +90036,8 @@
       <c r="D2542" s="12" t="s">
         <v>5394</v>
       </c>
-      <c r="F2542" s="2"/>
+      <c r="E2542" s="2"/>
+      <c r="F2542" s="3"/>
     </row>
     <row r="2543" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2543" s="8" t="s">
@@ -89346,7 +90052,8 @@
       <c r="D2543" s="12" t="s">
         <v>5396</v>
       </c>
-      <c r="F2543" s="2"/>
+      <c r="E2543" s="2"/>
+      <c r="F2543" s="3"/>
     </row>
     <row r="2544" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2544" s="8" t="s">
@@ -89361,7 +90068,8 @@
       <c r="D2544" s="12" t="s">
         <v>5398</v>
       </c>
-      <c r="F2544" s="2"/>
+      <c r="E2544" s="2"/>
+      <c r="F2544" s="3"/>
     </row>
     <row r="2545" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2545" s="8" t="s">
@@ -89376,7 +90084,8 @@
       <c r="D2545" s="12" t="s">
         <v>5400</v>
       </c>
-      <c r="F2545" s="2"/>
+      <c r="E2545" s="2"/>
+      <c r="F2545" s="3"/>
     </row>
     <row r="2546" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2546" s="8" t="s">
@@ -89391,7 +90100,8 @@
       <c r="D2546" s="12" t="s">
         <v>5402</v>
       </c>
-      <c r="F2546" s="2"/>
+      <c r="E2546" s="2"/>
+      <c r="F2546" s="3"/>
     </row>
     <row r="2547" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2547" s="8" t="s">
@@ -89406,7 +90116,8 @@
       <c r="D2547" s="12" t="s">
         <v>5404</v>
       </c>
-      <c r="F2547" s="2"/>
+      <c r="E2547" s="2"/>
+      <c r="F2547" s="3"/>
     </row>
     <row r="2548" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2548" s="8" t="s">
@@ -89421,7 +90132,8 @@
       <c r="D2548" s="12" t="s">
         <v>5407</v>
       </c>
-      <c r="F2548" s="2"/>
+      <c r="E2548" s="2"/>
+      <c r="F2548" s="3"/>
     </row>
     <row r="2549" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2549" s="8" t="s">
@@ -89436,7 +90148,8 @@
       <c r="D2549" s="12" t="s">
         <v>5409</v>
       </c>
-      <c r="F2549" s="2"/>
+      <c r="E2549" s="2"/>
+      <c r="F2549" s="3"/>
     </row>
     <row r="2550" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2550" s="8" t="s">
@@ -89451,7 +90164,8 @@
       <c r="D2550" s="12" t="s">
         <v>5411</v>
       </c>
-      <c r="F2550" s="2"/>
+      <c r="E2550" s="2"/>
+      <c r="F2550" s="3"/>
     </row>
     <row r="2551" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2551" s="8" t="s">
@@ -89466,7 +90180,8 @@
       <c r="D2551" s="12" t="s">
         <v>5413</v>
       </c>
-      <c r="F2551" s="2"/>
+      <c r="E2551" s="2"/>
+      <c r="F2551" s="3"/>
     </row>
     <row r="2552" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2552" s="8" t="s">
@@ -89481,7 +90196,8 @@
       <c r="D2552" s="12" t="s">
         <v>5415</v>
       </c>
-      <c r="F2552" s="2"/>
+      <c r="E2552" s="2"/>
+      <c r="F2552" s="3"/>
     </row>
     <row r="2553" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2553" s="8" t="s">
@@ -89496,7 +90212,8 @@
       <c r="D2553" s="12" t="s">
         <v>5417</v>
       </c>
-      <c r="F2553" s="2"/>
+      <c r="E2553" s="2"/>
+      <c r="F2553" s="3"/>
     </row>
     <row r="2554" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2554" s="8" t="s">
@@ -89511,7 +90228,8 @@
       <c r="D2554" s="12" t="s">
         <v>5420</v>
       </c>
-      <c r="F2554" s="2"/>
+      <c r="E2554" s="2"/>
+      <c r="F2554" s="3"/>
     </row>
     <row r="2555" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2555" s="8" t="s">
@@ -89526,7 +90244,8 @@
       <c r="D2555" s="12" t="s">
         <v>5422</v>
       </c>
-      <c r="F2555" s="2"/>
+      <c r="E2555" s="2"/>
+      <c r="F2555" s="3"/>
     </row>
     <row r="2556" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2556" s="8" t="s">
@@ -89541,7 +90260,8 @@
       <c r="D2556" s="12" t="s">
         <v>5424</v>
       </c>
-      <c r="F2556" s="2"/>
+      <c r="E2556" s="2"/>
+      <c r="F2556" s="3"/>
     </row>
     <row r="2557" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2557" s="8" t="s">
@@ -89556,7 +90276,8 @@
       <c r="D2557" s="12" t="s">
         <v>5426</v>
       </c>
-      <c r="F2557" s="2"/>
+      <c r="E2557" s="2"/>
+      <c r="F2557" s="3"/>
     </row>
     <row r="2558" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2558" s="8" t="s">
@@ -89571,7 +90292,8 @@
       <c r="D2558" s="12" t="s">
         <v>5429</v>
       </c>
-      <c r="F2558" s="2"/>
+      <c r="E2558" s="2"/>
+      <c r="F2558" s="3"/>
     </row>
     <row r="2559" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2559" s="8" t="s">
@@ -89586,7 +90308,8 @@
       <c r="D2559" s="12" t="s">
         <v>5431</v>
       </c>
-      <c r="F2559" s="2"/>
+      <c r="E2559" s="2"/>
+      <c r="F2559" s="3"/>
     </row>
     <row r="2560" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2560" s="8" t="s">
@@ -89601,7 +90324,8 @@
       <c r="D2560" s="12" t="s">
         <v>5433</v>
       </c>
-      <c r="F2560" s="2"/>
+      <c r="E2560" s="2"/>
+      <c r="F2560" s="3"/>
     </row>
     <row r="2561" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2561" s="8" t="s">
@@ -89616,7 +90340,8 @@
       <c r="D2561" s="12" t="s">
         <v>5435</v>
       </c>
-      <c r="F2561" s="2"/>
+      <c r="E2561" s="2"/>
+      <c r="F2561" s="3"/>
     </row>
     <row r="2562" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2562" s="8" t="s">
@@ -89631,7 +90356,8 @@
       <c r="D2562" s="12" t="s">
         <v>5438</v>
       </c>
-      <c r="F2562" s="2"/>
+      <c r="E2562" s="2"/>
+      <c r="F2562" s="3"/>
     </row>
     <row r="2563" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2563" s="8" t="s">
@@ -89646,7 +90372,8 @@
       <c r="D2563" s="12" t="s">
         <v>5440</v>
       </c>
-      <c r="F2563" s="2"/>
+      <c r="E2563" s="2"/>
+      <c r="F2563" s="3"/>
     </row>
     <row r="2564" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2564" s="8" t="s">
@@ -89661,7 +90388,8 @@
       <c r="D2564" s="12" t="s">
         <v>5442</v>
       </c>
-      <c r="F2564" s="2"/>
+      <c r="E2564" s="2"/>
+      <c r="F2564" s="3"/>
     </row>
     <row r="2565" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2565" s="8" t="s">
@@ -89676,7 +90404,8 @@
       <c r="D2565" s="12" t="s">
         <v>5444</v>
       </c>
-      <c r="F2565" s="2"/>
+      <c r="E2565" s="2"/>
+      <c r="F2565" s="3"/>
     </row>
     <row r="2566" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2566" s="8" t="s">
@@ -89691,7 +90420,8 @@
       <c r="D2566" s="12" t="s">
         <v>5446</v>
       </c>
-      <c r="F2566" s="2"/>
+      <c r="E2566" s="2"/>
+      <c r="F2566" s="3"/>
     </row>
     <row r="2567" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2567" s="8" t="s">
@@ -89706,7 +90436,8 @@
       <c r="D2567" s="12" t="s">
         <v>5449</v>
       </c>
-      <c r="F2567" s="2"/>
+      <c r="E2567" s="2"/>
+      <c r="F2567" s="3"/>
     </row>
     <row r="2568" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2568" s="8" t="s">
@@ -89721,7 +90452,8 @@
       <c r="D2568" s="12" t="s">
         <v>5451</v>
       </c>
-      <c r="F2568" s="2"/>
+      <c r="E2568" s="2"/>
+      <c r="F2568" s="3"/>
     </row>
     <row r="2569" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2569" s="8" t="s">
@@ -89736,7 +90468,8 @@
       <c r="D2569" s="12" t="s">
         <v>5453</v>
       </c>
-      <c r="F2569" s="2"/>
+      <c r="E2569" s="2"/>
+      <c r="F2569" s="3"/>
     </row>
     <row r="2570" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2570" s="8" t="s">
@@ -89751,7 +90484,8 @@
       <c r="D2570" s="12" t="s">
         <v>5455</v>
       </c>
-      <c r="F2570" s="2"/>
+      <c r="E2570" s="2"/>
+      <c r="F2570" s="3"/>
     </row>
     <row r="2571" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2571" s="8" t="s">
@@ -89766,7 +90500,8 @@
       <c r="D2571" s="12" t="s">
         <v>5457</v>
       </c>
-      <c r="F2571" s="2"/>
+      <c r="E2571" s="2"/>
+      <c r="F2571" s="3"/>
     </row>
     <row r="2572" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2572" s="8" t="s">
@@ -89781,7 +90516,8 @@
       <c r="D2572" s="12" t="s">
         <v>5459</v>
       </c>
-      <c r="F2572" s="2"/>
+      <c r="E2572" s="2"/>
+      <c r="F2572" s="3"/>
     </row>
     <row r="2573" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2573" s="8" t="s">
@@ -89796,7 +90532,8 @@
       <c r="D2573" s="12" t="s">
         <v>5462</v>
       </c>
-      <c r="F2573" s="2"/>
+      <c r="E2573" s="2"/>
+      <c r="F2573" s="3"/>
     </row>
     <row r="2574" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2574" s="8" t="s">
@@ -89811,7 +90548,8 @@
       <c r="D2574" s="12" t="s">
         <v>5464</v>
       </c>
-      <c r="F2574" s="2"/>
+      <c r="E2574" s="2"/>
+      <c r="F2574" s="3"/>
     </row>
     <row r="2575" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2575" s="8" t="s">
@@ -89826,7 +90564,8 @@
       <c r="D2575" s="12" t="s">
         <v>5466</v>
       </c>
-      <c r="F2575" s="2"/>
+      <c r="E2575" s="2"/>
+      <c r="F2575" s="3"/>
     </row>
     <row r="2576" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2576" s="8" t="s">
@@ -89841,7 +90580,8 @@
       <c r="D2576" s="12" t="s">
         <v>5468</v>
       </c>
-      <c r="F2576" s="2"/>
+      <c r="E2576" s="2"/>
+      <c r="F2576" s="3"/>
     </row>
     <row r="2577" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2577" s="8" t="s">
@@ -89856,7 +90596,8 @@
       <c r="D2577" s="12" t="s">
         <v>5470</v>
       </c>
-      <c r="F2577" s="2"/>
+      <c r="E2577" s="2"/>
+      <c r="F2577" s="3"/>
     </row>
     <row r="2578" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2578" s="8" t="s">
@@ -89871,7 +90612,8 @@
       <c r="D2578" s="12" t="s">
         <v>5472</v>
       </c>
-      <c r="F2578" s="2"/>
+      <c r="E2578" s="2"/>
+      <c r="F2578" s="3"/>
     </row>
     <row r="2579" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2579" s="8" t="s">
@@ -89886,7 +90628,8 @@
       <c r="D2579" s="12" t="s">
         <v>5475</v>
       </c>
-      <c r="F2579" s="2"/>
+      <c r="E2579" s="2"/>
+      <c r="F2579" s="3"/>
     </row>
     <row r="2580" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2580" s="8" t="s">
@@ -89901,7 +90644,8 @@
       <c r="D2580" s="12" t="s">
         <v>5477</v>
       </c>
-      <c r="F2580" s="2"/>
+      <c r="E2580" s="2"/>
+      <c r="F2580" s="3"/>
     </row>
     <row r="2581" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2581" s="8" t="s">
@@ -89916,7 +90660,8 @@
       <c r="D2581" s="12" t="s">
         <v>5479</v>
       </c>
-      <c r="F2581" s="2"/>
+      <c r="E2581" s="2"/>
+      <c r="F2581" s="3"/>
     </row>
     <row r="2582" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2582" s="8" t="s">
@@ -89931,7 +90676,8 @@
       <c r="D2582" s="12" t="s">
         <v>5481</v>
       </c>
-      <c r="F2582" s="2"/>
+      <c r="E2582" s="2"/>
+      <c r="F2582" s="3"/>
     </row>
     <row r="2583" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2583" s="8" t="s">
@@ -89946,7 +90692,8 @@
       <c r="D2583" s="12" t="s">
         <v>5483</v>
       </c>
-      <c r="F2583" s="2"/>
+      <c r="E2583" s="2"/>
+      <c r="F2583" s="3"/>
     </row>
     <row r="2584" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2584" s="8" t="s">
@@ -89961,7 +90708,8 @@
       <c r="D2584" s="12" t="s">
         <v>5485</v>
       </c>
-      <c r="F2584" s="2"/>
+      <c r="E2584" s="2"/>
+      <c r="F2584" s="3"/>
     </row>
     <row r="2585" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2585" s="8" t="s">
@@ -90416,7 +91164,8 @@
       <c r="D2607" s="12" t="s">
         <v>5539</v>
       </c>
-      <c r="F2607" s="2"/>
+      <c r="E2607" s="2"/>
+      <c r="F2607" s="3"/>
     </row>
     <row r="2608" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2608" s="8" t="s">
@@ -90431,7 +91180,8 @@
       <c r="D2608" s="12" t="s">
         <v>5541</v>
       </c>
-      <c r="F2608" s="2"/>
+      <c r="E2608" s="2"/>
+      <c r="F2608" s="3"/>
     </row>
     <row r="2609" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2609" s="8" t="s">
@@ -90446,7 +91196,8 @@
       <c r="D2609" s="12" t="s">
         <v>5543</v>
       </c>
-      <c r="F2609" s="2"/>
+      <c r="E2609" s="2"/>
+      <c r="F2609" s="3"/>
     </row>
     <row r="2610" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2610" s="8" t="s">
@@ -90461,7 +91212,8 @@
       <c r="D2610" s="12" t="s">
         <v>5545</v>
       </c>
-      <c r="F2610" s="2"/>
+      <c r="E2610" s="2"/>
+      <c r="F2610" s="3"/>
     </row>
     <row r="2611" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2611" s="8" t="s">
@@ -90476,7 +91228,8 @@
       <c r="D2611" s="12" t="s">
         <v>5547</v>
       </c>
-      <c r="F2611" s="2"/>
+      <c r="E2611" s="2"/>
+      <c r="F2611" s="3"/>
     </row>
     <row r="2612" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2612" s="8" t="s">
@@ -90491,7 +91244,8 @@
       <c r="D2612" s="12" t="s">
         <v>5549</v>
       </c>
-      <c r="F2612" s="2"/>
+      <c r="E2612" s="2"/>
+      <c r="F2612" s="3"/>
     </row>
     <row r="2613" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2613" s="8" t="s">
@@ -90506,7 +91260,8 @@
       <c r="D2613" s="12" t="s">
         <v>5551</v>
       </c>
-      <c r="F2613" s="2"/>
+      <c r="E2613" s="2"/>
+      <c r="F2613" s="3"/>
     </row>
     <row r="2614" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2614" s="8" t="s">
@@ -90521,7 +91276,8 @@
       <c r="D2614" s="12" t="s">
         <v>5553</v>
       </c>
-      <c r="F2614" s="2"/>
+      <c r="E2614" s="2"/>
+      <c r="F2614" s="3"/>
     </row>
     <row r="2615" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2615" s="8" t="s">
@@ -90536,7 +91292,8 @@
       <c r="D2615" s="12" t="s">
         <v>5556</v>
       </c>
-      <c r="F2615" s="2"/>
+      <c r="E2615" s="2"/>
+      <c r="F2615" s="3"/>
     </row>
     <row r="2616" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2616" s="8" t="s">
@@ -90551,7 +91308,8 @@
       <c r="D2616" s="12" t="s">
         <v>5558</v>
       </c>
-      <c r="F2616" s="2"/>
+      <c r="E2616" s="2"/>
+      <c r="F2616" s="3"/>
     </row>
     <row r="2617" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2617" s="8" t="s">
@@ -90566,7 +91324,8 @@
       <c r="D2617" s="12" t="s">
         <v>5560</v>
       </c>
-      <c r="F2617" s="2"/>
+      <c r="E2617" s="2"/>
+      <c r="F2617" s="3"/>
     </row>
     <row r="2618" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2618" s="8" t="s">
@@ -90581,7 +91340,8 @@
       <c r="D2618" s="12" t="s">
         <v>5562</v>
       </c>
-      <c r="F2618" s="2"/>
+      <c r="E2618" s="2"/>
+      <c r="F2618" s="3"/>
     </row>
     <row r="2619" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2619" s="8" t="s">
@@ -90596,7 +91356,8 @@
       <c r="D2619" s="12" t="s">
         <v>5565</v>
       </c>
-      <c r="F2619" s="2"/>
+      <c r="E2619" s="2"/>
+      <c r="F2619" s="3"/>
     </row>
     <row r="2620" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2620" s="8" t="s">
@@ -90611,7 +91372,8 @@
       <c r="D2620" s="12" t="s">
         <v>5567</v>
       </c>
-      <c r="F2620" s="2"/>
+      <c r="E2620" s="2"/>
+      <c r="F2620" s="3"/>
     </row>
     <row r="2621" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2621" s="8" t="s">
@@ -90626,7 +91388,8 @@
       <c r="D2621" s="12" t="s">
         <v>5569</v>
       </c>
-      <c r="F2621" s="2"/>
+      <c r="E2621" s="2"/>
+      <c r="F2621" s="3"/>
     </row>
     <row r="2622" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2622" s="8" t="s">
@@ -90641,7 +91404,8 @@
       <c r="D2622" s="12" t="s">
         <v>5572</v>
       </c>
-      <c r="F2622" s="2"/>
+      <c r="E2622" s="2"/>
+      <c r="F2622" s="3"/>
     </row>
     <row r="2623" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2623" s="8" t="s">
@@ -90656,7 +91420,8 @@
       <c r="D2623" s="12" t="s">
         <v>5574</v>
       </c>
-      <c r="F2623" s="2"/>
+      <c r="E2623" s="2"/>
+      <c r="F2623" s="3"/>
     </row>
     <row r="2624" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2624" s="8" t="s">
@@ -90671,7 +91436,8 @@
       <c r="D2624" s="12" t="s">
         <v>5576</v>
       </c>
-      <c r="F2624" s="2"/>
+      <c r="E2624" s="2"/>
+      <c r="F2624" s="3"/>
     </row>
     <row r="2625" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2625" s="8" t="s">
@@ -90686,7 +91452,8 @@
       <c r="D2625" s="12" t="s">
         <v>5579</v>
       </c>
-      <c r="F2625" s="2"/>
+      <c r="E2625" s="2"/>
+      <c r="F2625" s="3"/>
     </row>
     <row r="2626" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2626" s="8" t="s">
@@ -90701,7 +91468,8 @@
       <c r="D2626" s="12" t="s">
         <v>5581</v>
       </c>
-      <c r="F2626" s="2"/>
+      <c r="E2626" s="2"/>
+      <c r="F2626" s="3"/>
     </row>
     <row r="2627" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2627" s="8" t="s">
@@ -90716,7 +91484,8 @@
       <c r="D2627" s="12" t="s">
         <v>5583</v>
       </c>
-      <c r="F2627" s="2"/>
+      <c r="E2627" s="2"/>
+      <c r="F2627" s="3"/>
     </row>
     <row r="2628" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2628" s="8" t="s">
@@ -90731,7 +91500,8 @@
       <c r="D2628" s="12" t="s">
         <v>5585</v>
       </c>
-      <c r="F2628" s="2"/>
+      <c r="E2628" s="2"/>
+      <c r="F2628" s="3"/>
     </row>
     <row r="2629" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2629" s="8" t="s">
@@ -90746,7 +91516,8 @@
       <c r="D2629" s="12" t="s">
         <v>5587</v>
       </c>
-      <c r="F2629" s="2"/>
+      <c r="E2629" s="2"/>
+      <c r="F2629" s="3"/>
     </row>
     <row r="2630" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2630" s="8" t="s">
@@ -90761,7 +91532,8 @@
       <c r="D2630" s="12" t="s">
         <v>5589</v>
       </c>
-      <c r="F2630" s="2"/>
+      <c r="E2630" s="2"/>
+      <c r="F2630" s="3"/>
     </row>
     <row r="2631" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2631" s="8" t="s">
@@ -90776,7 +91548,8 @@
       <c r="D2631" s="12" t="s">
         <v>5591</v>
       </c>
-      <c r="F2631" s="2"/>
+      <c r="E2631" s="2"/>
+      <c r="F2631" s="3"/>
     </row>
     <row r="2632" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2632" s="8" t="s">
@@ -90791,7 +91564,8 @@
       <c r="D2632" s="12" t="s">
         <v>5594</v>
       </c>
-      <c r="F2632" s="2"/>
+      <c r="E2632" s="2"/>
+      <c r="F2632" s="3"/>
     </row>
     <row r="2633" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2633" s="8" t="s">
@@ -90806,7 +91580,8 @@
       <c r="D2633" s="12" t="s">
         <v>5596</v>
       </c>
-      <c r="F2633" s="2"/>
+      <c r="E2633" s="2"/>
+      <c r="F2633" s="3"/>
     </row>
     <row r="2634" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2634" s="8" t="s">
@@ -90821,7 +91596,8 @@
       <c r="D2634" s="12" t="s">
         <v>5598</v>
       </c>
-      <c r="F2634" s="2"/>
+      <c r="E2634" s="2"/>
+      <c r="F2634" s="3"/>
     </row>
     <row r="2635" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2635" s="8" t="s">
@@ -90836,7 +91612,8 @@
       <c r="D2635" s="12" t="s">
         <v>5600</v>
       </c>
-      <c r="F2635" s="2"/>
+      <c r="E2635" s="2"/>
+      <c r="F2635" s="3"/>
     </row>
     <row r="2636" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2636" s="8" t="s">
@@ -90851,7 +91628,8 @@
       <c r="D2636" s="12" t="s">
         <v>5603</v>
       </c>
-      <c r="F2636" s="2"/>
+      <c r="E2636" s="2"/>
+      <c r="F2636" s="3"/>
     </row>
     <row r="2637" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2637" s="8" t="s">
@@ -90866,7 +91644,8 @@
       <c r="D2637" s="12" t="s">
         <v>5605</v>
       </c>
-      <c r="F2637" s="2"/>
+      <c r="E2637" s="2"/>
+      <c r="F2637" s="3"/>
     </row>
     <row r="2638" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2638" s="8" t="s">
@@ -90881,7 +91660,8 @@
       <c r="D2638" s="12" t="s">
         <v>5607</v>
       </c>
-      <c r="F2638" s="2"/>
+      <c r="E2638" s="2"/>
+      <c r="F2638" s="3"/>
     </row>
     <row r="2639" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2639" s="8" t="s">
@@ -90896,7 +91676,8 @@
       <c r="D2639" s="12" t="s">
         <v>5609</v>
       </c>
-      <c r="F2639" s="2"/>
+      <c r="E2639" s="2"/>
+      <c r="F2639" s="3"/>
     </row>
     <row r="2640" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2640" s="8" t="s">
@@ -90911,7 +91692,8 @@
       <c r="D2640" s="12" t="s">
         <v>5611</v>
       </c>
-      <c r="F2640" s="2"/>
+      <c r="E2640" s="2"/>
+      <c r="F2640" s="3"/>
     </row>
     <row r="2641" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2641" s="8" t="s">
@@ -90926,7 +91708,8 @@
       <c r="D2641" s="12" t="s">
         <v>5613</v>
       </c>
-      <c r="F2641" s="2"/>
+      <c r="E2641" s="2"/>
+      <c r="F2641" s="3"/>
     </row>
     <row r="2642" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2642" s="8" t="s">
@@ -90941,7 +91724,8 @@
       <c r="D2642" s="12" t="s">
         <v>5615</v>
       </c>
-      <c r="F2642" s="2"/>
+      <c r="E2642" s="2"/>
+      <c r="F2642" s="3"/>
     </row>
     <row r="2643" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2643" s="8" t="s">
@@ -90956,7 +91740,8 @@
       <c r="D2643" s="12" t="s">
         <v>5617</v>
       </c>
-      <c r="F2643" s="2"/>
+      <c r="E2643" s="2"/>
+      <c r="F2643" s="3"/>
     </row>
     <row r="2644" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2644" s="8" t="s">
@@ -90971,7 +91756,8 @@
       <c r="D2644" s="12" t="s">
         <v>5619</v>
       </c>
-      <c r="F2644" s="2"/>
+      <c r="E2644" s="2"/>
+      <c r="F2644" s="3"/>
     </row>
     <row r="2645" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2645" s="8" t="s">
@@ -90986,7 +91772,8 @@
       <c r="D2645" s="12" t="s">
         <v>5622</v>
       </c>
-      <c r="F2645" s="2"/>
+      <c r="E2645" s="2"/>
+      <c r="F2645" s="3"/>
     </row>
     <row r="2646" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2646" s="8" t="s">
@@ -91001,7 +91788,8 @@
       <c r="D2646" s="12" t="s">
         <v>5624</v>
       </c>
-      <c r="F2646" s="2"/>
+      <c r="E2646" s="2"/>
+      <c r="F2646" s="3"/>
     </row>
     <row r="2647" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2647" s="8" t="s">
@@ -91016,7 +91804,8 @@
       <c r="D2647" s="12" t="s">
         <v>5626</v>
       </c>
-      <c r="F2647" s="2"/>
+      <c r="E2647" s="2"/>
+      <c r="F2647" s="3"/>
     </row>
     <row r="2648" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2648" s="8" t="s">
@@ -91031,7 +91820,8 @@
       <c r="D2648" s="12" t="s">
         <v>5628</v>
       </c>
-      <c r="F2648" s="2"/>
+      <c r="E2648" s="2"/>
+      <c r="F2648" s="3"/>
     </row>
     <row r="2649" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2649" s="8" t="s">
@@ -91046,7 +91836,8 @@
       <c r="D2649" s="12" t="s">
         <v>5630</v>
       </c>
-      <c r="F2649" s="2"/>
+      <c r="E2649" s="2"/>
+      <c r="F2649" s="3"/>
     </row>
     <row r="2650" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2650" s="8" t="s">
@@ -91061,7 +91852,8 @@
       <c r="D2650" s="12" t="s">
         <v>5632</v>
       </c>
-      <c r="F2650" s="2"/>
+      <c r="E2650" s="2"/>
+      <c r="F2650" s="3"/>
     </row>
     <row r="2651" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2651" s="8" t="s">
@@ -91076,7 +91868,8 @@
       <c r="D2651" s="12" t="s">
         <v>5634</v>
       </c>
-      <c r="F2651" s="2"/>
+      <c r="E2651" s="2"/>
+      <c r="F2651" s="3"/>
     </row>
     <row r="2652" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2652" s="8" t="s">
@@ -91091,7 +91884,8 @@
       <c r="D2652" s="12" t="s">
         <v>5636</v>
       </c>
-      <c r="F2652" s="2"/>
+      <c r="E2652" s="2"/>
+      <c r="F2652" s="3"/>
     </row>
     <row r="2653" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2653" s="8" t="s">
@@ -91106,7 +91900,8 @@
       <c r="D2653" s="12" t="s">
         <v>5638</v>
       </c>
-      <c r="F2653" s="2"/>
+      <c r="E2653" s="2"/>
+      <c r="F2653" s="3"/>
     </row>
     <row r="2654" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2654" s="8" t="s">
@@ -91121,7 +91916,8 @@
       <c r="D2654" s="12" t="s">
         <v>5641</v>
       </c>
-      <c r="F2654" s="2"/>
+      <c r="E2654" s="2"/>
+      <c r="F2654" s="3"/>
     </row>
     <row r="2655" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2655" s="8" t="s">
@@ -91136,7 +91932,8 @@
       <c r="D2655" s="12" t="s">
         <v>5643</v>
       </c>
-      <c r="F2655" s="2"/>
+      <c r="E2655" s="2"/>
+      <c r="F2655" s="3"/>
     </row>
     <row r="2656" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2656" s="8" t="s">
@@ -91151,7 +91948,8 @@
       <c r="D2656" s="12" t="s">
         <v>5645</v>
       </c>
-      <c r="F2656" s="2"/>
+      <c r="E2656" s="2"/>
+      <c r="F2656" s="3"/>
     </row>
     <row r="2657" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2657" s="8" t="s">
@@ -91166,7 +91964,8 @@
       <c r="D2657" s="12" t="s">
         <v>5647</v>
       </c>
-      <c r="F2657" s="2"/>
+      <c r="E2657" s="2"/>
+      <c r="F2657" s="3"/>
     </row>
     <row r="2658" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2658" s="8" t="s">
@@ -91181,7 +91980,8 @@
       <c r="D2658" s="12" t="s">
         <v>5650</v>
       </c>
-      <c r="F2658" s="2"/>
+      <c r="E2658" s="2"/>
+      <c r="F2658" s="3"/>
     </row>
     <row r="2659" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2659" s="8" t="s">
@@ -91196,7 +91996,8 @@
       <c r="D2659" s="12" t="s">
         <v>5652</v>
       </c>
-      <c r="F2659" s="2"/>
+      <c r="E2659" s="2"/>
+      <c r="F2659" s="3"/>
     </row>
     <row r="2660" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2660" s="8" t="s">
@@ -91211,7 +92012,8 @@
       <c r="D2660" s="12" t="s">
         <v>5654</v>
       </c>
-      <c r="F2660" s="2"/>
+      <c r="E2660" s="2"/>
+      <c r="F2660" s="3"/>
     </row>
     <row r="2661" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2661" s="8" t="s">
@@ -91226,7 +92028,8 @@
       <c r="D2661" s="12" t="s">
         <v>5656</v>
       </c>
-      <c r="F2661" s="2"/>
+      <c r="E2661" s="2"/>
+      <c r="F2661" s="3"/>
     </row>
     <row r="2662" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2662" s="8" t="s">
@@ -91241,7 +92044,8 @@
       <c r="D2662" s="12" t="s">
         <v>5658</v>
       </c>
-      <c r="F2662" s="2"/>
+      <c r="E2662" s="2"/>
+      <c r="F2662" s="3"/>
     </row>
     <row r="2663" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2663" s="8" t="s">
@@ -91256,7 +92060,8 @@
       <c r="D2663" s="12" t="s">
         <v>5660</v>
       </c>
-      <c r="F2663" s="2"/>
+      <c r="E2663" s="2"/>
+      <c r="F2663" s="3"/>
     </row>
     <row r="2664" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2664" s="8" t="s">
@@ -91271,7 +92076,8 @@
       <c r="D2664" s="12" t="s">
         <v>5662</v>
       </c>
-      <c r="F2664" s="2"/>
+      <c r="E2664" s="2"/>
+      <c r="F2664" s="3"/>
     </row>
     <row r="2665" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2665" s="8" t="s">
@@ -91286,7 +92092,8 @@
       <c r="D2665" s="12" t="s">
         <v>5664</v>
       </c>
-      <c r="F2665" s="2"/>
+      <c r="E2665" s="2"/>
+      <c r="F2665" s="3"/>
     </row>
     <row r="2666" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2666" s="8" t="s">
@@ -91301,7 +92108,8 @@
       <c r="D2666" s="12" t="s">
         <v>5666</v>
       </c>
-      <c r="F2666" s="2"/>
+      <c r="E2666" s="2"/>
+      <c r="F2666" s="3"/>
     </row>
     <row r="2667" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2667" s="8" t="s">
@@ -91316,7 +92124,8 @@
       <c r="D2667" s="12" t="s">
         <v>5668</v>
       </c>
-      <c r="F2667" s="2"/>
+      <c r="E2667" s="2"/>
+      <c r="F2667" s="3"/>
     </row>
     <row r="2668" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2668" s="8" t="s">
@@ -91331,7 +92140,8 @@
       <c r="D2668" s="12" t="s">
         <v>5670</v>
       </c>
-      <c r="F2668" s="2"/>
+      <c r="E2668" s="2"/>
+      <c r="F2668" s="3"/>
     </row>
     <row r="2669" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2669" s="8" t="s">
@@ -91346,7 +92156,8 @@
       <c r="D2669" s="12" t="s">
         <v>5672</v>
       </c>
-      <c r="F2669" s="2"/>
+      <c r="E2669" s="2"/>
+      <c r="F2669" s="3"/>
     </row>
     <row r="2670" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2670" s="8" t="s">
@@ -91361,7 +92172,8 @@
       <c r="D2670" s="12" t="s">
         <v>5675</v>
       </c>
-      <c r="F2670" s="2"/>
+      <c r="E2670" s="2"/>
+      <c r="F2670" s="3"/>
     </row>
     <row r="2671" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2671" s="8" t="s">
@@ -91376,7 +92188,8 @@
       <c r="D2671" s="12" t="s">
         <v>5677</v>
       </c>
-      <c r="F2671" s="2"/>
+      <c r="E2671" s="2"/>
+      <c r="F2671" s="3"/>
     </row>
     <row r="2672" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2672" s="8" t="s">
@@ -91391,7 +92204,8 @@
       <c r="D2672" s="12" t="s">
         <v>5679</v>
       </c>
-      <c r="F2672" s="2"/>
+      <c r="E2672" s="2"/>
+      <c r="F2672" s="3"/>
     </row>
     <row r="2673" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2673" s="8" t="s">
@@ -91406,7 +92220,8 @@
       <c r="D2673" s="12" t="s">
         <v>5681</v>
       </c>
-      <c r="F2673" s="2"/>
+      <c r="E2673" s="2"/>
+      <c r="F2673" s="3"/>
     </row>
     <row r="2674" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2674" s="8" t="s">
@@ -91421,7 +92236,8 @@
       <c r="D2674" s="12" t="s">
         <v>5683</v>
       </c>
-      <c r="F2674" s="2"/>
+      <c r="E2674" s="2"/>
+      <c r="F2674" s="3"/>
     </row>
     <row r="2675" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2675" s="8" t="s">
@@ -91436,7 +92252,8 @@
       <c r="D2675" s="12" t="s">
         <v>5685</v>
       </c>
-      <c r="F2675" s="2"/>
+      <c r="E2675" s="2"/>
+      <c r="F2675" s="3"/>
     </row>
     <row r="2676" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2676" s="8" t="s">
@@ -91451,7 +92268,8 @@
       <c r="D2676" s="12" t="s">
         <v>5687</v>
       </c>
-      <c r="F2676" s="2"/>
+      <c r="E2676" s="2"/>
+      <c r="F2676" s="3"/>
     </row>
     <row r="2677" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2677" s="8" t="s">
@@ -91466,7 +92284,8 @@
       <c r="D2677" s="12" t="s">
         <v>5689</v>
       </c>
-      <c r="F2677" s="2"/>
+      <c r="E2677" s="2"/>
+      <c r="F2677" s="3"/>
     </row>
     <row r="2678" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2678" s="8" t="s">
@@ -91481,7 +92300,8 @@
       <c r="D2678" s="12" t="s">
         <v>5692</v>
       </c>
-      <c r="F2678" s="2"/>
+      <c r="E2678" s="2"/>
+      <c r="F2678" s="3"/>
     </row>
     <row r="2679" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2679" s="8" t="s">
@@ -91496,7 +92316,8 @@
       <c r="D2679" s="12" t="s">
         <v>5694</v>
       </c>
-      <c r="F2679" s="2"/>
+      <c r="E2679" s="2"/>
+      <c r="F2679" s="3"/>
     </row>
     <row r="2680" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2680" s="8" t="s">
@@ -91511,7 +92332,8 @@
       <c r="D2680" s="12" t="s">
         <v>5696</v>
       </c>
-      <c r="F2680" s="2"/>
+      <c r="E2680" s="2"/>
+      <c r="F2680" s="3"/>
     </row>
     <row r="2681" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2681" s="8" t="s">
@@ -91526,7 +92348,8 @@
       <c r="D2681" s="12" t="s">
         <v>5698</v>
       </c>
-      <c r="F2681" s="2"/>
+      <c r="E2681" s="2"/>
+      <c r="F2681" s="3"/>
     </row>
     <row r="2682" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2682" s="8" t="s">
@@ -91541,7 +92364,8 @@
       <c r="D2682" s="12" t="s">
         <v>5700</v>
       </c>
-      <c r="F2682" s="2"/>
+      <c r="E2682" s="2"/>
+      <c r="F2682" s="3"/>
     </row>
     <row r="2683" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2683" s="8" t="s">
@@ -91556,7 +92380,8 @@
       <c r="D2683" s="12" t="s">
         <v>5702</v>
       </c>
-      <c r="F2683" s="2"/>
+      <c r="E2683" s="2"/>
+      <c r="F2683" s="3"/>
     </row>
     <row r="2684" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2684" s="8" t="s">
@@ -91571,7 +92396,8 @@
       <c r="D2684" s="12" t="s">
         <v>5704</v>
       </c>
-      <c r="F2684" s="2"/>
+      <c r="E2684" s="2"/>
+      <c r="F2684" s="3"/>
     </row>
     <row r="2685" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2685" s="8" t="s">
@@ -91586,7 +92412,8 @@
       <c r="D2685" s="12" t="s">
         <v>5706</v>
       </c>
-      <c r="F2685" s="2"/>
+      <c r="E2685" s="2"/>
+      <c r="F2685" s="3"/>
     </row>
     <row r="2686" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2686" s="8" t="s">
@@ -91601,7 +92428,8 @@
       <c r="D2686" s="12" t="s">
         <v>5708</v>
       </c>
-      <c r="F2686" s="2"/>
+      <c r="E2686" s="2"/>
+      <c r="F2686" s="3"/>
     </row>
     <row r="2687" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2687" s="8" t="s">
@@ -91616,7 +92444,8 @@
       <c r="D2687" s="12" t="s">
         <v>5710</v>
       </c>
-      <c r="F2687" s="2"/>
+      <c r="E2687" s="2"/>
+      <c r="F2687" s="3"/>
     </row>
     <row r="2688" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2688" s="8" t="s">
@@ -91631,7 +92460,8 @@
       <c r="D2688" s="12" t="s">
         <v>5713</v>
       </c>
-      <c r="F2688" s="2"/>
+      <c r="E2688" s="2"/>
+      <c r="F2688" s="3"/>
     </row>
     <row r="2689" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2689" s="8" t="s">
@@ -91646,7 +92476,8 @@
       <c r="D2689" s="12" t="s">
         <v>5715</v>
       </c>
-      <c r="F2689" s="2"/>
+      <c r="E2689" s="2"/>
+      <c r="F2689" s="3"/>
     </row>
     <row r="2690" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2690" s="8" t="s">
@@ -91661,7 +92492,8 @@
       <c r="D2690" s="12" t="s">
         <v>5717</v>
       </c>
-      <c r="F2690" s="2"/>
+      <c r="E2690" s="2"/>
+      <c r="F2690" s="3"/>
     </row>
     <row r="2691" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2691" s="8" t="s">
@@ -91676,7 +92508,8 @@
       <c r="D2691" s="12" t="s">
         <v>5719</v>
       </c>
-      <c r="F2691" s="2"/>
+      <c r="E2691" s="2"/>
+      <c r="F2691" s="3"/>
     </row>
     <row r="2692" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2692" s="8" t="s">
@@ -91691,7 +92524,8 @@
       <c r="D2692" s="12" t="s">
         <v>5721</v>
       </c>
-      <c r="F2692" s="2"/>
+      <c r="E2692" s="2"/>
+      <c r="F2692" s="3"/>
     </row>
     <row r="2693" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2693" s="8" t="s">
@@ -91706,7 +92540,8 @@
       <c r="D2693" s="12" t="s">
         <v>5723</v>
       </c>
-      <c r="F2693" s="2"/>
+      <c r="E2693" s="2"/>
+      <c r="F2693" s="3"/>
     </row>
     <row r="2694" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2694" s="8" t="s">
@@ -91721,7 +92556,8 @@
       <c r="D2694" s="12" t="s">
         <v>5725</v>
       </c>
-      <c r="F2694" s="2"/>
+      <c r="E2694" s="2"/>
+      <c r="F2694" s="3"/>
     </row>
     <row r="2695" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2695" s="8" t="s">
@@ -91736,7 +92572,8 @@
       <c r="D2695" s="12" t="s">
         <v>5728</v>
       </c>
-      <c r="F2695" s="2"/>
+      <c r="E2695" s="2"/>
+      <c r="F2695" s="3"/>
     </row>
     <row r="2696" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2696" s="8" t="s">
@@ -91751,7 +92588,8 @@
       <c r="D2696" s="12" t="s">
         <v>5730</v>
       </c>
-      <c r="F2696" s="2"/>
+      <c r="E2696" s="2"/>
+      <c r="F2696" s="3"/>
     </row>
     <row r="2697" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2697" s="8" t="s">
@@ -91766,7 +92604,8 @@
       <c r="D2697" s="12" t="s">
         <v>5732</v>
       </c>
-      <c r="F2697" s="2"/>
+      <c r="E2697" s="2"/>
+      <c r="F2697" s="3"/>
     </row>
     <row r="2698" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2698" s="8" t="s">
@@ -91781,7 +92620,8 @@
       <c r="D2698" s="12" t="s">
         <v>5734</v>
       </c>
-      <c r="F2698" s="2"/>
+      <c r="E2698" s="2"/>
+      <c r="F2698" s="3"/>
     </row>
     <row r="2699" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2699" s="8" t="s">
@@ -91796,7 +92636,8 @@
       <c r="D2699" s="12" t="s">
         <v>5736</v>
       </c>
-      <c r="F2699" s="2"/>
+      <c r="E2699" s="2"/>
+      <c r="F2699" s="3"/>
     </row>
     <row r="2700" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2700" s="8" t="s">
@@ -91811,7 +92652,8 @@
       <c r="D2700" s="12" t="s">
         <v>5738</v>
       </c>
-      <c r="F2700" s="2"/>
+      <c r="E2700" s="2"/>
+      <c r="F2700" s="3"/>
     </row>
     <row r="2701" s="1" customFormat="1" ht="17" spans="1:6">
       <c r="A2701" s="8" t="s">
@@ -91826,7 +92668,8 @@
       <c r="D2701" s="12" t="s">
         <v>5740</v>
       </c>
-      <c r="F2701" s="2"/>
+      <c r="E2701" s="2"/>
+      <c r="F2701" s="3"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F2701" etc:filterBottomFollowUsedRange="0">
